--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198085</t>
+          <t>2026-03-02T04:10:34.999713</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198099</t>
+          <t>2026-03-02T04:10:34.999727</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198103</t>
+          <t>2026-03-02T04:10:34.999731</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198106</t>
+          <t>2026-03-02T04:10:34.999734</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198112</t>
+          <t>2026-03-02T04:10:34.999741</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198115</t>
+          <t>2026-03-02T04:10:34.999744</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198118</t>
+          <t>2026-03-02T04:10:34.999746</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198121</t>
+          <t>2026-03-02T04:10:34.999749</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198123</t>
+          <t>2026-03-02T04:10:34.999752</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198126</t>
+          <t>2026-03-02T04:10:34.999755</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198129</t>
+          <t>2026-03-02T04:10:34.999758</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198132</t>
+          <t>2026-03-02T04:10:34.999760</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198135</t>
+          <t>2026-03-02T04:10:34.999763</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198137</t>
+          <t>2026-03-02T04:10:34.999766</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198146</t>
+          <t>2026-03-02T04:10:34.999771</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198151</t>
+          <t>2026-03-02T04:10:34.999774</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198154</t>
+          <t>2026-03-02T04:10:34.999778</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198157</t>
+          <t>2026-03-02T04:10:34.999781</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198159</t>
+          <t>2026-03-02T04:10:34.999784</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198162</t>
+          <t>2026-03-02T04:10:34.999788</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198165</t>
+          <t>2026-03-02T04:10:34.999791</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198168</t>
+          <t>2026-03-02T04:10:34.999793</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198171</t>
+          <t>2026-03-02T04:10:34.999796</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198173</t>
+          <t>2026-03-02T04:10:34.999799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198177</t>
+          <t>2026-03-02T04:10:34.999802</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198179</t>
+          <t>2026-03-02T04:10:34.999805</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198182</t>
+          <t>2026-03-02T04:10:34.999807</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198185</t>
+          <t>2026-03-02T04:10:34.999810</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198188</t>
+          <t>2026-03-02T04:10:34.999813</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198190</t>
+          <t>2026-03-02T04:10:34.999816</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198193</t>
+          <t>2026-03-02T04:10:34.999818</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198196</t>
+          <t>2026-03-02T04:10:34.999821</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1545.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198198</t>
+          <t>2026-03-02T04:10:34.999824</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198201</t>
+          <t>2026-03-02T04:10:34.999826</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198204</t>
+          <t>2026-03-02T04:10:34.999829</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198206</t>
+          <t>2026-03-02T04:10:34.999832</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1518.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1518</v>
+        <v>1538</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198209</t>
+          <t>2026-03-02T04:10:34.999835</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198212</t>
+          <t>2026-03-02T04:10:34.999837</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198215</t>
+          <t>2026-03-02T04:10:34.999840</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198217</t>
+          <t>2026-03-02T04:10:34.999842</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198220</t>
+          <t>2026-03-02T04:10:34.999845</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198223</t>
+          <t>2026-03-02T04:10:34.999848</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1499.00</t>
+          <t>1518.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1499</v>
+        <v>1518</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198226</t>
+          <t>2026-03-02T04:10:34.999851</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1497.00</t>
+          <t>1543.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1497</v>
+        <v>1543</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198228</t>
+          <t>2026-03-02T04:10:34.999854</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1497.00</t>
+          <t>1543.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1497</v>
+        <v>1543</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198231</t>
+          <t>2026-03-02T04:10:34.999856</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1505.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1492</v>
+        <v>1505</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198234</t>
+          <t>2026-03-02T04:10:34.999859</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1499.00</t>
+          <t>1545.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1499</v>
+        <v>1545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198237</t>
+          <t>2026-03-02T04:10:34.999862</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1502.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1502</v>
+        <v>1550</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198240</t>
+          <t>2026-03-02T04:10:34.999864</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1500.00</t>
+          <t>1502.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198242</t>
+          <t>2026-03-02T04:10:34.999867</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1502.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1502</v>
+        <v>1492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-01T04:19:55.198245</t>
+          <t>2026-03-02T04:10:34.999870</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999713</t>
+          <t>2026-03-03T04:11:30.822997</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999727</t>
+          <t>2026-03-03T04:11:30.823010</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999731</t>
+          <t>2026-03-03T04:11:30.823014</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999734</t>
+          <t>2026-03-03T04:11:30.823017</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999741</t>
+          <t>2026-03-03T04:11:30.823021</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999744</t>
+          <t>2026-03-03T04:11:30.823024</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999746</t>
+          <t>2026-03-03T04:11:30.823027</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999749</t>
+          <t>2026-03-03T04:11:30.823030</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999752</t>
+          <t>2026-03-03T04:11:30.823033</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999755</t>
+          <t>2026-03-03T04:11:30.823036</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999758</t>
+          <t>2026-03-03T04:11:30.823039</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999760</t>
+          <t>2026-03-03T04:11:30.823042</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999763</t>
+          <t>2026-03-03T04:11:30.823044</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999766</t>
+          <t>2026-03-03T04:11:30.823047</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999771</t>
+          <t>2026-03-03T04:11:30.823052</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999774</t>
+          <t>2026-03-03T04:11:30.823055</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999778</t>
+          <t>2026-03-03T04:11:30.823058</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999781</t>
+          <t>2026-03-03T04:11:30.823061</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999784</t>
+          <t>2026-03-03T04:11:30.823064</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999788</t>
+          <t>2026-03-03T04:11:30.823067</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999791</t>
+          <t>2026-03-03T04:11:30.823069</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999793</t>
+          <t>2026-03-03T04:11:30.823073</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999796</t>
+          <t>2026-03-03T04:11:30.823078</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999799</t>
+          <t>2026-03-03T04:11:30.823083</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999802</t>
+          <t>2026-03-03T04:11:30.823088</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999805</t>
+          <t>2026-03-03T04:11:30.823093</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999807</t>
+          <t>2026-03-03T04:11:30.823097</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999810</t>
+          <t>2026-03-03T04:11:30.823102</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999813</t>
+          <t>2026-03-03T04:11:30.823110</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999816</t>
+          <t>2026-03-03T04:11:30.823114</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999818</t>
+          <t>2026-03-03T04:11:30.823117</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999821</t>
+          <t>2026-03-03T04:11:30.823120</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999824</t>
+          <t>2026-03-03T04:11:30.823123</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999826</t>
+          <t>2026-03-03T04:11:30.823126</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999829</t>
+          <t>2026-03-03T04:11:30.823145</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999832</t>
+          <t>2026-03-03T04:11:30.823156</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999835</t>
+          <t>2026-03-03T04:11:30.823160</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1545.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999837</t>
+          <t>2026-03-03T04:11:30.823163</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999840</t>
+          <t>2026-03-03T04:11:30.823166</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999842</t>
+          <t>2026-03-03T04:11:30.823169</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999845</t>
+          <t>2026-03-03T04:11:30.823172</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999848</t>
+          <t>2026-03-03T04:11:30.823175</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1518.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1518</v>
+        <v>1538</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999851</t>
+          <t>2026-03-03T04:11:30.823178</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999854</t>
+          <t>2026-03-03T04:11:30.823181</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999856</t>
+          <t>2026-03-03T04:11:30.823184</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999859</t>
+          <t>2026-03-03T04:11:30.823187</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999862</t>
+          <t>2026-03-03T04:11:30.823190</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999864</t>
+          <t>2026-03-03T04:11:30.823193</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1502.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1502</v>
+        <v>1550</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999867</t>
+          <t>2026-03-03T04:11:30.823195</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1505.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1492</v>
+        <v>1505</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-02T04:10:34.999870</t>
+          <t>2026-03-03T04:11:30.823198</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.822997</t>
+          <t>2026-03-04T04:05:07.980078</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823010</t>
+          <t>2026-03-04T04:05:07.980092</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823014</t>
+          <t>2026-03-04T04:05:07.980095</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823017</t>
+          <t>2026-03-04T04:05:07.980100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823021</t>
+          <t>2026-03-04T04:05:07.980111</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823024</t>
+          <t>2026-03-04T04:05:07.980114</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823027</t>
+          <t>2026-03-04T04:05:07.980117</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823030</t>
+          <t>2026-03-04T04:05:07.980120</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823033</t>
+          <t>2026-03-04T04:05:07.980123</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823036</t>
+          <t>2026-03-04T04:05:07.980126</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823039</t>
+          <t>2026-03-04T04:05:07.980129</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823042</t>
+          <t>2026-03-04T04:05:07.980131</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823044</t>
+          <t>2026-03-04T04:05:07.980134</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823047</t>
+          <t>2026-03-04T04:05:07.980137</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823052</t>
+          <t>2026-03-04T04:05:07.980141</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823055</t>
+          <t>2026-03-04T04:05:07.980145</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823058</t>
+          <t>2026-03-04T04:05:07.980148</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823061</t>
+          <t>2026-03-04T04:05:07.980150</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823064</t>
+          <t>2026-03-04T04:05:07.980153</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823067</t>
+          <t>2026-03-04T04:05:07.980156</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823069</t>
+          <t>2026-03-04T04:05:07.980159</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823073</t>
+          <t>2026-03-04T04:05:07.980161</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823078</t>
+          <t>2026-03-04T04:05:07.980164</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823083</t>
+          <t>2026-03-04T04:05:07.980167</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823088</t>
+          <t>2026-03-04T04:05:07.980170</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823093</t>
+          <t>2026-03-04T04:05:07.980173</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823097</t>
+          <t>2026-03-04T04:05:07.980175</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823102</t>
+          <t>2026-03-04T04:05:07.980178</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823110</t>
+          <t>2026-03-04T04:05:07.980181</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823114</t>
+          <t>2026-03-04T04:05:07.980184</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823117</t>
+          <t>2026-03-04T04:05:07.980186</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823120</t>
+          <t>2026-03-04T04:05:07.980189</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823123</t>
+          <t>2026-03-04T04:05:07.980191</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823126</t>
+          <t>2026-03-04T04:05:07.980194</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823145</t>
+          <t>2026-03-04T04:05:07.980197</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823156</t>
+          <t>2026-03-04T04:05:07.980200</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823160</t>
+          <t>2026-03-04T04:05:07.980202</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823163</t>
+          <t>2026-03-04T04:05:07.980205</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823166</t>
+          <t>2026-03-04T04:05:07.980208</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823169</t>
+          <t>2026-03-04T04:05:07.980210</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823172</t>
+          <t>2026-03-04T04:05:07.980213</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823175</t>
+          <t>2026-03-04T04:05:07.980216</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1538</v>
+        <v>1565</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823178</t>
+          <t>2026-03-04T04:05:07.980219</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823181</t>
+          <t>2026-03-04T04:05:07.980221</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1543.00</t>
+          <t>1563.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1543</v>
+        <v>1563</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823184</t>
+          <t>2026-03-04T04:05:07.980224</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823187</t>
+          <t>2026-03-04T04:05:07.980227</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1545.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1545</v>
+        <v>1565</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823190</t>
+          <t>2026-03-04T04:05:07.980230</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823193</t>
+          <t>2026-03-04T04:05:07.980232</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823195</t>
+          <t>2026-03-04T04:05:07.980235</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-21</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-03T04:11:30.823198</t>
+          <t>2026-03-04T04:05:07.980238</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980078</t>
+          <t>2026-03-05T04:09:02.928761</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980092</t>
+          <t>2026-03-05T04:09:02.928774</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980095</t>
+          <t>2026-03-05T04:09:02.928778</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980100</t>
+          <t>2026-03-05T04:09:02.928781</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980111</t>
+          <t>2026-03-05T04:09:02.928787</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980114</t>
+          <t>2026-03-05T04:09:02.928790</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980117</t>
+          <t>2026-03-05T04:09:02.928793</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980120</t>
+          <t>2026-03-05T04:09:02.928796</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980123</t>
+          <t>2026-03-05T04:09:02.928799</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980126</t>
+          <t>2026-03-05T04:09:02.928802</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980129</t>
+          <t>2026-03-05T04:09:02.928804</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980131</t>
+          <t>2026-03-05T04:09:02.928807</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980134</t>
+          <t>2026-03-05T04:09:02.928810</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980137</t>
+          <t>2026-03-05T04:09:02.928813</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980141</t>
+          <t>2026-03-05T04:09:02.928818</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980145</t>
+          <t>2026-03-05T04:09:02.928821</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980148</t>
+          <t>2026-03-05T04:09:02.928824</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980150</t>
+          <t>2026-03-05T04:09:02.928827</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980153</t>
+          <t>2026-03-05T04:09:02.928830</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980156</t>
+          <t>2026-03-05T04:09:02.928833</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980159</t>
+          <t>2026-03-05T04:09:02.928835</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980161</t>
+          <t>2026-03-05T04:09:02.928838</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980164</t>
+          <t>2026-03-05T04:09:02.928841</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980167</t>
+          <t>2026-03-05T04:09:02.928844</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980170</t>
+          <t>2026-03-05T04:09:02.928847</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980173</t>
+          <t>2026-03-05T04:09:02.928850</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980175</t>
+          <t>2026-03-05T04:09:02.928853</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980178</t>
+          <t>2026-03-05T04:09:02.928855</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980181</t>
+          <t>2026-03-05T04:09:02.928858</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980184</t>
+          <t>2026-03-05T04:09:02.928861</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980186</t>
+          <t>2026-03-05T04:09:02.928864</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980189</t>
+          <t>2026-03-05T04:09:02.928866</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980191</t>
+          <t>2026-03-05T04:09:02.928869</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980194</t>
+          <t>2026-03-05T04:09:02.928872</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980197</t>
+          <t>2026-03-05T04:09:02.928875</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980200</t>
+          <t>2026-03-05T04:09:02.928877</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980202</t>
+          <t>2026-03-05T04:09:02.928880</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980205</t>
+          <t>2026-03-05T04:09:02.928883</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980208</t>
+          <t>2026-03-05T04:09:02.928885</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980210</t>
+          <t>2026-03-05T04:09:02.928888</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980213</t>
+          <t>2026-03-05T04:09:02.928891</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980216</t>
+          <t>2026-03-05T04:09:02.928893</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980219</t>
+          <t>2026-03-05T04:09:02.928896</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980221</t>
+          <t>2026-03-05T04:09:02.928899</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1563.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1563</v>
+        <v>1568</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980224</t>
+          <t>2026-03-05T04:09:02.928902</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980227</t>
+          <t>2026-03-05T04:09:02.928905</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1565</v>
+        <v>1570</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980230</t>
+          <t>2026-03-05T04:09:02.928907</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980232</t>
+          <t>2026-03-05T04:09:02.928910</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1550</v>
+        <v>1570</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980235</t>
+          <t>2026-03-05T04:09:02.928913</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1505.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1505</v>
+        <v>1535</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-04T04:05:07.980238</t>
+          <t>2026-03-05T04:09:02.928916</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928761</t>
+          <t>2026-03-06T04:06:05.174366</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928774</t>
+          <t>2026-03-06T04:06:05.174382</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928778</t>
+          <t>2026-03-06T04:06:05.174385</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928781</t>
+          <t>2026-03-06T04:06:05.174388</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928787</t>
+          <t>2026-03-06T04:06:05.174395</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928790</t>
+          <t>2026-03-06T04:06:05.174398</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928793</t>
+          <t>2026-03-06T04:06:05.174401</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928796</t>
+          <t>2026-03-06T04:06:05.174404</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928799</t>
+          <t>2026-03-06T04:06:05.174407</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928802</t>
+          <t>2026-03-06T04:06:05.174410</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928804</t>
+          <t>2026-03-06T04:06:05.174412</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928807</t>
+          <t>2026-03-06T04:06:05.174415</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928810</t>
+          <t>2026-03-06T04:06:05.174418</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928813</t>
+          <t>2026-03-06T04:06:05.174421</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928818</t>
+          <t>2026-03-06T04:06:05.174426</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928821</t>
+          <t>2026-03-06T04:06:05.174429</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928824</t>
+          <t>2026-03-06T04:06:05.174432</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928827</t>
+          <t>2026-03-06T04:06:05.174435</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928830</t>
+          <t>2026-03-06T04:06:05.174438</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928833</t>
+          <t>2026-03-06T04:06:05.174441</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928835</t>
+          <t>2026-03-06T04:06:05.174443</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928838</t>
+          <t>2026-03-06T04:06:05.174446</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928841</t>
+          <t>2026-03-06T04:06:05.174449</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928844</t>
+          <t>2026-03-06T04:06:05.174452</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928847</t>
+          <t>2026-03-06T04:06:05.174455</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928850</t>
+          <t>2026-03-06T04:06:05.174458</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928853</t>
+          <t>2026-03-06T04:06:05.174461</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928855</t>
+          <t>2026-03-06T04:06:05.174464</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928858</t>
+          <t>2026-03-06T04:06:05.174466</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928861</t>
+          <t>2026-03-06T04:06:05.174469</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928864</t>
+          <t>2026-03-06T04:06:05.174472</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928866</t>
+          <t>2026-03-06T04:06:05.174476</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928869</t>
+          <t>2026-03-06T04:06:05.174480</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928872</t>
+          <t>2026-03-06T04:06:05.174483</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928875</t>
+          <t>2026-03-06T04:06:05.174486</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928877</t>
+          <t>2026-03-06T04:06:05.174488</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928880</t>
+          <t>2026-03-06T04:06:05.174491</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928883</t>
+          <t>2026-03-06T04:06:05.174494</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928885</t>
+          <t>2026-03-06T04:06:05.174497</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928888</t>
+          <t>2026-03-06T04:06:05.174499</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928891</t>
+          <t>2026-03-06T04:06:05.174502</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928893</t>
+          <t>2026-03-06T04:06:05.174505</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928896</t>
+          <t>2026-03-06T04:06:05.174508</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928899</t>
+          <t>2026-03-06T04:06:05.174511</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928902</t>
+          <t>2026-03-06T04:06:05.174514</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928905</t>
+          <t>2026-03-06T04:06:05.174517</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1570</v>
+        <v>1576</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928907</t>
+          <t>2026-03-06T04:06:05.174519</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928910</t>
+          <t>2026-03-06T04:06:05.174522</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928913</t>
+          <t>2026-03-06T04:06:05.174525</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-05T04:09:02.928916</t>
+          <t>2026-03-06T04:06:05.174528</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174366</t>
+          <t>2026-03-07T03:57:01.332924</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1577</v>
+        <v>1555</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174382</t>
+          <t>2026-03-07T03:57:01.332935</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174385</t>
+          <t>2026-03-07T03:57:01.332938</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1555</v>
+        <v>1577</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174388</t>
+          <t>2026-03-07T03:57:01.332941</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1580</v>
+        <v>1577</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174395</t>
+          <t>2026-03-07T03:57:01.332944</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174398</t>
+          <t>2026-03-07T03:57:01.332951</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174401</t>
+          <t>2026-03-07T03:57:01.332954</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174404</t>
+          <t>2026-03-07T03:57:01.332957</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1590</v>
+        <v>1597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174407</t>
+          <t>2026-03-07T03:57:01.332959</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1565</v>
+        <v>1599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174410</t>
+          <t>2026-03-07T03:57:01.332962</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1596</v>
+        <v>1565</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174412</t>
+          <t>2026-03-07T03:57:01.332965</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1597</v>
+        <v>1590</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174415</t>
+          <t>2026-03-07T03:57:01.332968</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1565</v>
+        <v>1597</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174418</t>
+          <t>2026-03-07T03:57:01.332971</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1603</v>
+        <v>1597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174421</t>
+          <t>2026-03-07T03:57:01.332974</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1597</v>
+        <v>1565</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174426</t>
+          <t>2026-03-07T03:57:01.332976</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174429</t>
+          <t>2026-03-07T03:57:01.332996</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1596</v>
+        <v>1603</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174432</t>
+          <t>2026-03-07T03:57:01.333000</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174435</t>
+          <t>2026-03-07T03:57:01.333003</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1642</v>
+        <v>1585</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174438</t>
+          <t>2026-03-07T03:57:01.333006</t>
         </is>
       </c>
     </row>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174441</t>
+          <t>2026-03-07T03:57:01.333009</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174443</t>
+          <t>2026-03-07T03:57:01.333012</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1650</v>
+        <v>1642</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174446</t>
+          <t>2026-03-07T03:57:01.333014</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174449</t>
+          <t>2026-03-07T03:57:01.333018</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1585</v>
+        <v>1650</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174452</t>
+          <t>2026-03-07T03:57:01.333021</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174455</t>
+          <t>2026-03-07T03:57:01.333025</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1622</v>
+        <v>1585</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174458</t>
+          <t>2026-03-07T03:57:01.333029</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174461</t>
+          <t>2026-03-07T03:57:01.333032</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1585</v>
+        <v>1620</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174464</t>
+          <t>2026-03-07T03:57:01.333035</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1620</v>
+        <v>1624</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174466</t>
+          <t>2026-03-07T03:57:01.333037</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174469</t>
+          <t>2026-03-07T03:57:01.333040</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1555</v>
+        <v>1606</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174472</t>
+          <t>2026-03-07T03:57:01.333043</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1602</v>
+        <v>1608</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174476</t>
+          <t>2026-03-07T03:57:01.333045</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174480</t>
+          <t>2026-03-07T03:57:01.333048</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1606</v>
+        <v>1602</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174483</t>
+          <t>2026-03-07T03:57:01.333051</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174486</t>
+          <t>2026-03-07T03:57:01.333053</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1608</v>
+        <v>1555</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174488</t>
+          <t>2026-03-07T03:57:01.333056</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174491</t>
+          <t>2026-03-07T03:57:01.333059</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174494</t>
+          <t>2026-03-07T03:57:01.333062</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1570</v>
+        <v>1574</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174497</t>
+          <t>2026-03-07T03:57:01.333064</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174499</t>
+          <t>2026-03-07T03:57:01.333067</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174502</t>
+          <t>2026-03-07T03:57:01.333070</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1574</v>
+        <v>1570</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174505</t>
+          <t>2026-03-07T03:57:01.333072</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1566</v>
+        <v>1574</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174508</t>
+          <t>2026-03-07T03:57:01.333075</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1535.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1574</v>
+        <v>1535</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174511</t>
+          <t>2026-03-07T03:57:01.333078</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1574</v>
+        <v>1568</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174514</t>
+          <t>2026-03-07T03:57:01.333080</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1535</v>
+        <v>1574</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174517</t>
+          <t>2026-03-07T03:57:01.333083</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174519</t>
+          <t>2026-03-07T03:57:01.333086</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1566.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174522</t>
+          <t>2026-03-07T03:57:01.333089</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174525</t>
+          <t>2026-03-07T03:57:01.333092</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1568.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1535</v>
+        <v>1568</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-06T04:06:05.174528</t>
+          <t>2026-03-07T03:57:01.333094</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332924</t>
+          <t>2026-03-08T04:07:51.386085</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332935</t>
+          <t>2026-03-08T04:07:51.386100</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332938</t>
+          <t>2026-03-08T04:07:51.386103</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332941</t>
+          <t>2026-03-08T04:07:51.386107</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332944</t>
+          <t>2026-03-08T04:07:51.386110</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332951</t>
+          <t>2026-03-08T04:07:51.386112</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332954</t>
+          <t>2026-03-08T04:07:51.386116</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332957</t>
+          <t>2026-03-08T04:07:51.386118</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332959</t>
+          <t>2026-03-08T04:07:51.386124</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332962</t>
+          <t>2026-03-08T04:07:51.386127</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332965</t>
+          <t>2026-03-08T04:07:51.386130</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332968</t>
+          <t>2026-03-08T04:07:51.386132</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332971</t>
+          <t>2026-03-08T04:07:51.386135</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332974</t>
+          <t>2026-03-08T04:07:51.386138</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332976</t>
+          <t>2026-03-08T04:07:51.386141</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.332996</t>
+          <t>2026-03-08T04:07:51.386144</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333000</t>
+          <t>2026-03-08T04:07:51.386146</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333003</t>
+          <t>2026-03-08T04:07:51.386149</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333006</t>
+          <t>2026-03-08T04:07:51.386155</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333009</t>
+          <t>2026-03-08T04:07:51.386158</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333012</t>
+          <t>2026-03-08T04:07:51.386160</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333014</t>
+          <t>2026-03-08T04:07:51.386164</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333018</t>
+          <t>2026-03-08T04:07:51.386166</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333021</t>
+          <t>2026-03-08T04:07:51.386169</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333025</t>
+          <t>2026-03-08T04:07:51.386172</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333029</t>
+          <t>2026-03-08T04:07:51.386175</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333032</t>
+          <t>2026-03-08T04:07:51.386178</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333035</t>
+          <t>2026-03-08T04:07:51.386180</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333037</t>
+          <t>2026-03-08T04:07:51.386183</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333040</t>
+          <t>2026-03-08T04:07:51.386186</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333043</t>
+          <t>2026-03-08T04:07:51.386189</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333045</t>
+          <t>2026-03-08T04:07:51.386192</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333048</t>
+          <t>2026-03-08T04:07:51.386195</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333051</t>
+          <t>2026-03-08T04:07:51.386198</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333053</t>
+          <t>2026-03-08T04:07:51.386201</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333056</t>
+          <t>2026-03-08T04:07:51.386203</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333059</t>
+          <t>2026-03-08T04:07:51.386206</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333062</t>
+          <t>2026-03-08T04:07:51.386209</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333064</t>
+          <t>2026-03-08T04:07:51.386212</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333067</t>
+          <t>2026-03-08T04:07:51.386214</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333070</t>
+          <t>2026-03-08T04:07:51.386217</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333072</t>
+          <t>2026-03-08T04:07:51.386220</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333075</t>
+          <t>2026-03-08T04:07:51.386223</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333078</t>
+          <t>2026-03-08T04:07:51.386225</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333080</t>
+          <t>2026-03-08T04:07:51.386228</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333083</t>
+          <t>2026-03-08T04:07:51.386231</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333086</t>
+          <t>2026-03-08T04:07:51.386234</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333089</t>
+          <t>2026-03-08T04:07:51.386237</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333092</t>
+          <t>2026-03-08T04:07:51.386239</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1574.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1568</v>
+        <v>1574</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-07T03:57:01.333094</t>
+          <t>2026-03-08T04:07:51.386242</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386085</t>
+          <t>2026-03-09T04:13:11.031932</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386100</t>
+          <t>2026-03-09T04:13:11.031945</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386103</t>
+          <t>2026-03-09T04:13:11.031949</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386107</t>
+          <t>2026-03-09T04:13:11.031952</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386110</t>
+          <t>2026-03-09T04:13:11.031955</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386112</t>
+          <t>2026-03-09T04:13:11.031958</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386116</t>
+          <t>2026-03-09T04:13:11.031961</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386118</t>
+          <t>2026-03-09T04:13:11.031963</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386124</t>
+          <t>2026-03-09T04:13:11.031969</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386127</t>
+          <t>2026-03-09T04:13:11.031972</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386130</t>
+          <t>2026-03-09T04:13:11.031975</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386132</t>
+          <t>2026-03-09T04:13:11.031977</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386135</t>
+          <t>2026-03-09T04:13:11.031980</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386138</t>
+          <t>2026-03-09T04:13:11.031983</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386141</t>
+          <t>2026-03-09T04:13:11.031986</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386144</t>
+          <t>2026-03-09T04:13:11.031988</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386146</t>
+          <t>2026-03-09T04:13:11.031991</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386149</t>
+          <t>2026-03-09T04:13:11.031997</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386155</t>
+          <t>2026-03-09T04:13:11.032008</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386158</t>
+          <t>2026-03-09T04:13:11.032011</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386160</t>
+          <t>2026-03-09T04:13:11.032013</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386164</t>
+          <t>2026-03-09T04:13:11.032016</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386166</t>
+          <t>2026-03-09T04:13:11.032019</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386169</t>
+          <t>2026-03-09T04:13:11.032022</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386172</t>
+          <t>2026-03-09T04:13:11.032025</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386175</t>
+          <t>2026-03-09T04:13:11.032028</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386178</t>
+          <t>2026-03-09T04:13:11.032030</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386180</t>
+          <t>2026-03-09T04:13:11.032033</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386183</t>
+          <t>2026-03-09T04:13:11.032036</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386186</t>
+          <t>2026-03-09T04:13:11.032039</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386189</t>
+          <t>2026-03-09T04:13:11.032042</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386192</t>
+          <t>2026-03-09T04:13:11.032044</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386195</t>
+          <t>2026-03-09T04:13:11.032047</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386198</t>
+          <t>2026-03-09T04:13:11.032050</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386201</t>
+          <t>2026-03-09T04:13:11.032052</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386203</t>
+          <t>2026-03-09T04:13:11.032055</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386206</t>
+          <t>2026-03-09T04:13:11.032058</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386209</t>
+          <t>2026-03-09T04:13:11.032060</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386212</t>
+          <t>2026-03-09T04:13:11.032063</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386214</t>
+          <t>2026-03-09T04:13:11.032066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386217</t>
+          <t>2026-03-09T04:13:11.032068</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386220</t>
+          <t>2026-03-09T04:13:11.032071</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386223</t>
+          <t>2026-03-09T04:13:11.032074</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1535.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1535</v>
+        <v>1555</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386225</t>
+          <t>2026-03-09T04:13:11.032077</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386228</t>
+          <t>2026-03-09T04:13:11.032079</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386231</t>
+          <t>2026-03-09T04:13:11.032082</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1576</v>
+        <v>1608</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386234</t>
+          <t>2026-03-09T04:13:11.032085</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1566.00</t>
+          <t>1608.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1566</v>
+        <v>1608</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386237</t>
+          <t>2026-03-09T04:13:11.032087</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1568.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386239</t>
+          <t>2026-03-09T04:13:11.032090</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-08T04:07:51.386242</t>
+          <t>2026-03-09T04:13:11.032093</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031932</t>
+          <t>2026-03-10T04:05:20.818878</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031945</t>
+          <t>2026-03-10T04:05:20.818892</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031949</t>
+          <t>2026-03-10T04:05:20.818896</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031952</t>
+          <t>2026-03-10T04:05:20.818899</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031955</t>
+          <t>2026-03-10T04:05:20.818902</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031958</t>
+          <t>2026-03-10T04:05:20.818905</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031961</t>
+          <t>2026-03-10T04:05:20.818908</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031963</t>
+          <t>2026-03-10T04:05:20.818911</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031969</t>
+          <t>2026-03-10T04:05:20.818917</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031972</t>
+          <t>2026-03-10T04:05:20.818920</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031975</t>
+          <t>2026-03-10T04:05:20.818922</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031977</t>
+          <t>2026-03-10T04:05:20.818925</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031980</t>
+          <t>2026-03-10T04:05:20.818928</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031983</t>
+          <t>2026-03-10T04:05:20.818931</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031986</t>
+          <t>2026-03-10T04:05:20.818933</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031988</t>
+          <t>2026-03-10T04:05:20.818936</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031991</t>
+          <t>2026-03-10T04:05:20.818939</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.031997</t>
+          <t>2026-03-10T04:05:20.818942</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032008</t>
+          <t>2026-03-10T04:05:20.818947</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032011</t>
+          <t>2026-03-10T04:05:20.818950</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032013</t>
+          <t>2026-03-10T04:05:20.818952</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032016</t>
+          <t>2026-03-10T04:05:20.818956</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032019</t>
+          <t>2026-03-10T04:05:20.818959</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032022</t>
+          <t>2026-03-10T04:05:20.818961</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032025</t>
+          <t>2026-03-10T04:05:20.818964</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032028</t>
+          <t>2026-03-10T04:05:20.818967</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032030</t>
+          <t>2026-03-10T04:05:20.818970</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032033</t>
+          <t>2026-03-10T04:05:20.818973</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032036</t>
+          <t>2026-03-10T04:05:20.818976</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032039</t>
+          <t>2026-03-10T04:05:20.818979</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032042</t>
+          <t>2026-03-10T04:05:20.818982</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032044</t>
+          <t>2026-03-10T04:05:20.818984</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032047</t>
+          <t>2026-03-10T04:05:20.818987</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032050</t>
+          <t>2026-03-10T04:05:20.818990</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032052</t>
+          <t>2026-03-10T04:05:20.818993</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032055</t>
+          <t>2026-03-10T04:05:20.818995</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032058</t>
+          <t>2026-03-10T04:05:20.818998</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032060</t>
+          <t>2026-03-10T04:05:20.819001</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032063</t>
+          <t>2026-03-10T04:05:20.819003</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032066</t>
+          <t>2026-03-10T04:05:20.819006</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032068</t>
+          <t>2026-03-10T04:05:20.819009</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032071</t>
+          <t>2026-03-10T04:05:20.819012</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032074</t>
+          <t>2026-03-10T04:05:20.819015</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1585.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1555</v>
+        <v>1585</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032077</t>
+          <t>2026-03-10T04:05:20.819017</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032079</t>
+          <t>2026-03-10T04:05:20.819020</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032082</t>
+          <t>2026-03-10T04:05:20.819023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1629.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1608</v>
+        <v>1629</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032085</t>
+          <t>2026-03-10T04:05:20.819027</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1608.00</t>
+          <t>1620.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1608</v>
+        <v>1620</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032087</t>
+          <t>2026-03-10T04:05:20.819030</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1602.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1570</v>
+        <v>1602</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032090</t>
+          <t>2026-03-10T04:05:20.819033</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1574.00</t>
+          <t>1606.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1574</v>
+        <v>1606</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-09T04:13:11.032093</t>
+          <t>2026-03-10T04:05:20.819036</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818878</t>
+          <t>2026-03-11T04:06:21.483686</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818892</t>
+          <t>2026-03-11T04:06:21.483706</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818896</t>
+          <t>2026-03-11T04:06:21.483710</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818899</t>
+          <t>2026-03-11T04:06:21.483713</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818902</t>
+          <t>2026-03-11T04:06:21.483716</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818905</t>
+          <t>2026-03-11T04:06:21.483719</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818908</t>
+          <t>2026-03-11T04:06:21.483722</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818911</t>
+          <t>2026-03-11T04:06:21.483725</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818917</t>
+          <t>2026-03-11T04:06:21.483731</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818920</t>
+          <t>2026-03-11T04:06:21.483734</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818922</t>
+          <t>2026-03-11T04:06:21.483737</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818925</t>
+          <t>2026-03-11T04:06:21.483739</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818928</t>
+          <t>2026-03-11T04:06:21.483742</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818931</t>
+          <t>2026-03-11T04:06:21.483745</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818933</t>
+          <t>2026-03-11T04:06:21.483748</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818936</t>
+          <t>2026-03-11T04:06:21.483750</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818939</t>
+          <t>2026-03-11T04:06:21.483753</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818942</t>
+          <t>2026-03-11T04:06:21.483756</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818947</t>
+          <t>2026-03-11T04:06:21.483761</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818950</t>
+          <t>2026-03-11T04:06:21.483764</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818952</t>
+          <t>2026-03-11T04:06:21.483767</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818956</t>
+          <t>2026-03-11T04:06:21.483770</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818959</t>
+          <t>2026-03-11T04:06:21.483773</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818961</t>
+          <t>2026-03-11T04:06:21.483776</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818964</t>
+          <t>2026-03-11T04:06:21.483779</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818967</t>
+          <t>2026-03-11T04:06:21.483781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818970</t>
+          <t>2026-03-11T04:06:21.483784</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818973</t>
+          <t>2026-03-11T04:06:21.483787</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818976</t>
+          <t>2026-03-11T04:06:21.483790</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818979</t>
+          <t>2026-03-11T04:06:21.483793</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818982</t>
+          <t>2026-03-11T04:06:21.483796</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818984</t>
+          <t>2026-03-11T04:06:21.483799</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818987</t>
+          <t>2026-03-11T04:06:21.483801</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818990</t>
+          <t>2026-03-11T04:06:21.483804</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818993</t>
+          <t>2026-03-11T04:06:21.483807</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818995</t>
+          <t>2026-03-11T04:06:21.483810</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.818998</t>
+          <t>2026-03-11T04:06:21.483813</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819001</t>
+          <t>2026-03-11T04:06:21.483815</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819003</t>
+          <t>2026-03-11T04:06:21.483818</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819006</t>
+          <t>2026-03-11T04:06:21.483821</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819009</t>
+          <t>2026-03-11T04:06:21.483824</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819012</t>
+          <t>2026-03-11T04:06:21.483827</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819015</t>
+          <t>2026-03-11T04:06:21.483830</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819017</t>
+          <t>2026-03-11T04:06:21.483833</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819020</t>
+          <t>2026-03-11T04:06:21.483835</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819023</t>
+          <t>2026-03-11T04:06:21.483838</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1629.00</t>
+          <t>1652.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1629</v>
+        <v>1652</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819027</t>
+          <t>2026-03-11T04:06:21.483841</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1620.00</t>
+          <t>1642.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1620</v>
+        <v>1642</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819030</t>
+          <t>2026-03-11T04:06:21.483843</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1602.00</t>
+          <t>1622.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1602</v>
+        <v>1622</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819033</t>
+          <t>2026-03-11T04:06:21.483846</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1606.00</t>
+          <t>1624.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1606</v>
+        <v>1624</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-10T04:05:20.819036</t>
+          <t>2026-03-11T04:06:21.483849</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483686</t>
+          <t>2026-03-12T04:10:07.487021</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483706</t>
+          <t>2026-03-12T04:10:07.487033</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483710</t>
+          <t>2026-03-12T04:10:07.487036</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483713</t>
+          <t>2026-03-12T04:10:07.487040</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483716</t>
+          <t>2026-03-12T04:10:07.487043</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483719</t>
+          <t>2026-03-12T04:10:07.487046</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483722</t>
+          <t>2026-03-12T04:10:07.487049</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483725</t>
+          <t>2026-03-12T04:10:07.487052</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483731</t>
+          <t>2026-03-12T04:10:07.487077</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483734</t>
+          <t>2026-03-12T04:10:07.487080</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483737</t>
+          <t>2026-03-12T04:10:07.487083</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483739</t>
+          <t>2026-03-12T04:10:07.487086</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483742</t>
+          <t>2026-03-12T04:10:07.487089</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483745</t>
+          <t>2026-03-12T04:10:07.487091</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483748</t>
+          <t>2026-03-12T04:10:07.487094</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483750</t>
+          <t>2026-03-12T04:10:07.487097</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483753</t>
+          <t>2026-03-12T04:10:07.487100</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483756</t>
+          <t>2026-03-12T04:10:07.487103</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483761</t>
+          <t>2026-03-12T04:10:07.487108</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483764</t>
+          <t>2026-03-12T04:10:07.487110</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483767</t>
+          <t>2026-03-12T04:10:07.487113</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483770</t>
+          <t>2026-03-12T04:10:07.487116</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483773</t>
+          <t>2026-03-12T04:10:07.487119</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483776</t>
+          <t>2026-03-12T04:10:07.487122</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483779</t>
+          <t>2026-03-12T04:10:07.487125</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483781</t>
+          <t>2026-03-12T04:10:07.487127</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483784</t>
+          <t>2026-03-12T04:10:07.487130</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483787</t>
+          <t>2026-03-12T04:10:07.487133</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483790</t>
+          <t>2026-03-12T04:10:07.487137</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483793</t>
+          <t>2026-03-12T04:10:07.487140</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483796</t>
+          <t>2026-03-12T04:10:07.487143</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483799</t>
+          <t>2026-03-12T04:10:07.487146</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483801</t>
+          <t>2026-03-12T04:10:07.487148</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483804</t>
+          <t>2026-03-12T04:10:07.487151</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483807</t>
+          <t>2026-03-12T04:10:07.487154</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483810</t>
+          <t>2026-03-12T04:10:07.487156</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483813</t>
+          <t>2026-03-12T04:10:07.487159</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483815</t>
+          <t>2026-03-12T04:10:07.487162</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483818</t>
+          <t>2026-03-12T04:10:07.487165</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483821</t>
+          <t>2026-03-12T04:10:07.487167</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483824</t>
+          <t>2026-03-12T04:10:07.487170</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483827</t>
+          <t>2026-03-12T04:10:07.487173</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483830</t>
+          <t>2026-03-12T04:10:07.487175</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1585.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1585</v>
+        <v>1565</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483833</t>
+          <t>2026-03-12T04:10:07.487178</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483835</t>
+          <t>2026-03-12T04:10:07.487181</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483838</t>
+          <t>2026-03-12T04:10:07.487183</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1652.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1652</v>
+        <v>1599</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483841</t>
+          <t>2026-03-12T04:10:07.487186</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1642.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1642</v>
+        <v>1603</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483843</t>
+          <t>2026-03-12T04:10:07.487189</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1622.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1622</v>
+        <v>1650</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483846</t>
+          <t>2026-03-12T04:10:07.487192</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1624.00</t>
+          <t>1650.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1624</v>
+        <v>1650</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-11T04:06:21.483849</t>
+          <t>2026-03-12T04:10:07.487195</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487021</t>
+          <t>2026-03-13T04:08:49.151563</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487033</t>
+          <t>2026-03-13T04:08:49.151583</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487036</t>
+          <t>2026-03-13T04:08:49.151586</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487040</t>
+          <t>2026-03-13T04:08:49.151589</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487043</t>
+          <t>2026-03-13T04:08:49.151593</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487046</t>
+          <t>2026-03-13T04:08:49.151598</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487049</t>
+          <t>2026-03-13T04:08:49.151601</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487052</t>
+          <t>2026-03-13T04:08:49.151604</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487077</t>
+          <t>2026-03-13T04:08:49.151607</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487080</t>
+          <t>2026-03-13T04:08:49.151610</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487083</t>
+          <t>2026-03-13T04:08:49.151613</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487086</t>
+          <t>2026-03-13T04:08:49.151616</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487089</t>
+          <t>2026-03-13T04:08:49.151619</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487091</t>
+          <t>2026-03-13T04:08:49.151622</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487094</t>
+          <t>2026-03-13T04:08:49.151624</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487097</t>
+          <t>2026-03-13T04:08:49.151629</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487100</t>
+          <t>2026-03-13T04:08:49.151632</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487103</t>
+          <t>2026-03-13T04:08:49.151635</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487108</t>
+          <t>2026-03-13T04:08:49.151638</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487110</t>
+          <t>2026-03-13T04:08:49.151642</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487113</t>
+          <t>2026-03-13T04:08:49.151644</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487116</t>
+          <t>2026-03-13T04:08:49.151647</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487119</t>
+          <t>2026-03-13T04:08:49.151650</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487122</t>
+          <t>2026-03-13T04:08:49.151653</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487125</t>
+          <t>2026-03-13T04:08:49.151656</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487127</t>
+          <t>2026-03-13T04:08:49.151659</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487130</t>
+          <t>2026-03-13T04:08:49.151662</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487133</t>
+          <t>2026-03-13T04:08:49.151665</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487137</t>
+          <t>2026-03-13T04:08:49.151667</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487140</t>
+          <t>2026-03-13T04:08:49.151670</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487143</t>
+          <t>2026-03-13T04:08:49.151673</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487146</t>
+          <t>2026-03-13T04:08:49.151676</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487148</t>
+          <t>2026-03-13T04:08:49.151678</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487151</t>
+          <t>2026-03-13T04:08:49.151681</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487154</t>
+          <t>2026-03-13T04:08:49.151684</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487156</t>
+          <t>2026-03-13T04:08:49.151687</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487159</t>
+          <t>2026-03-13T04:08:49.151689</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487162</t>
+          <t>2026-03-13T04:08:49.151692</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487165</t>
+          <t>2026-03-13T04:08:49.151695</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487167</t>
+          <t>2026-03-13T04:08:49.151698</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487170</t>
+          <t>2026-03-13T04:08:49.151701</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487173</t>
+          <t>2026-03-13T04:08:49.151704</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487175</t>
+          <t>2026-03-13T04:08:49.151707</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487178</t>
+          <t>2026-03-13T04:08:49.151710</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487181</t>
+          <t>2026-03-13T04:08:49.151712</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487183</t>
+          <t>2026-03-13T04:08:49.151716</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487186</t>
+          <t>2026-03-13T04:08:49.151718</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487189</t>
+          <t>2026-03-13T04:08:49.151721</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1650</v>
+        <v>1596</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487192</t>
+          <t>2026-03-13T04:08:49.151724</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1650.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1650</v>
+        <v>1597</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-12T04:10:07.487195</t>
+          <t>2026-03-13T04:08:49.151727</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1572</v>
+        <v>1538</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151563</t>
+          <t>2026-03-14T04:07:12.077976</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1538</v>
+        <v>1570</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151583</t>
+          <t>2026-03-14T04:07:12.077990</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151586</t>
+          <t>2026-03-14T04:07:12.077994</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1578</v>
+        <v>1572</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151589</t>
+          <t>2026-03-14T04:07:12.077997</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151593</t>
+          <t>2026-03-14T04:07:12.078000</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1570</v>
+        <v>1578</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151598</t>
+          <t>2026-03-14T04:07:12.078003</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1579</v>
+        <v>1586</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151601</t>
+          <t>2026-03-14T04:07:12.078006</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151604</t>
+          <t>2026-03-14T04:07:12.078012</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1584</v>
+        <v>1548</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151607</t>
+          <t>2026-03-14T04:07:12.078016</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1586</v>
+        <v>1579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151610</t>
+          <t>2026-03-14T04:07:12.078019</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1548</v>
+        <v>1584</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151613</t>
+          <t>2026-03-14T04:07:12.078022</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151616</t>
+          <t>2026-03-14T04:07:12.078025</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151619</t>
+          <t>2026-03-14T04:07:12.078030</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151622</t>
+          <t>2026-03-14T04:07:12.078032</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1548</v>
+        <v>1600</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151624</t>
+          <t>2026-03-14T04:07:12.078035</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1600</v>
+        <v>1597</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151629</t>
+          <t>2026-03-14T04:07:12.078038</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1593</v>
+        <v>1548</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151632</t>
+          <t>2026-03-14T04:07:12.078041</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151635</t>
+          <t>2026-03-14T04:07:12.078046</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1548</v>
+        <v>1580</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151638</t>
+          <t>2026-03-14T04:07:12.078049</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1584</v>
+        <v>1588</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151642</t>
+          <t>2026-03-14T04:07:12.078052</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151644</t>
+          <t>2026-03-14T04:07:12.078055</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151647</t>
+          <t>2026-03-14T04:07:12.078058</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1588</v>
+        <v>1584</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151650</t>
+          <t>2026-03-14T04:07:12.078061</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1584</v>
+        <v>1548</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151653</t>
+          <t>2026-03-14T04:07:12.078063</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151656</t>
+          <t>2026-03-14T04:07:12.078066</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1548</v>
+        <v>1562</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151659</t>
+          <t>2026-03-14T04:07:12.078069</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1562</v>
+        <v>1571</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151662</t>
+          <t>2026-03-14T04:07:12.078072</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151665</t>
+          <t>2026-03-14T04:07:12.078076</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151667</t>
+          <t>2026-03-14T04:07:12.078079</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1573</v>
+        <v>1548</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151670</t>
+          <t>2026-03-14T04:07:12.078082</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151673</t>
+          <t>2026-03-14T04:07:12.078086</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1583</v>
+        <v>1555</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151676</t>
+          <t>2026-03-14T04:07:12.078088</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151678</t>
+          <t>2026-03-14T04:07:12.078091</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151681</t>
+          <t>2026-03-14T04:07:12.078094</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151684</t>
+          <t>2026-03-14T04:07:12.078097</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1555</v>
+        <v>1595</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151687</t>
+          <t>2026-03-14T04:07:12.078099</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151689</t>
+          <t>2026-03-14T04:07:12.078102</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1577</v>
+        <v>1555</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151692</t>
+          <t>2026-03-14T04:07:12.078105</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151695</t>
+          <t>2026-03-14T04:07:12.078108</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151698</t>
+          <t>2026-03-14T04:07:12.078111</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1555</v>
+        <v>1577</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151701</t>
+          <t>2026-03-14T04:07:12.078113</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151704</t>
+          <t>2026-03-14T04:07:12.078119</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151707</t>
+          <t>2026-03-14T04:07:12.078121</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1596.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1565</v>
+        <v>1596</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151710</t>
+          <t>2026-03-14T04:07:12.078124</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151712</t>
+          <t>2026-03-14T04:07:12.078127</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151716</t>
+          <t>2026-03-14T04:07:12.078130</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1599</v>
+        <v>1565</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151718</t>
+          <t>2026-03-14T04:07:12.078133</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151721</t>
+          <t>2026-03-14T04:07:12.078135</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1596</v>
+        <v>1565</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151724</t>
+          <t>2026-03-14T04:07:12.078138</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1603.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1597</v>
+        <v>1603</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-13T04:08:49.151727</t>
+          <t>2026-03-14T04:07:12.078141</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077976</t>
+          <t>2026-03-15T04:29:48.255151</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077990</t>
+          <t>2026-03-15T04:29:48.255166</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077994</t>
+          <t>2026-03-15T04:29:48.255170</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.077997</t>
+          <t>2026-03-15T04:29:48.255173</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078000</t>
+          <t>2026-03-15T04:29:48.255176</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078003</t>
+          <t>2026-03-15T04:29:48.255182</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078006</t>
+          <t>2026-03-15T04:29:48.255185</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078012</t>
+          <t>2026-03-15T04:29:48.255188</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078016</t>
+          <t>2026-03-15T04:29:48.255191</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078019</t>
+          <t>2026-03-15T04:29:48.255212</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078022</t>
+          <t>2026-03-15T04:29:48.255216</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078025</t>
+          <t>2026-03-15T04:29:48.255219</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078030</t>
+          <t>2026-03-15T04:29:48.255222</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078032</t>
+          <t>2026-03-15T04:29:48.255224</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078035</t>
+          <t>2026-03-15T04:29:48.255227</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078038</t>
+          <t>2026-03-15T04:29:48.255233</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078041</t>
+          <t>2026-03-15T04:29:48.255236</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078046</t>
+          <t>2026-03-15T04:29:48.255239</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078049</t>
+          <t>2026-03-15T04:29:48.255242</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078052</t>
+          <t>2026-03-15T04:29:48.255245</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078055</t>
+          <t>2026-03-15T04:29:48.255248</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078058</t>
+          <t>2026-03-15T04:29:48.255251</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078061</t>
+          <t>2026-03-15T04:29:48.255254</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078063</t>
+          <t>2026-03-15T04:29:48.255256</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078066</t>
+          <t>2026-03-15T04:29:48.255260</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078069</t>
+          <t>2026-03-15T04:29:48.255266</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078072</t>
+          <t>2026-03-15T04:29:48.255269</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078076</t>
+          <t>2026-03-15T04:29:48.255273</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078079</t>
+          <t>2026-03-15T04:29:48.255276</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078082</t>
+          <t>2026-03-15T04:29:48.255279</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078086</t>
+          <t>2026-03-15T04:29:48.255282</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078088</t>
+          <t>2026-03-15T04:29:48.255285</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078091</t>
+          <t>2026-03-15T04:29:48.255287</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078094</t>
+          <t>2026-03-15T04:29:48.255290</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078097</t>
+          <t>2026-03-15T04:29:48.255293</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078099</t>
+          <t>2026-03-15T04:29:48.255296</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1579</v>
+        <v>1590</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078102</t>
+          <t>2026-03-15T04:29:48.255298</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078105</t>
+          <t>2026-03-15T04:29:48.255301</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078108</t>
+          <t>2026-03-15T04:29:48.255304</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078111</t>
+          <t>2026-03-15T04:29:48.255307</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078113</t>
+          <t>2026-03-15T04:29:48.255309</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078119</t>
+          <t>2026-03-15T04:29:48.255312</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078121</t>
+          <t>2026-03-15T04:29:48.255315</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1596.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1596</v>
+        <v>1576</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078124</t>
+          <t>2026-03-15T04:29:48.255318</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1597</v>
+        <v>1577</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078127</t>
+          <t>2026-03-15T04:29:48.255321</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1599</v>
+        <v>1579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078130</t>
+          <t>2026-03-15T04:29:48.255324</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1565</v>
+        <v>1555</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078133</t>
+          <t>2026-03-15T04:29:48.255327</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1590</v>
+        <v>1580</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078135</t>
+          <t>2026-03-15T04:29:48.255330</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078138</t>
+          <t>2026-03-15T04:29:48.255333</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1603.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1603</v>
+        <v>1590</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-14T04:07:12.078141</t>
+          <t>2026-03-15T04:29:48.255336</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255151</t>
+          <t>2026-03-16T04:36:49.867488</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1565</v>
+        <v>1530</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255166</t>
+          <t>2026-03-16T04:36:49.867502</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255170</t>
+          <t>2026-03-16T04:36:49.867506</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1547</v>
+        <v>1555</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255173</t>
+          <t>2026-03-16T04:36:49.867509</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255176</t>
+          <t>2026-03-16T04:36:49.867512</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1555</v>
+        <v>1560</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255182</t>
+          <t>2026-03-16T04:36:49.867515</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1580</v>
+        <v>1547</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255185</t>
+          <t>2026-03-16T04:36:49.867517</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255188</t>
+          <t>2026-03-16T04:36:49.867520</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1538</v>
+        <v>1555</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255191</t>
+          <t>2026-03-16T04:36:49.867523</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1572</v>
+        <v>1557</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255212</t>
+          <t>2026-03-16T04:36:49.867526</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1578</v>
+        <v>1530</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255216</t>
+          <t>2026-03-16T04:36:49.867528</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255219</t>
+          <t>2026-03-16T04:36:49.867531</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255222</t>
+          <t>2026-03-16T04:36:49.867534</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255224</t>
+          <t>2026-03-16T04:36:49.867537</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1579</v>
+        <v>1538</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255227</t>
+          <t>2026-03-16T04:36:49.867540</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1584</v>
+        <v>1572</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255233</t>
+          <t>2026-03-16T04:36:49.867543</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1548</v>
+        <v>1570</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255236</t>
+          <t>2026-03-16T04:36:49.867546</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1584</v>
+        <v>1580</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255239</t>
+          <t>2026-03-16T04:36:49.867549</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1593</v>
+        <v>1548</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255242</t>
+          <t>2026-03-16T04:36:49.867552</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1600</v>
+        <v>1584</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255245</t>
+          <t>2026-03-16T04:36:49.867555</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255248</t>
+          <t>2026-03-16T04:36:49.867557</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1597</v>
+        <v>1580</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255251</t>
+          <t>2026-03-16T04:36:49.867560</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1597</v>
+        <v>1579</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255254</t>
+          <t>2026-03-16T04:36:49.867563</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1548</v>
+        <v>1584</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255256</t>
+          <t>2026-03-16T04:36:49.867569</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255260</t>
+          <t>2026-03-16T04:36:49.867572</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1588</v>
+        <v>1548</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255266</t>
+          <t>2026-03-16T04:36:49.867574</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1584</v>
+        <v>1600</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255269</t>
+          <t>2026-03-16T04:36:49.867577</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255273</t>
+          <t>2026-03-16T04:36:49.867580</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1586</v>
+        <v>1597</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255276</t>
+          <t>2026-03-16T04:36:49.867583</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1548</v>
+        <v>1599</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255279</t>
+          <t>2026-03-16T04:36:49.867585</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255282</t>
+          <t>2026-03-16T04:36:49.867588</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1548</v>
+        <v>1580</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255285</t>
+          <t>2026-03-16T04:36:49.867590</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1571</v>
+        <v>1586</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255287</t>
+          <t>2026-03-16T04:36:49.867594</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1573</v>
+        <v>1588</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255290</t>
+          <t>2026-03-16T04:36:49.867601</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255293</t>
+          <t>2026-03-16T04:36:49.867604</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1562</v>
+        <v>1548</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255296</t>
+          <t>2026-03-16T04:36:49.867607</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1590</v>
+        <v>1571</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255298</t>
+          <t>2026-03-16T04:36:49.867609</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1555</v>
+        <v>1571</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255301</t>
+          <t>2026-03-16T04:36:49.867612</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255304</t>
+          <t>2026-03-16T04:36:49.867615</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1583</v>
+        <v>1573</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255307</t>
+          <t>2026-03-16T04:36:49.867617</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1588</v>
+        <v>1548</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255309</t>
+          <t>2026-03-16T04:36:49.867620</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255312</t>
+          <t>2026-03-16T04:36:49.867623</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255315</t>
+          <t>2026-03-16T04:36:49.867626</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1576</v>
+        <v>1555</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255318</t>
+          <t>2026-03-16T04:36:49.867631</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1577</v>
+        <v>1595</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255321</t>
+          <t>2026-03-16T04:36:49.867634</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1579</v>
+        <v>1588</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255324</t>
+          <t>2026-03-16T04:36:49.867636</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1590.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1555</v>
+        <v>1590</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255327</t>
+          <t>2026-03-16T04:36:49.867639</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1583.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255330</t>
+          <t>2026-03-16T04:36:49.867642</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1576.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1565</v>
+        <v>1576</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255333</t>
+          <t>2026-03-16T04:36:49.867645</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1577.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1590</v>
+        <v>1577</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-15T04:29:48.255336</t>
+          <t>2026-03-16T04:36:49.867647</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867488</t>
+          <t>2026-03-17T04:14:33.716608</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867502</t>
+          <t>2026-03-17T04:14:33.716622</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867506</t>
+          <t>2026-03-17T04:14:33.716625</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867509</t>
+          <t>2026-03-17T04:14:33.716628</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867512</t>
+          <t>2026-03-17T04:14:33.716631</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867515</t>
+          <t>2026-03-17T04:14:33.716634</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867517</t>
+          <t>2026-03-17T04:14:33.716637</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867520</t>
+          <t>2026-03-17T04:14:33.716640</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867523</t>
+          <t>2026-03-17T04:14:33.716643</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867526</t>
+          <t>2026-03-17T04:14:33.716646</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867528</t>
+          <t>2026-03-17T04:14:33.716649</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867531</t>
+          <t>2026-03-17T04:14:33.716652</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867534</t>
+          <t>2026-03-17T04:14:33.716655</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867537</t>
+          <t>2026-03-17T04:14:33.716658</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867540</t>
+          <t>2026-03-17T04:14:33.716661</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867543</t>
+          <t>2026-03-17T04:14:33.716664</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867546</t>
+          <t>2026-03-17T04:14:33.716666</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867549</t>
+          <t>2026-03-17T04:14:33.716669</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867552</t>
+          <t>2026-03-17T04:14:33.716672</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867555</t>
+          <t>2026-03-17T04:14:33.716675</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867557</t>
+          <t>2026-03-17T04:14:33.716678</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867560</t>
+          <t>2026-03-17T04:14:33.716680</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867563</t>
+          <t>2026-03-17T04:14:33.716683</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867569</t>
+          <t>2026-03-17T04:14:33.716686</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867572</t>
+          <t>2026-03-17T04:14:33.716688</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867574</t>
+          <t>2026-03-17T04:14:33.716694</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867577</t>
+          <t>2026-03-17T04:14:33.716705</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867580</t>
+          <t>2026-03-17T04:14:33.716710</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867583</t>
+          <t>2026-03-17T04:14:33.716717</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867585</t>
+          <t>2026-03-17T04:14:33.716723</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867588</t>
+          <t>2026-03-17T04:14:33.716730</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867590</t>
+          <t>2026-03-17T04:14:33.716733</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867594</t>
+          <t>2026-03-17T04:14:33.716736</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867601</t>
+          <t>2026-03-17T04:14:33.716739</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867604</t>
+          <t>2026-03-17T04:14:33.716742</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867607</t>
+          <t>2026-03-17T04:14:33.716745</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867609</t>
+          <t>2026-03-17T04:14:33.716748</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867612</t>
+          <t>2026-03-17T04:14:33.716750</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867615</t>
+          <t>2026-03-17T04:14:33.716753</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867617</t>
+          <t>2026-03-17T04:14:33.716756</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867620</t>
+          <t>2026-03-17T04:14:33.716759</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867623</t>
+          <t>2026-03-17T04:14:33.716762</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867626</t>
+          <t>2026-03-17T04:14:33.716765</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1555</v>
+        <v>1548</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867631</t>
+          <t>2026-03-17T04:14:33.716768</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867634</t>
+          <t>2026-03-17T04:14:33.716771</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867636</t>
+          <t>2026-03-17T04:14:33.716774</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1590.00</t>
+          <t>1573.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1590</v>
+        <v>1573</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867639</t>
+          <t>2026-03-17T04:14:33.716776</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1583.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1583</v>
+        <v>1571</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867642</t>
+          <t>2026-03-17T04:14:33.716779</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1576.00</t>
+          <t>1595.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1576</v>
+        <v>1595</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867645</t>
+          <t>2026-03-17T04:14:33.716782</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1577.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1577</v>
+        <v>1588</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-16T04:36:49.867647</t>
+          <t>2026-03-17T04:14:33.716785</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716608</t>
+          <t>2026-03-18T04:22:03.547322</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716622</t>
+          <t>2026-03-18T04:22:03.547335</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716625</t>
+          <t>2026-03-18T04:22:03.547339</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716628</t>
+          <t>2026-03-18T04:22:03.547342</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716631</t>
+          <t>2026-03-18T04:22:03.547345</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716634</t>
+          <t>2026-03-18T04:22:03.547348</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716637</t>
+          <t>2026-03-18T04:22:03.547351</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716640</t>
+          <t>2026-03-18T04:22:03.547354</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716643</t>
+          <t>2026-03-18T04:22:03.547357</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716646</t>
+          <t>2026-03-18T04:22:03.547361</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716649</t>
+          <t>2026-03-18T04:22:03.547364</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716652</t>
+          <t>2026-03-18T04:22:03.547367</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716655</t>
+          <t>2026-03-18T04:22:03.547370</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716658</t>
+          <t>2026-03-18T04:22:03.547373</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716661</t>
+          <t>2026-03-18T04:22:03.547376</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716664</t>
+          <t>2026-03-18T04:22:03.547379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716666</t>
+          <t>2026-03-18T04:22:03.547382</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716669</t>
+          <t>2026-03-18T04:22:03.547385</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716672</t>
+          <t>2026-03-18T04:22:03.547388</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716675</t>
+          <t>2026-03-18T04:22:03.547391</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716678</t>
+          <t>2026-03-18T04:22:03.547394</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716680</t>
+          <t>2026-03-18T04:22:03.547397</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716683</t>
+          <t>2026-03-18T04:22:03.547399</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716686</t>
+          <t>2026-03-18T04:22:03.547402</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716688</t>
+          <t>2026-03-18T04:22:03.547405</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716694</t>
+          <t>2026-03-18T04:22:03.547408</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716705</t>
+          <t>2026-03-18T04:22:03.547410</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716710</t>
+          <t>2026-03-18T04:22:03.547413</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716717</t>
+          <t>2026-03-18T04:22:03.547416</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716723</t>
+          <t>2026-03-18T04:22:03.547419</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716730</t>
+          <t>2026-03-18T04:22:03.547421</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716733</t>
+          <t>2026-03-18T04:22:03.547424</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716736</t>
+          <t>2026-03-18T04:22:03.547427</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716739</t>
+          <t>2026-03-18T04:22:03.547430</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716742</t>
+          <t>2026-03-18T04:22:03.547432</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716745</t>
+          <t>2026-03-18T04:22:03.547435</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716748</t>
+          <t>2026-03-18T04:22:03.547438</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716750</t>
+          <t>2026-03-18T04:22:03.547441</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716753</t>
+          <t>2026-03-18T04:22:03.547444</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716756</t>
+          <t>2026-03-18T04:22:03.547446</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716759</t>
+          <t>2026-03-18T04:22:03.547449</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716762</t>
+          <t>2026-03-18T04:22:03.547452</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716765</t>
+          <t>2026-03-18T04:22:03.547455</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716768</t>
+          <t>2026-03-18T04:22:03.547458</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716771</t>
+          <t>2026-03-18T04:22:03.547461</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716774</t>
+          <t>2026-03-18T04:22:03.547464</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1573.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1573</v>
+        <v>1586</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716776</t>
+          <t>2026-03-18T04:22:03.547466</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1571</v>
+        <v>1580</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716779</t>
+          <t>2026-03-18T04:22:03.547469</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1595.00</t>
+          <t>1562.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1595</v>
+        <v>1562</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716782</t>
+          <t>2026-03-18T04:22:03.547472</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1571.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1588</v>
+        <v>1571</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-17T04:14:33.716785</t>
+          <t>2026-03-18T04:22:03.547475</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547322</t>
+          <t>2026-03-19T04:21:08.539092</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547335</t>
+          <t>2026-03-19T04:21:08.539112</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547339</t>
+          <t>2026-03-19T04:21:08.539118</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547342</t>
+          <t>2026-03-19T04:21:08.539126</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547345</t>
+          <t>2026-03-19T04:21:08.539132</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547348</t>
+          <t>2026-03-19T04:21:08.539138</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547351</t>
+          <t>2026-03-19T04:21:08.539144</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547354</t>
+          <t>2026-03-19T04:21:08.539148</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547357</t>
+          <t>2026-03-19T04:21:08.539151</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547361</t>
+          <t>2026-03-19T04:21:08.539154</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547364</t>
+          <t>2026-03-19T04:21:08.539157</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547367</t>
+          <t>2026-03-19T04:21:08.539160</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547370</t>
+          <t>2026-03-19T04:21:08.539163</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547373</t>
+          <t>2026-03-19T04:21:08.539166</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547376</t>
+          <t>2026-03-19T04:21:08.539169</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547379</t>
+          <t>2026-03-19T04:21:08.539172</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547382</t>
+          <t>2026-03-19T04:21:08.539175</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547385</t>
+          <t>2026-03-19T04:21:08.539178</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547388</t>
+          <t>2026-03-19T04:21:08.539181</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547391</t>
+          <t>2026-03-19T04:21:08.539184</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547394</t>
+          <t>2026-03-19T04:21:08.539187</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547397</t>
+          <t>2026-03-19T04:21:08.539189</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547399</t>
+          <t>2026-03-19T04:21:08.539193</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547402</t>
+          <t>2026-03-19T04:21:08.539195</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547405</t>
+          <t>2026-03-19T04:21:08.539198</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547408</t>
+          <t>2026-03-19T04:21:08.539201</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547410</t>
+          <t>2026-03-19T04:21:08.539204</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547413</t>
+          <t>2026-03-19T04:21:08.539207</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547416</t>
+          <t>2026-03-19T04:21:08.539210</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547419</t>
+          <t>2026-03-19T04:21:08.539213</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547421</t>
+          <t>2026-03-19T04:21:08.539215</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547424</t>
+          <t>2026-03-19T04:21:08.539218</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547427</t>
+          <t>2026-03-19T04:21:08.539221</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547430</t>
+          <t>2026-03-19T04:21:08.539224</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547432</t>
+          <t>2026-03-19T04:21:08.539227</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547435</t>
+          <t>2026-03-19T04:21:08.539230</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547438</t>
+          <t>2026-03-19T04:21:08.539233</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547441</t>
+          <t>2026-03-19T04:21:08.539236</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547444</t>
+          <t>2026-03-19T04:21:08.539239</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547446</t>
+          <t>2026-03-19T04:21:08.539241</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547449</t>
+          <t>2026-03-19T04:21:08.539244</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547452</t>
+          <t>2026-03-19T04:21:08.539247</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547455</t>
+          <t>2026-03-19T04:21:08.539250</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547458</t>
+          <t>2026-03-19T04:21:08.539253</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547461</t>
+          <t>2026-03-19T04:21:08.539256</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547464</t>
+          <t>2026-03-19T04:21:08.539259</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1599.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1586</v>
+        <v>1599</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547466</t>
+          <t>2026-03-19T04:21:08.539262</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547469</t>
+          <t>2026-03-19T04:21:08.539265</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1562.00</t>
+          <t>1588.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1562</v>
+        <v>1588</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547472</t>
+          <t>2026-03-19T04:21:08.539268</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1571.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1571</v>
+        <v>1584</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-18T04:22:03.547475</t>
+          <t>2026-03-19T04:21:08.539271</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1492</v>
+        <v>1443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539092</t>
+          <t>2026-03-20T04:10:45.580718</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1495</v>
+        <v>1478</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539112</t>
+          <t>2026-03-20T04:10:45.580732</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539118</t>
+          <t>2026-03-20T04:10:45.580736</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539126</t>
+          <t>2026-03-20T04:10:45.580740</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539132</t>
+          <t>2026-03-20T04:10:45.580743</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539138</t>
+          <t>2026-03-20T04:10:45.580746</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539144</t>
+          <t>2026-03-20T04:10:45.580749</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539148</t>
+          <t>2026-03-20T04:10:45.580752</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539151</t>
+          <t>2026-03-20T04:10:45.580755</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539154</t>
+          <t>2026-03-20T04:10:45.580758</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539157</t>
+          <t>2026-03-20T04:10:45.580761</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539160</t>
+          <t>2026-03-20T04:10:45.580764</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539163</t>
+          <t>2026-03-20T04:10:45.580767</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539166</t>
+          <t>2026-03-20T04:10:45.580770</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539169</t>
+          <t>2026-03-20T04:10:45.580773</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539172</t>
+          <t>2026-03-20T04:10:45.580775</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539175</t>
+          <t>2026-03-20T04:10:45.580778</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539178</t>
+          <t>2026-03-20T04:10:45.580781</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539181</t>
+          <t>2026-03-20T04:10:45.580784</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539184</t>
+          <t>2026-03-20T04:10:45.580787</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539187</t>
+          <t>2026-03-20T04:10:45.580789</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539189</t>
+          <t>2026-03-20T04:10:45.580792</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539193</t>
+          <t>2026-03-20T04:10:45.580795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539195</t>
+          <t>2026-03-20T04:10:45.580798</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539198</t>
+          <t>2026-03-20T04:10:45.580800</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539201</t>
+          <t>2026-03-20T04:10:45.580803</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539204</t>
+          <t>2026-03-20T04:10:45.580806</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539207</t>
+          <t>2026-03-20T04:10:45.580809</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539210</t>
+          <t>2026-03-20T04:10:45.580812</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539213</t>
+          <t>2026-03-20T04:10:45.580814</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539215</t>
+          <t>2026-03-20T04:10:45.580817</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539218</t>
+          <t>2026-03-20T04:10:45.580820</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539221</t>
+          <t>2026-03-20T04:10:45.580823</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539224</t>
+          <t>2026-03-20T04:10:45.580826</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539227</t>
+          <t>2026-03-20T04:10:45.580828</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539230</t>
+          <t>2026-03-20T04:10:45.580831</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539233</t>
+          <t>2026-03-20T04:10:45.580834</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539236</t>
+          <t>2026-03-20T04:10:45.580836</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539239</t>
+          <t>2026-03-20T04:10:45.580839</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539241</t>
+          <t>2026-03-20T04:10:45.580842</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539244</t>
+          <t>2026-03-20T04:10:45.580845</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539247</t>
+          <t>2026-03-20T04:10:45.580847</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539250</t>
+          <t>2026-03-20T04:10:45.580850</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539253</t>
+          <t>2026-03-20T04:10:45.580853</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1600</v>
+        <v>1579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539256</t>
+          <t>2026-03-20T04:10:45.580856</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1597</v>
+        <v>1584</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539259</t>
+          <t>2026-03-20T04:10:45.580859</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1599.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539262</t>
+          <t>2026-03-20T04:10:45.580861</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539265</t>
+          <t>2026-03-20T04:10:45.580864</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1588.00</t>
+          <t>1600.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1588</v>
+        <v>1600</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539268</t>
+          <t>2026-03-20T04:10:45.580867</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1597.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1584</v>
+        <v>1597</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-19T04:21:08.539271</t>
+          <t>2026-03-20T04:10:45.580870</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1443</v>
+        <v>1478</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580718</t>
+          <t>2026-03-21T04:02:00.565837</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1478</v>
+        <v>1445</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580732</t>
+          <t>2026-03-21T04:02:00.565851</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580736</t>
+          <t>2026-03-21T04:02:00.565854</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580740</t>
+          <t>2026-03-21T04:02:00.565858</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580743</t>
+          <t>2026-03-21T04:02:00.565860</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580746</t>
+          <t>2026-03-21T04:02:00.565863</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1492</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580749</t>
+          <t>2026-03-21T04:02:00.565867</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580752</t>
+          <t>2026-03-21T04:02:00.565870</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1501</v>
+        <v>1495</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580755</t>
+          <t>2026-03-21T04:02:00.565873</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>1492</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580758</t>
+          <t>2026-03-21T04:02:00.565876</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1495</v>
+        <v>1501</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580761</t>
+          <t>2026-03-21T04:02:00.565879</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580764</t>
+          <t>2026-03-21T04:02:00.565882</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580767</t>
+          <t>2026-03-21T04:02:00.565885</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580770</t>
+          <t>2026-03-21T04:02:00.565888</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1530</v>
+        <v>1547</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580773</t>
+          <t>2026-03-21T04:02:00.565891</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580775</t>
+          <t>2026-03-21T04:02:00.565894</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580778</t>
+          <t>2026-03-21T04:02:00.565899</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580781</t>
+          <t>2026-03-21T04:02:00.565902</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580784</t>
+          <t>2026-03-21T04:02:00.565905</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580787</t>
+          <t>2026-03-21T04:02:00.565908</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580789</t>
+          <t>2026-03-21T04:02:00.565911</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580792</t>
+          <t>2026-03-21T04:02:00.565913</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580795</t>
+          <t>2026-03-21T04:02:00.565916</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1549</v>
+        <v>1530</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580798</t>
+          <t>2026-03-21T04:02:00.565919</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580800</t>
+          <t>2026-03-21T04:02:00.565922</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1530</v>
+        <v>1550</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580803</t>
+          <t>2026-03-21T04:02:00.565924</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1550</v>
+        <v>1555</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580806</t>
+          <t>2026-03-21T04:02:00.565929</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580809</t>
+          <t>2026-03-21T04:02:00.565932</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580812</t>
+          <t>2026-03-21T04:02:00.565935</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1557</v>
+        <v>1530</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580814</t>
+          <t>2026-03-21T04:02:00.565938</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580817</t>
+          <t>2026-03-21T04:02:00.565941</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1565</v>
+        <v>1530</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580820</t>
+          <t>2026-03-21T04:02:00.565944</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1557</v>
+        <v>1555</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580823</t>
+          <t>2026-03-21T04:02:00.565946</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1547</v>
+        <v>1557</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580826</t>
+          <t>2026-03-21T04:02:00.565949</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1555</v>
+        <v>1565</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580828</t>
+          <t>2026-03-21T04:02:00.565952</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1530</v>
+        <v>1547</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580831</t>
+          <t>2026-03-21T04:02:00.565955</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1570</v>
+        <v>1580</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580834</t>
+          <t>2026-03-21T04:02:00.565960</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1578</v>
+        <v>1538</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580836</t>
+          <t>2026-03-21T04:02:00.565963</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580839</t>
+          <t>2026-03-21T04:02:00.565965</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580842</t>
+          <t>2026-03-21T04:02:00.565968</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1538</v>
+        <v>1578</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580845</t>
+          <t>2026-03-21T04:02:00.565971</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580847</t>
+          <t>2026-03-21T04:02:00.565974</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580850</t>
+          <t>2026-03-21T04:02:00.565977</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1579.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1548</v>
+        <v>1579</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580853</t>
+          <t>2026-03-21T04:02:00.565979</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1584.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1579</v>
+        <v>1584</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580856</t>
+          <t>2026-03-21T04:02:00.565982</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1586.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580859</t>
+          <t>2026-03-21T04:02:00.565985</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1586</v>
+        <v>1548</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580861</t>
+          <t>2026-03-21T04:02:00.565988</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580864</t>
+          <t>2026-03-21T04:02:00.565991</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1600.00</t>
+          <t>1548.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1600</v>
+        <v>1548</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580867</t>
+          <t>2026-03-21T04:02:00.565994</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1597.00</t>
+          <t>1593.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1597</v>
+        <v>1593</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-20T04:10:45.580870</t>
+          <t>2026-03-21T04:02:00.565997</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1478</v>
+        <v>1448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565837</t>
+          <t>2026-03-22T04:16:39.040919</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565851</t>
+          <t>2026-03-22T04:16:39.040931</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1447</v>
+        <v>1397</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565854</t>
+          <t>2026-03-22T04:16:39.040934</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1443</v>
+        <v>1389</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565858</t>
+          <t>2026-03-22T04:16:39.040938</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565860</t>
+          <t>2026-03-22T04:16:39.040940</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565863</t>
+          <t>2026-03-22T04:16:39.040943</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565867</t>
+          <t>2026-03-22T04:16:39.040946</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565870</t>
+          <t>2026-03-22T04:16:39.040949</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1495</v>
+        <v>1478</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565873</t>
+          <t>2026-03-22T04:16:39.040952</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1492</v>
+        <v>1443</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565876</t>
+          <t>2026-03-22T04:16:39.040955</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565879</t>
+          <t>2026-03-22T04:16:39.040958</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565882</t>
+          <t>2026-03-22T04:16:39.040961</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565885</t>
+          <t>2026-03-22T04:16:39.040963</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565888</t>
+          <t>2026-03-22T04:16:39.040966</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565891</t>
+          <t>2026-03-22T04:16:39.040969</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565894</t>
+          <t>2026-03-22T04:16:39.040972</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565899</t>
+          <t>2026-03-22T04:16:39.040975</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565902</t>
+          <t>2026-03-22T04:16:39.040978</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565905</t>
+          <t>2026-03-22T04:16:39.040981</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565908</t>
+          <t>2026-03-22T04:16:39.040983</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565911</t>
+          <t>2026-03-22T04:16:39.040986</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565913</t>
+          <t>2026-03-22T04:16:39.040989</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565916</t>
+          <t>2026-03-22T04:16:39.040992</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565919</t>
+          <t>2026-03-22T04:16:39.040995</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565922</t>
+          <t>2026-03-22T04:16:39.040997</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565924</t>
+          <t>2026-03-22T04:16:39.041000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565929</t>
+          <t>2026-03-22T04:16:39.041003</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565932</t>
+          <t>2026-03-22T04:16:39.041006</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565935</t>
+          <t>2026-03-22T04:16:39.041008</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565938</t>
+          <t>2026-03-22T04:16:39.041011</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565941</t>
+          <t>2026-03-22T04:16:39.041014</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565944</t>
+          <t>2026-03-22T04:16:39.041017</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565946</t>
+          <t>2026-03-22T04:16:39.041019</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565949</t>
+          <t>2026-03-22T04:16:39.041022</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565952</t>
+          <t>2026-03-22T04:16:39.041025</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565955</t>
+          <t>2026-03-22T04:16:39.041028</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1580</v>
+        <v>1557</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565960</t>
+          <t>2026-03-22T04:16:39.041031</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565963</t>
+          <t>2026-03-22T04:16:39.041033</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565965</t>
+          <t>2026-03-22T04:16:39.041036</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565968</t>
+          <t>2026-03-22T04:16:39.041039</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565971</t>
+          <t>2026-03-22T04:16:39.041042</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565974</t>
+          <t>2026-03-22T04:16:39.041045</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565977</t>
+          <t>2026-03-22T04:16:39.041050</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1579.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1579</v>
+        <v>1572</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565979</t>
+          <t>2026-03-22T04:16:39.041053</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1584.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1584</v>
+        <v>1578</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565982</t>
+          <t>2026-03-22T04:16:39.041056</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1586.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1586</v>
+        <v>1580</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565985</t>
+          <t>2026-03-22T04:16:39.041059</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1538.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1548</v>
+        <v>1538</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565988</t>
+          <t>2026-03-22T04:16:39.041062</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1570.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1580</v>
+        <v>1570</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565991</t>
+          <t>2026-03-22T04:16:39.041064</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565994</t>
+          <t>2026-03-22T04:16:39.041067</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1593.00</t>
+          <t>1580.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1593</v>
+        <v>1580</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-21T04:02:00.565997</t>
+          <t>2026-03-22T04:16:39.041070</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1448</v>
+        <v>1367</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040919</t>
+          <t>2026-03-23T04:26:08.383922</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1397</v>
+        <v>1418</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040931</t>
+          <t>2026-03-23T04:26:08.383935</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040934</t>
+          <t>2026-03-23T04:26:08.383939</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1389</v>
+        <v>1373</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040938</t>
+          <t>2026-03-23T04:26:08.383942</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040940</t>
+          <t>2026-03-23T04:26:08.383946</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1395</v>
+        <v>1374</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040943</t>
+          <t>2026-03-23T04:26:08.383949</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1447</v>
+        <v>1389</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040946</t>
+          <t>2026-03-23T04:26:08.383952</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040949</t>
+          <t>2026-03-23T04:26:08.383956</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1478</v>
+        <v>1395</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040952</t>
+          <t>2026-03-23T04:26:08.383959</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1443</v>
+        <v>1397</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040955</t>
+          <t>2026-03-23T04:26:08.383962</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040958</t>
+          <t>2026-03-23T04:26:08.383965</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040961</t>
+          <t>2026-03-23T04:26:08.383967</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040963</t>
+          <t>2026-03-23T04:26:08.383970</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1503</v>
+        <v>1445</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040966</t>
+          <t>2026-03-23T04:26:08.383973</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1492</v>
+        <v>1478</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040969</t>
+          <t>2026-03-23T04:26:08.383980</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1501</v>
+        <v>1443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040972</t>
+          <t>2026-03-23T04:26:08.383983</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1495</v>
+        <v>1445</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040975</t>
+          <t>2026-03-23T04:26:08.383986</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1501</v>
+        <v>1447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040978</t>
+          <t>2026-03-23T04:26:08.383989</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1550</v>
+        <v>1495</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040981</t>
+          <t>2026-03-23T04:26:08.383992</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1547</v>
+        <v>1501</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040983</t>
+          <t>2026-03-23T04:26:08.383995</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040986</t>
+          <t>2026-03-23T04:26:08.383998</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1549</v>
+        <v>1498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040989</t>
+          <t>2026-03-23T04:26:08.384000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1549</v>
+        <v>1492</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040992</t>
+          <t>2026-03-23T04:26:08.384003</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1530</v>
+        <v>1501</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040995</t>
+          <t>2026-03-23T04:26:08.384006</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.040997</t>
+          <t>2026-03-23T04:26:08.384009</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041000</t>
+          <t>2026-03-23T04:26:08.384026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041003</t>
+          <t>2026-03-23T04:26:08.384029</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041006</t>
+          <t>2026-03-23T04:26:08.384032</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041008</t>
+          <t>2026-03-23T04:26:08.384035</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1530</v>
+        <v>1551</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041011</t>
+          <t>2026-03-23T04:26:08.384038</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041014</t>
+          <t>2026-03-23T04:26:08.384041</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1530</v>
+        <v>1552</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041017</t>
+          <t>2026-03-23T04:26:08.384044</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1555</v>
+        <v>1551</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041019</t>
+          <t>2026-03-23T04:26:08.384046</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1557</v>
+        <v>1550</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041022</t>
+          <t>2026-03-23T04:26:08.384049</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1560</v>
+        <v>1549</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041025</t>
+          <t>2026-03-23T04:26:08.384052</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1550</v>
+        <v>1530</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041028</t>
+          <t>2026-03-23T04:26:08.384055</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041031</t>
+          <t>2026-03-23T04:26:08.384058</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1530</v>
+        <v>1555</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041033</t>
+          <t>2026-03-23T04:26:08.384061</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041036</t>
+          <t>2026-03-23T04:26:08.384064</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041039</t>
+          <t>2026-03-23T04:26:08.384066</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1555</v>
+        <v>1530</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041042</t>
+          <t>2026-03-23T04:26:08.384069</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041045</t>
+          <t>2026-03-23T04:26:08.384072</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041050</t>
+          <t>2026-03-23T04:26:08.384075</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1572</v>
+        <v>1530</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041053</t>
+          <t>2026-03-23T04:26:08.384077</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1578</v>
+        <v>1547</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041056</t>
+          <t>2026-03-23T04:26:08.384080</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1580</v>
+        <v>1555</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041059</t>
+          <t>2026-03-23T04:26:08.384083</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1538.00</t>
+          <t>1557.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1538</v>
+        <v>1557</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041062</t>
+          <t>2026-03-23T04:26:08.384086</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1570.00</t>
+          <t>1565.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041064</t>
+          <t>2026-03-23T04:26:08.384089</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1548.00</t>
+          <t>1572.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1548</v>
+        <v>1572</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041067</t>
+          <t>2026-03-23T04:26:08.384092</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1580.00</t>
+          <t>1578.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-22T04:16:39.041070</t>
+          <t>2026-03-23T04:26:08.384094</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1367</v>
+        <v>1350</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383922</t>
+          <t>2026-03-24T04:15:02.399750</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383935</t>
+          <t>2026-03-24T04:15:02.399762</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1375</v>
+        <v>1346</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383939</t>
+          <t>2026-03-24T04:15:02.399766</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383942</t>
+          <t>2026-03-24T04:15:02.399769</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383946</t>
+          <t>2026-03-24T04:15:02.399772</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1374</v>
+        <v>1345</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383949</t>
+          <t>2026-03-24T04:15:02.399775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1389</v>
+        <v>1367</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383952</t>
+          <t>2026-03-24T04:15:02.399778</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383956</t>
+          <t>2026-03-24T04:15:02.399782</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383959</t>
+          <t>2026-03-24T04:15:02.399785</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383962</t>
+          <t>2026-03-24T04:15:02.399788</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1448</v>
+        <v>1418</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383965</t>
+          <t>2026-03-24T04:15:02.399790</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1397</v>
+        <v>1374</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383967</t>
+          <t>2026-03-24T04:15:02.399793</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383970</t>
+          <t>2026-03-24T04:15:02.399796</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383973</t>
+          <t>2026-03-24T04:15:02.399799</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1478</v>
+        <v>1448</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383980</t>
+          <t>2026-03-24T04:15:02.399802</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1443</v>
+        <v>1389</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383983</t>
+          <t>2026-03-24T04:15:02.399804</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383986</t>
+          <t>2026-03-24T04:15:02.399807</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1447</v>
+        <v>1397</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383989</t>
+          <t>2026-03-24T04:15:02.399810</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1495</v>
+        <v>1478</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383992</t>
+          <t>2026-03-24T04:15:02.399813</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383995</t>
+          <t>2026-03-24T04:15:02.399816</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.383998</t>
+          <t>2026-03-24T04:15:02.399819</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384000</t>
+          <t>2026-03-24T04:15:02.399821</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1492</v>
+        <v>1443</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384003</t>
+          <t>2026-03-24T04:15:02.399824</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384006</t>
+          <t>2026-03-24T04:15:02.399827</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384009</t>
+          <t>2026-03-24T04:15:02.399829</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384026</t>
+          <t>2026-03-24T04:15:02.399832</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384029</t>
+          <t>2026-03-24T04:15:02.399835</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384032</t>
+          <t>2026-03-24T04:15:02.399837</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384035</t>
+          <t>2026-03-24T04:15:02.399840</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384038</t>
+          <t>2026-03-24T04:15:02.399843</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384041</t>
+          <t>2026-03-24T04:15:02.399846</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384044</t>
+          <t>2026-03-24T04:15:02.399848</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384046</t>
+          <t>2026-03-24T04:15:02.399851</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384049</t>
+          <t>2026-03-24T04:15:02.399855</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384052</t>
+          <t>2026-03-24T04:15:02.399858</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384055</t>
+          <t>2026-03-24T04:15:02.399861</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384058</t>
+          <t>2026-03-24T04:15:02.399864</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384061</t>
+          <t>2026-03-24T04:15:02.399867</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384064</t>
+          <t>2026-03-24T04:15:02.399885</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384066</t>
+          <t>2026-03-24T04:15:02.399888</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384069</t>
+          <t>2026-03-24T04:15:02.399891</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384072</t>
+          <t>2026-03-24T04:15:02.399894</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384075</t>
+          <t>2026-03-24T04:15:02.399897</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384077</t>
+          <t>2026-03-24T04:15:02.399899</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384080</t>
+          <t>2026-03-24T04:15:02.399902</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384083</t>
+          <t>2026-03-24T04:15:02.399905</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384086</t>
+          <t>2026-03-24T04:15:02.399908</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1565.00</t>
+          <t>1560.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384089</t>
+          <t>2026-03-24T04:15:02.399911</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1572.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1572</v>
+        <v>1547</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384092</t>
+          <t>2026-03-24T04:15:02.399914</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1578.00</t>
+          <t>1555.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1578</v>
+        <v>1555</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-23T04:26:08.384094</t>
+          <t>2026-03-24T04:15:02.399916</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1350</v>
+        <v>1418</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399750</t>
+          <t>2026-03-25T04:17:41.592338</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399762</t>
+          <t>2026-03-25T04:17:41.592356</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1346</v>
+        <v>1412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399766</t>
+          <t>2026-03-25T04:17:41.592359</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399769</t>
+          <t>2026-03-25T04:17:41.592363</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399772</t>
+          <t>2026-03-25T04:17:41.592366</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1345</v>
+        <v>1411</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399775</t>
+          <t>2026-03-25T04:17:41.592369</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1367</v>
+        <v>1350</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399778</t>
+          <t>2026-03-25T04:17:41.592372</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399782</t>
+          <t>2026-03-25T04:17:41.592375</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399785</t>
+          <t>2026-03-25T04:17:41.592378</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1375</v>
+        <v>1346</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399788</t>
+          <t>2026-03-25T04:17:41.592381</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399790</t>
+          <t>2026-03-25T04:17:41.592384</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1374</v>
+        <v>1345</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399793</t>
+          <t>2026-03-25T04:17:41.592386</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399796</t>
+          <t>2026-03-25T04:17:41.592389</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399799</t>
+          <t>2026-03-25T04:17:41.592392</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1448</v>
+        <v>1418</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399802</t>
+          <t>2026-03-25T04:17:41.592395</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1389</v>
+        <v>1367</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399804</t>
+          <t>2026-03-25T04:17:41.592397</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1397</v>
+        <v>1374</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399807</t>
+          <t>2026-03-25T04:17:41.592400</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399810</t>
+          <t>2026-03-25T04:17:41.592403</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1478</v>
+        <v>1448</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399813</t>
+          <t>2026-03-25T04:17:41.592406</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399816</t>
+          <t>2026-03-25T04:17:41.592409</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1447</v>
+        <v>1397</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399819</t>
+          <t>2026-03-25T04:17:41.592412</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399821</t>
+          <t>2026-03-25T04:17:41.592414</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1443</v>
+        <v>1389</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399824</t>
+          <t>2026-03-25T04:17:41.592417</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399827</t>
+          <t>2026-03-25T04:17:41.592420</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399829</t>
+          <t>2026-03-25T04:17:41.592422</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1495</v>
+        <v>1478</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399832</t>
+          <t>2026-03-25T04:17:41.592425</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1492</v>
+        <v>1443</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399835</t>
+          <t>2026-03-25T04:17:41.592428</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399837</t>
+          <t>2026-03-25T04:17:41.592431</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399840</t>
+          <t>2026-03-25T04:17:41.592434</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399843</t>
+          <t>2026-03-25T04:17:41.592436</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399846</t>
+          <t>2026-03-25T04:17:41.592439</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399848</t>
+          <t>2026-03-25T04:17:41.592442</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399851</t>
+          <t>2026-03-25T04:17:41.592444</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1547</v>
+        <v>1492</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399855</t>
+          <t>2026-03-25T04:17:41.592447</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399858</t>
+          <t>2026-03-25T04:17:41.592450</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399861</t>
+          <t>2026-03-25T04:17:41.592453</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1552</v>
+        <v>1550</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399864</t>
+          <t>2026-03-25T04:17:41.592456</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399867</t>
+          <t>2026-03-25T04:17:41.592458</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399885</t>
+          <t>2026-03-25T04:17:41.592461</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399888</t>
+          <t>2026-03-25T04:17:41.592464</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399891</t>
+          <t>2026-03-25T04:17:41.592467</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1550</v>
+        <v>1547</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399894</t>
+          <t>2026-03-25T04:17:41.592469</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399897</t>
+          <t>2026-03-25T04:17:41.592476</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399899</t>
+          <t>2026-03-25T04:17:41.592479</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399902</t>
+          <t>2026-03-25T04:17:41.592482</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399905</t>
+          <t>2026-03-25T04:17:41.592485</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1557.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1557</v>
+        <v>1551</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399908</t>
+          <t>2026-03-25T04:17:41.592488</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1560.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399911</t>
+          <t>2026-03-25T04:17:41.592490</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399914</t>
+          <t>2026-03-25T04:17:41.592493</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-24T04:15:02.399916</t>
+          <t>2026-03-25T04:17:41.592496</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592338</t>
+          <t>2026-03-26T04:30:35.455198</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1392</v>
+        <v>1412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592356</t>
+          <t>2026-03-26T04:30:35.455212</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592359</t>
+          <t>2026-03-26T04:30:35.455216</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592363</t>
+          <t>2026-03-26T04:30:35.455219</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592366</t>
+          <t>2026-03-26T04:30:35.455222</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1411</v>
+        <v>1392</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592369</t>
+          <t>2026-03-26T04:30:35.455225</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1350</v>
+        <v>1412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592372</t>
+          <t>2026-03-26T04:30:35.455228</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592375</t>
+          <t>2026-03-26T04:30:35.455231</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1344</v>
+        <v>1418</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592378</t>
+          <t>2026-03-26T04:30:35.455234</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1346</v>
+        <v>1411</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592381</t>
+          <t>2026-03-26T04:30:35.455237</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592384</t>
+          <t>2026-03-26T04:30:35.455240</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1345</v>
+        <v>1392</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592386</t>
+          <t>2026-03-26T04:30:35.455243</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1373</v>
+        <v>1346</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592389</t>
+          <t>2026-03-26T04:30:35.455246</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1373</v>
+        <v>1350</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592392</t>
+          <t>2026-03-26T04:30:35.455249</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1418</v>
+        <v>1344</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592395</t>
+          <t>2026-03-26T04:30:35.455252</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1367</v>
+        <v>1345</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592397</t>
+          <t>2026-03-26T04:30:35.455255</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1374</v>
+        <v>1344</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592400</t>
+          <t>2026-03-26T04:30:35.455257</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592403</t>
+          <t>2026-03-26T04:30:35.455260</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1448</v>
+        <v>1367</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592406</t>
+          <t>2026-03-26T04:30:35.455263</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592409</t>
+          <t>2026-03-26T04:30:35.455266</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592412</t>
+          <t>2026-03-26T04:30:35.455269</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1397</v>
+        <v>1373</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592414</t>
+          <t>2026-03-26T04:30:35.455271</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1389</v>
+        <v>1374</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592417</t>
+          <t>2026-03-26T04:30:35.455274</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592420</t>
+          <t>2026-03-26T04:30:35.455277</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1445</v>
+        <v>1448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592422</t>
+          <t>2026-03-26T04:30:35.455279</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1478</v>
+        <v>1395</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592425</t>
+          <t>2026-03-26T04:30:35.455282</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1443</v>
+        <v>1397</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592428</t>
+          <t>2026-03-26T04:30:35.455285</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592431</t>
+          <t>2026-03-26T04:30:35.455288</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1445</v>
+        <v>1389</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592434</t>
+          <t>2026-03-26T04:30:35.455291</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592436</t>
+          <t>2026-03-26T04:30:35.455293</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592439</t>
+          <t>2026-03-26T04:30:35.455296</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1498</v>
+        <v>1478</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592442</t>
+          <t>2026-03-26T04:30:35.455299</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592444</t>
+          <t>2026-03-26T04:30:35.455302</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1492</v>
+        <v>1445</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592447</t>
+          <t>2026-03-26T04:30:35.455305</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592450</t>
+          <t>2026-03-26T04:30:35.455308</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1495</v>
+        <v>1498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592453</t>
+          <t>2026-03-26T04:30:35.455310</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1550</v>
+        <v>1501</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592456</t>
+          <t>2026-03-26T04:30:35.455313</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1549</v>
+        <v>1495</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592458</t>
+          <t>2026-03-26T04:30:35.455316</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1549</v>
+        <v>1501</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592461</t>
+          <t>2026-03-26T04:30:35.455319</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1551</v>
+        <v>1503</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592464</t>
+          <t>2026-03-26T04:30:35.455322</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1530</v>
+        <v>1492</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592467</t>
+          <t>2026-03-26T04:30:35.455325</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592469</t>
+          <t>2026-03-26T04:30:35.455327</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592476</t>
+          <t>2026-03-26T04:30:35.455330</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1530</v>
+        <v>1549</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592479</t>
+          <t>2026-03-26T04:30:35.455333</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592482</t>
+          <t>2026-03-26T04:30:35.455336</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1551.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592485</t>
+          <t>2026-03-26T04:30:35.455339</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1551</v>
+        <v>1530</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592488</t>
+          <t>2026-03-26T04:30:35.455344</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592490</t>
+          <t>2026-03-26T04:30:35.455347</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1552.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592493</t>
+          <t>2026-03-26T04:30:35.455350</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1555.00</t>
+          <t>1549.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1555</v>
+        <v>1549</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-25T04:17:41.592496</t>
+          <t>2026-03-26T04:30:35.455353</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455198</t>
+          <t>2026-03-27T04:31:23.940297</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1412</v>
+        <v>1378</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455212</t>
+          <t>2026-03-27T04:31:23.940310</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1410</v>
+        <v>1366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455216</t>
+          <t>2026-03-27T04:31:23.940314</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1404</v>
+        <v>1364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455219</t>
+          <t>2026-03-27T04:31:23.940317</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455222</t>
+          <t>2026-03-27T04:31:23.940320</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1392</v>
+        <v>1365</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455225</t>
+          <t>2026-03-27T04:31:23.940346</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455228</t>
+          <t>2026-03-27T04:31:23.940353</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455231</t>
+          <t>2026-03-27T04:31:23.940360</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455234</t>
+          <t>2026-03-27T04:31:23.940366</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455237</t>
+          <t>2026-03-27T04:31:23.940372</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455240</t>
+          <t>2026-03-27T04:31:23.940378</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455243</t>
+          <t>2026-03-27T04:31:23.940384</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1346</v>
+        <v>1410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455246</t>
+          <t>2026-03-27T04:31:23.940390</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1350</v>
+        <v>1410</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455249</t>
+          <t>2026-03-27T04:31:23.940393</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1344</v>
+        <v>1392</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455252</t>
+          <t>2026-03-27T04:31:23.940396</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1345</v>
+        <v>1418</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455255</t>
+          <t>2026-03-27T04:31:23.940398</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1344</v>
+        <v>1411</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455257</t>
+          <t>2026-03-27T04:31:23.940401</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1373</v>
+        <v>1412</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455260</t>
+          <t>2026-03-27T04:31:23.940404</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1367</v>
+        <v>1392</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455263</t>
+          <t>2026-03-27T04:31:23.940407</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1418</v>
+        <v>1344</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455266</t>
+          <t>2026-03-27T04:31:23.940410</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1375</v>
+        <v>1346</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455269</t>
+          <t>2026-03-27T04:31:23.940412</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1373</v>
+        <v>1345</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455271</t>
+          <t>2026-03-27T04:31:23.940415</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1374</v>
+        <v>1350</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455274</t>
+          <t>2026-03-27T04:31:23.940418</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1397</v>
+        <v>1344</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455277</t>
+          <t>2026-03-27T04:31:23.940421</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1448</v>
+        <v>1373</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455279</t>
+          <t>2026-03-27T04:31:23.940424</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455282</t>
+          <t>2026-03-27T04:31:23.940426</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1397</v>
+        <v>1367</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455285</t>
+          <t>2026-03-27T04:31:23.940429</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1395</v>
+        <v>1374</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455288</t>
+          <t>2026-03-27T04:31:23.940432</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1389</v>
+        <v>1373</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455291</t>
+          <t>2026-03-27T04:31:23.940435</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1443</v>
+        <v>1375</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455293</t>
+          <t>2026-03-27T04:31:23.940437</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455296</t>
+          <t>2026-03-27T04:31:23.940440</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1478</v>
+        <v>1397</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455299</t>
+          <t>2026-03-27T04:31:23.940443</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1447</v>
+        <v>1397</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455302</t>
+          <t>2026-03-27T04:31:23.940445</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1445</v>
+        <v>1389</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455305</t>
+          <t>2026-03-27T04:31:23.940448</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455308</t>
+          <t>2026-03-27T04:31:23.940451</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1498</v>
+        <v>1448</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455310</t>
+          <t>2026-03-27T04:31:23.940454</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455313</t>
+          <t>2026-03-27T04:31:23.940456</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1495</v>
+        <v>1445</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455316</t>
+          <t>2026-03-27T04:31:23.940459</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455319</t>
+          <t>2026-03-27T04:31:23.940462</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455322</t>
+          <t>2026-03-27T04:31:23.940469</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1492</v>
+        <v>1478</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455325</t>
+          <t>2026-03-27T04:31:23.940471</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1550</v>
+        <v>1443</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455327</t>
+          <t>2026-03-27T04:31:23.940474</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1547</v>
+        <v>1501</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455330</t>
+          <t>2026-03-27T04:31:23.940477</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1549</v>
+        <v>1495</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455333</t>
+          <t>2026-03-27T04:31:23.940480</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1549</v>
+        <v>1492</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455336</t>
+          <t>2026-03-27T04:31:23.940483</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1551.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1551</v>
+        <v>1501</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455339</t>
+          <t>2026-03-27T04:31:23.940485</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1530</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455344</t>
+          <t>2026-03-27T04:31:23.940488</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1549</v>
+        <v>1498</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455347</t>
+          <t>2026-03-27T04:31:23.940491</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1552.00</t>
+          <t>1547.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455350</t>
+          <t>2026-03-27T04:31:23.940494</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-26T04:30:35.455353</t>
+          <t>2026-03-27T04:31:23.940497</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940297</t>
+          <t>2026-03-28T04:16:57.577640</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1378</v>
+        <v>1365</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940310</t>
+          <t>2026-03-28T04:16:57.577654</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940314</t>
+          <t>2026-03-28T04:16:57.577657</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940317</t>
+          <t>2026-03-28T04:16:57.577660</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940320</t>
+          <t>2026-03-28T04:16:57.577663</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940346</t>
+          <t>2026-03-28T04:16:57.577666</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1404</v>
+        <v>1412</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940353</t>
+          <t>2026-03-28T04:16:57.577669</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940360</t>
+          <t>2026-03-28T04:16:57.577673</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940366</t>
+          <t>2026-03-28T04:16:57.577676</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940372</t>
+          <t>2026-03-28T04:16:57.577679</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940378</t>
+          <t>2026-03-28T04:16:57.577682</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940384</t>
+          <t>2026-03-28T04:16:57.577685</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940390</t>
+          <t>2026-03-28T04:16:57.577687</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940393</t>
+          <t>2026-03-28T04:16:57.577690</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1392</v>
+        <v>1418</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940396</t>
+          <t>2026-03-28T04:16:57.577693</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940398</t>
+          <t>2026-03-28T04:16:57.577696</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1411</v>
+        <v>1392</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940401</t>
+          <t>2026-03-28T04:16:57.577699</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940404</t>
+          <t>2026-03-28T04:16:57.577702</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1392</v>
+        <v>1345</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940407</t>
+          <t>2026-03-28T04:16:57.577704</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1344</v>
+        <v>1350</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940410</t>
+          <t>2026-03-28T04:16:57.577707</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940412</t>
+          <t>2026-03-28T04:16:57.577710</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1345</v>
+        <v>1344</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940415</t>
+          <t>2026-03-28T04:16:57.577713</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1350</v>
+        <v>1344</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940418</t>
+          <t>2026-03-28T04:16:57.577716</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1344</v>
+        <v>1392</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940421</t>
+          <t>2026-03-28T04:16:57.577718</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940424</t>
+          <t>2026-03-28T04:16:57.577721</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1418</v>
+        <v>1367</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940426</t>
+          <t>2026-03-28T04:16:57.577724</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1367</v>
+        <v>1373</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940429</t>
+          <t>2026-03-28T04:16:57.577727</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940432</t>
+          <t>2026-03-28T04:16:57.577730</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940435</t>
+          <t>2026-03-28T04:16:57.577733</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1375</v>
+        <v>1418</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940437</t>
+          <t>2026-03-28T04:16:57.577736</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940440</t>
+          <t>2026-03-28T04:16:57.577738</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1397</v>
+        <v>1448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940443</t>
+          <t>2026-03-28T04:16:57.577741</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940445</t>
+          <t>2026-03-28T04:16:57.577744</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1389</v>
+        <v>1397</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940448</t>
+          <t>2026-03-28T04:16:57.577747</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940451</t>
+          <t>2026-03-28T04:16:57.577750</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1448</v>
+        <v>1389</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940454</t>
+          <t>2026-03-28T04:16:57.577755</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940456</t>
+          <t>2026-03-28T04:16:57.577758</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1445</v>
+        <v>1478</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940459</t>
+          <t>2026-03-28T04:16:57.577761</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940462</t>
+          <t>2026-03-28T04:16:57.577763</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940469</t>
+          <t>2026-03-28T04:16:57.577766</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1478</v>
+        <v>1445</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940471</t>
+          <t>2026-03-28T04:16:57.577769</t>
         </is>
       </c>
     </row>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940474</t>
+          <t>2026-03-28T04:16:57.577772</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940477</t>
+          <t>2026-03-28T04:16:57.577775</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1492.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940480</t>
+          <t>2026-03-28T04:16:57.577778</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1501.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1492</v>
+        <v>1501</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940483</t>
+          <t>2026-03-28T04:16:57.577781</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1503.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940485</t>
+          <t>2026-03-28T04:16:57.577784</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>1495</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940488</t>
+          <t>2026-03-28T04:16:57.577786</t>
         </is>
       </c>
     </row>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940491</t>
+          <t>2026-03-28T04:16:57.577789</t>
         </is>
       </c>
     </row>
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1547.00</t>
+          <t>1530.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1547</v>
+        <v>1530</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940494</t>
+          <t>2026-03-28T04:16:57.577792</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1549.00</t>
+          <t>1550.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-27T04:31:23.940497</t>
+          <t>2026-03-28T04:16:57.577795</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577640</t>
+          <t>2026-03-29T04:34:52.453367</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>1397</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577654</t>
+          <t>2026-03-29T04:34:52.453379</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1366</v>
+        <v>1395</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577657</t>
+          <t>2026-03-29T04:34:52.453383</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577660</t>
+          <t>2026-03-29T04:34:52.453389</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577663</t>
+          <t>2026-03-29T04:34:52.453399</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577666</t>
+          <t>2026-03-29T04:34:52.453404</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1412</v>
+        <v>1366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577669</t>
+          <t>2026-03-29T04:34:52.453411</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577673</t>
+          <t>2026-03-29T04:34:52.453417</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1392</v>
+        <v>1378</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577676</t>
+          <t>2026-03-29T04:34:52.453424</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1404</v>
+        <v>1364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577679</t>
+          <t>2026-03-29T04:34:52.453431</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577682</t>
+          <t>2026-03-29T04:34:52.453436</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1410</v>
+        <v>1365</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577685</t>
+          <t>2026-03-29T04:34:52.453439</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577687</t>
+          <t>2026-03-29T04:34:52.453442</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577690</t>
+          <t>2026-03-29T04:34:52.453445</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577693</t>
+          <t>2026-03-29T04:34:52.453447</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577696</t>
+          <t>2026-03-29T04:34:52.453450</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577699</t>
+          <t>2026-03-29T04:34:52.453453</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577702</t>
+          <t>2026-03-29T04:34:52.453456</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1345</v>
+        <v>1411</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577704</t>
+          <t>2026-03-29T04:34:52.453459</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1350</v>
+        <v>1418</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577707</t>
+          <t>2026-03-29T04:34:52.453462</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1346</v>
+        <v>1412</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577710</t>
+          <t>2026-03-29T04:34:52.453464</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577713</t>
+          <t>2026-03-29T04:34:52.453467</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577716</t>
+          <t>2026-03-29T04:34:52.453470</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577718</t>
+          <t>2026-03-29T04:34:52.453473</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577721</t>
+          <t>2026-03-29T04:34:52.453475</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1367</v>
+        <v>1350</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577724</t>
+          <t>2026-03-29T04:34:52.453478</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577727</t>
+          <t>2026-03-29T04:34:52.453481</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1374</v>
+        <v>1345</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577730</t>
+          <t>2026-03-29T04:34:52.453487</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1375</v>
+        <v>1346</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577733</t>
+          <t>2026-03-29T04:34:52.453490</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577736</t>
+          <t>2026-03-29T04:34:52.453493</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577738</t>
+          <t>2026-03-29T04:34:52.453496</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1448</v>
+        <v>1418</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577741</t>
+          <t>2026-03-29T04:34:52.453498</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577744</t>
+          <t>2026-03-29T04:34:52.453501</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577747</t>
+          <t>2026-03-29T04:34:52.453504</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1397</v>
+        <v>1374</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577750</t>
+          <t>2026-03-29T04:34:52.453507</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1389</v>
+        <v>1367</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577755</t>
+          <t>2026-03-29T04:34:52.453509</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1447</v>
+        <v>1397</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577758</t>
+          <t>2026-03-29T04:34:52.453512</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1478</v>
+        <v>1448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577761</t>
+          <t>2026-03-29T04:34:52.453515</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577763</t>
+          <t>2026-03-29T04:34:52.453518</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577766</t>
+          <t>2026-03-29T04:34:52.453521</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577769</t>
+          <t>2026-03-29T04:34:52.453524</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1443</v>
+        <v>1389</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577772</t>
+          <t>2026-03-29T04:34:52.453526</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577775</t>
+          <t>2026-03-29T04:34:52.453530</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1492.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1492</v>
+        <v>1443</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577778</t>
+          <t>2026-03-29T04:34:52.453533</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1501.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1501</v>
+        <v>1445</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577781</t>
+          <t>2026-03-29T04:34:52.453536</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1503.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1503</v>
+        <v>1447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577784</t>
+          <t>2026-03-29T04:34:52.453540</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1495</v>
+        <v>1478</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577786</t>
+          <t>2026-03-29T04:34:52.453542</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577789</t>
+          <t>2026-03-29T04:34:52.453545</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1530.00</t>
+          <t>1495.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1530</v>
+        <v>1495</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577792</t>
+          <t>2026-03-29T04:34:52.453548</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1550.00</t>
+          <t>1498.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1550</v>
+        <v>1498</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-28T04:16:57.577795</t>
+          <t>2026-03-29T04:34:52.453551</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453367</t>
+          <t>2026-03-30T04:42:13.639368</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1397</v>
+        <v>1378</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453379</t>
+          <t>2026-03-30T04:42:13.639384</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453383</t>
+          <t>2026-03-30T04:42:13.639388</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453389</t>
+          <t>2026-03-30T04:42:13.639392</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453399</t>
+          <t>2026-03-30T04:42:13.639396</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453404</t>
+          <t>2026-03-30T04:42:13.639399</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1366</v>
+        <v>1391</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453411</t>
+          <t>2026-03-30T04:42:13.639403</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453417</t>
+          <t>2026-03-30T04:42:13.639406</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1378</v>
+        <v>1393</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453424</t>
+          <t>2026-03-30T04:42:13.639410</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1364</v>
+        <v>1395</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453431</t>
+          <t>2026-03-30T04:42:13.639413</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453436</t>
+          <t>2026-03-30T04:42:13.639416</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1365</v>
+        <v>1397</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453439</t>
+          <t>2026-03-30T04:42:13.639419</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453442</t>
+          <t>2026-03-30T04:42:13.639423</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1412</v>
+        <v>1364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453445</t>
+          <t>2026-03-30T04:42:13.639426</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1404</v>
+        <v>1378</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453447</t>
+          <t>2026-03-30T04:42:13.639429</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453450</t>
+          <t>2026-03-30T04:42:13.639432</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1392</v>
+        <v>1365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453453</t>
+          <t>2026-03-30T04:42:13.639436</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1410</v>
+        <v>1366</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453456</t>
+          <t>2026-03-30T04:42:13.639439</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1411</v>
+        <v>1392</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453459</t>
+          <t>2026-03-30T04:42:13.639442</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453462</t>
+          <t>2026-03-30T04:42:13.639445</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453464</t>
+          <t>2026-03-30T04:42:13.639448</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453467</t>
+          <t>2026-03-30T04:42:13.639451</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453470</t>
+          <t>2026-03-30T04:42:13.639454</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453473</t>
+          <t>2026-03-30T04:42:13.639456</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453475</t>
+          <t>2026-03-30T04:42:13.639459</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1350</v>
+        <v>1392</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453478</t>
+          <t>2026-03-30T04:42:13.639462</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1344</v>
+        <v>1418</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453481</t>
+          <t>2026-03-30T04:42:13.639465</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1345</v>
+        <v>1411</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453487</t>
+          <t>2026-03-30T04:42:13.639468</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1346</v>
+        <v>1410</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453490</t>
+          <t>2026-03-30T04:42:13.639471</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1392</v>
+        <v>1412</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453493</t>
+          <t>2026-03-30T04:42:13.639474</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453496</t>
+          <t>2026-03-30T04:42:13.639477</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1418</v>
+        <v>1345</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453498</t>
+          <t>2026-03-30T04:42:13.639479</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1373</v>
+        <v>1346</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453501</t>
+          <t>2026-03-30T04:42:13.639482</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1375</v>
+        <v>1350</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453504</t>
+          <t>2026-03-30T04:42:13.639485</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1374</v>
+        <v>1344</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453507</t>
+          <t>2026-03-30T04:42:13.639488</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1367</v>
+        <v>1392</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453509</t>
+          <t>2026-03-30T04:42:13.639491</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1397</v>
+        <v>1374</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453512</t>
+          <t>2026-03-30T04:42:13.639494</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1448</v>
+        <v>1373</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453515</t>
+          <t>2026-03-30T04:42:13.639497</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453518</t>
+          <t>2026-03-30T04:42:13.639500</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453521</t>
+          <t>2026-03-30T04:42:13.639503</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1395</v>
+        <v>1418</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453524</t>
+          <t>2026-03-30T04:42:13.639506</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1389</v>
+        <v>1367</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453526</t>
+          <t>2026-03-30T04:42:13.639509</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453530</t>
+          <t>2026-03-30T04:42:13.639512</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453533</t>
+          <t>2026-03-30T04:42:13.639517</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1445</v>
+        <v>1389</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453536</t>
+          <t>2026-03-30T04:42:13.639520</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1447</v>
+        <v>1395</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453540</t>
+          <t>2026-03-30T04:42:13.639523</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1478</v>
+        <v>1397</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453542</t>
+          <t>2026-03-30T04:42:13.639526</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1445</v>
+        <v>1397</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453545</t>
+          <t>2026-03-30T04:42:13.639529</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1495.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1495</v>
+        <v>1443</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453548</t>
+          <t>2026-03-30T04:42:13.639532</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1498.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1498</v>
+        <v>1445</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-29T04:34:52.453551</t>
+          <t>2026-03-30T04:42:13.639535</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639368</t>
+          <t>2026-03-31T04:33:41.948173</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639384</t>
+          <t>2026-03-31T04:33:41.948187</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639388</t>
+          <t>2026-03-31T04:33:41.948190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639392</t>
+          <t>2026-03-31T04:33:41.948193</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639396</t>
+          <t>2026-03-31T04:33:41.948196</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639399</t>
+          <t>2026-03-31T04:33:41.948199</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639403</t>
+          <t>2026-03-31T04:33:41.948202</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639406</t>
+          <t>2026-03-31T04:33:41.948206</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639410</t>
+          <t>2026-03-31T04:33:41.948208</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639413</t>
+          <t>2026-03-31T04:33:41.948211</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639416</t>
+          <t>2026-03-31T04:33:41.948214</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639419</t>
+          <t>2026-03-31T04:33:41.948217</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639423</t>
+          <t>2026-03-31T04:33:41.948220</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639426</t>
+          <t>2026-03-31T04:33:41.948222</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639429</t>
+          <t>2026-03-31T04:33:41.948247</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639432</t>
+          <t>2026-03-31T04:33:41.948250</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1365</v>
+        <v>1397</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639436</t>
+          <t>2026-03-31T04:33:41.948253</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1366</v>
+        <v>1395</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639439</t>
+          <t>2026-03-31T04:33:41.948274</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1392</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639442</t>
+          <t>2026-03-31T04:33:41.948278</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639445</t>
+          <t>2026-03-31T04:33:41.948281</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1412</v>
+        <v>1366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639448</t>
+          <t>2026-03-31T04:33:41.948284</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1410</v>
+        <v>1365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639451</t>
+          <t>2026-03-31T04:33:41.948287</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1404</v>
+        <v>1364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639454</t>
+          <t>2026-03-31T04:33:41.948289</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639456</t>
+          <t>2026-03-31T04:33:41.948292</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639459</t>
+          <t>2026-03-31T04:33:41.948295</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639462</t>
+          <t>2026-03-31T04:33:41.948298</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639465</t>
+          <t>2026-03-31T04:33:41.948301</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639468</t>
+          <t>2026-03-31T04:33:41.948303</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639471</t>
+          <t>2026-03-31T04:33:41.948306</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639474</t>
+          <t>2026-03-31T04:33:41.948309</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639477</t>
+          <t>2026-03-31T04:33:41.948312</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1345</v>
+        <v>1411</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639479</t>
+          <t>2026-03-31T04:33:41.948314</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1346</v>
+        <v>1412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639482</t>
+          <t>2026-03-31T04:33:41.948317</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1350</v>
+        <v>1418</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639485</t>
+          <t>2026-03-31T04:33:41.948320</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639488</t>
+          <t>2026-03-31T04:33:41.948323</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639491</t>
+          <t>2026-03-31T04:33:41.948325</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1374</v>
+        <v>1345</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639494</t>
+          <t>2026-03-31T04:33:41.948328</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639497</t>
+          <t>2026-03-31T04:33:41.948332</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1373</v>
+        <v>1344</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639500</t>
+          <t>2026-03-31T04:33:41.948334</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1375</v>
+        <v>1346</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639503</t>
+          <t>2026-03-31T04:33:41.948337</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1418</v>
+        <v>1392</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639506</t>
+          <t>2026-03-31T04:33:41.948340</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1367</v>
+        <v>1350</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639509</t>
+          <t>2026-03-31T04:33:41.948343</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639512</t>
+          <t>2026-03-31T04:33:41.948346</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1448</v>
+        <v>1418</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639517</t>
+          <t>2026-03-31T04:33:41.948349</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1389</v>
+        <v>1367</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639520</t>
+          <t>2026-03-31T04:33:41.948351</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1373.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1395</v>
+        <v>1373</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639523</t>
+          <t>2026-03-31T04:33:41.948354</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1397</v>
+        <v>1375</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639526</t>
+          <t>2026-03-31T04:33:41.948360</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1374.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1397</v>
+        <v>1374</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639529</t>
+          <t>2026-03-31T04:33:41.948363</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1389.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1443</v>
+        <v>1389</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639532</t>
+          <t>2026-03-31T04:33:41.948366</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1445</v>
+        <v>1395</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-30T04:42:13.639535</t>
+          <t>2026-03-31T04:33:41.948368</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1400</v>
+        <v>1443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948173</t>
+          <t>2026-04-01T04:44:33.802122</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1378</v>
+        <v>1447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948187</t>
+          <t>2026-04-01T04:44:33.802138</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948190</t>
+          <t>2026-04-01T04:44:33.802142</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1393</v>
+        <v>1405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948193</t>
+          <t>2026-04-01T04:44:33.802145</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948196</t>
+          <t>2026-04-01T04:44:33.802149</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948199</t>
+          <t>2026-04-01T04:44:33.802152</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948202</t>
+          <t>2026-04-01T04:44:33.802155</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948206</t>
+          <t>2026-04-01T04:44:33.802158</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948208</t>
+          <t>2026-04-01T04:44:33.802162</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948211</t>
+          <t>2026-04-01T04:44:33.802165</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948214</t>
+          <t>2026-04-01T04:44:33.802168</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948217</t>
+          <t>2026-04-01T04:44:33.802171</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1393</v>
+        <v>1378</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948220</t>
+          <t>2026-04-01T04:44:33.802174</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948222</t>
+          <t>2026-04-01T04:44:33.802177</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1378</v>
+        <v>1395</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948247</t>
+          <t>2026-04-01T04:44:33.802180</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948250</t>
+          <t>2026-04-01T04:44:33.802183</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948253</t>
+          <t>2026-04-01T04:44:33.802186</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948274</t>
+          <t>2026-04-01T04:44:33.802189</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1395</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948278</t>
+          <t>2026-04-01T04:44:33.802192</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948281</t>
+          <t>2026-04-01T04:44:33.802195</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1366</v>
+        <v>1393</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948284</t>
+          <t>2026-04-01T04:44:33.802198</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1365</v>
+        <v>1393</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948287</t>
+          <t>2026-04-01T04:44:33.802204</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948289</t>
+          <t>2026-04-01T04:44:33.802208</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1364</v>
+        <v>1397</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948292</t>
+          <t>2026-04-01T04:44:33.802210</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948295</t>
+          <t>2026-04-01T04:44:33.802213</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948298</t>
+          <t>2026-04-01T04:44:33.802216</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1404</v>
+        <v>1365</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948301</t>
+          <t>2026-04-01T04:44:33.802219</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1410</v>
+        <v>1378</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948303</t>
+          <t>2026-04-01T04:44:33.802223</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1410</v>
+        <v>1366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948306</t>
+          <t>2026-04-01T04:44:33.802226</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1412</v>
+        <v>1364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948309</t>
+          <t>2026-04-01T04:44:33.802228</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948312</t>
+          <t>2026-04-01T04:44:33.802231</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948314</t>
+          <t>2026-04-01T04:44:33.802234</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948317</t>
+          <t>2026-04-01T04:44:33.802238</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948320</t>
+          <t>2026-04-01T04:44:33.802241</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948323</t>
+          <t>2026-04-01T04:44:33.802244</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948325</t>
+          <t>2026-04-01T04:44:33.802247</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1345</v>
+        <v>1418</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948328</t>
+          <t>2026-04-01T04:44:33.802250</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948332</t>
+          <t>2026-04-01T04:44:33.802253</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948334</t>
+          <t>2026-04-01T04:44:33.802256</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1346</v>
+        <v>1412</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948337</t>
+          <t>2026-04-01T04:44:33.802259</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948340</t>
+          <t>2026-04-01T04:44:33.802262</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1350</v>
+        <v>1411</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948343</t>
+          <t>2026-04-01T04:44:33.802265</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1373</v>
+        <v>1350</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948346</t>
+          <t>2026-04-01T04:44:33.802268</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1418</v>
+        <v>1344</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948349</t>
+          <t>2026-04-01T04:44:33.802271</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1344.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1367</v>
+        <v>1344</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948351</t>
+          <t>2026-04-01T04:44:33.802274</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1373.00</t>
+          <t>1345.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1373</v>
+        <v>1345</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948354</t>
+          <t>2026-04-01T04:44:33.802277</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1375</v>
+        <v>1346</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948360</t>
+          <t>2026-04-01T04:44:33.802280</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1374.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1374</v>
+        <v>1392</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948363</t>
+          <t>2026-04-01T04:44:33.802283</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1389.00</t>
+          <t>1375.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1389</v>
+        <v>1375</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948366</t>
+          <t>2026-04-01T04:44:33.802286</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1367.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1395</v>
+        <v>1367</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-03-31T04:33:41.948368</t>
+          <t>2026-04-01T04:44:33.802289</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802122</t>
+          <t>2026-04-02T04:27:08.208639</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802138</t>
+          <t>2026-04-02T04:27:08.208653</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802142</t>
+          <t>2026-04-02T04:27:08.208657</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1405</v>
+        <v>1443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802145</t>
+          <t>2026-04-02T04:27:08.208660</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802149</t>
+          <t>2026-04-02T04:27:08.208663</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1445</v>
+        <v>1428</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802152</t>
+          <t>2026-04-02T04:27:08.208666</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802155</t>
+          <t>2026-04-02T04:27:08.208669</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802158</t>
+          <t>2026-04-02T04:27:08.208672</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1393</v>
+        <v>1445</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802162</t>
+          <t>2026-04-02T04:27:08.208675</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1395</v>
+        <v>1447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802165</t>
+          <t>2026-04-02T04:27:08.208678</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1378</v>
+        <v>1443</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802168</t>
+          <t>2026-04-02T04:27:08.208681</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802171</t>
+          <t>2026-04-02T04:27:08.208683</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802174</t>
+          <t>2026-04-02T04:27:08.208686</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802177</t>
+          <t>2026-04-02T04:27:08.208689</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802180</t>
+          <t>2026-04-02T04:27:08.208692</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1393</v>
+        <v>1400</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802183</t>
+          <t>2026-04-02T04:27:08.208695</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802186</t>
+          <t>2026-04-02T04:27:08.208698</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1390</v>
+        <v>1395</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802189</t>
+          <t>2026-04-02T04:27:08.208701</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1395</v>
+        <v>1378</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802192</t>
+          <t>2026-04-02T04:27:08.208703</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802195</t>
+          <t>2026-04-02T04:27:08.208706</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1393</v>
+        <v>1390</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802198</t>
+          <t>2026-04-02T04:27:08.208709</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802204</t>
+          <t>2026-04-02T04:27:08.208712</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1378</v>
+        <v>1395</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802208</t>
+          <t>2026-04-02T04:27:08.208716</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802210</t>
+          <t>2026-04-02T04:27:08.208719</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1364</v>
+        <v>1395</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802213</t>
+          <t>2026-04-02T04:27:08.208722</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802216</t>
+          <t>2026-04-02T04:27:08.208725</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1365</v>
+        <v>1393</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802219</t>
+          <t>2026-04-02T04:27:08.208728</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1378</v>
+        <v>1397</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802223</t>
+          <t>2026-04-02T04:27:08.208731</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1366</v>
+        <v>1391</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802226</t>
+          <t>2026-04-02T04:27:08.208734</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802228</t>
+          <t>2026-04-02T04:27:08.208736</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802231</t>
+          <t>2026-04-02T04:27:08.208739</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1410</v>
+        <v>1365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802234</t>
+          <t>2026-04-02T04:27:08.208742</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1412</v>
+        <v>1378</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802238</t>
+          <t>2026-04-02T04:27:08.208744</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802241</t>
+          <t>2026-04-02T04:27:08.208750</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1404</v>
+        <v>1366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802244</t>
+          <t>2026-04-02T04:27:08.208753</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802247</t>
+          <t>2026-04-02T04:27:08.208756</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802250</t>
+          <t>2026-04-02T04:27:08.208759</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1410</v>
+        <v>1404</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802253</t>
+          <t>2026-04-02T04:27:08.208761</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802256</t>
+          <t>2026-04-02T04:27:08.208764</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802259</t>
+          <t>2026-04-02T04:27:08.208767</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802262</t>
+          <t>2026-04-02T04:27:08.208770</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802265</t>
+          <t>2026-04-02T04:27:08.208773</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1350</v>
+        <v>1392</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802268</t>
+          <t>2026-04-02T04:27:08.208775</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1344</v>
+        <v>1418</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802271</t>
+          <t>2026-04-02T04:27:08.208778</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1344.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1344</v>
+        <v>1410</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802274</t>
+          <t>2026-04-02T04:27:08.208781</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1345.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1345</v>
+        <v>1412</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802277</t>
+          <t>2026-04-02T04:27:08.208784</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1411.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1346</v>
+        <v>1411</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802280</t>
+          <t>2026-04-02T04:27:08.208786</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802283</t>
+          <t>2026-04-02T04:27:08.208789</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1375.00</t>
+          <t>1346.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1375</v>
+        <v>1346</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802286</t>
+          <t>2026-04-02T04:27:08.208792</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1367.00</t>
+          <t>1350.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1367</v>
+        <v>1350</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-01T04:44:33.802289</t>
+          <t>2026-04-02T04:27:08.208795</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208639</t>
+          <t>2026-04-03T04:27:19.860912</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208653</t>
+          <t>2026-04-03T04:27:19.860927</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208657</t>
+          <t>2026-04-03T04:27:19.860931</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208660</t>
+          <t>2026-04-03T04:27:19.860934</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208663</t>
+          <t>2026-04-03T04:27:19.860937</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1428</v>
+        <v>1443</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208666</t>
+          <t>2026-04-03T04:27:19.860940</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1405</v>
+        <v>1443</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208669</t>
+          <t>2026-04-03T04:27:19.860943</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208672</t>
+          <t>2026-04-03T04:27:19.860946</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1445</v>
+        <v>1428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208675</t>
+          <t>2026-04-03T04:27:19.860949</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1447</v>
+        <v>1445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208678</t>
+          <t>2026-04-03T04:27:19.860953</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208681</t>
+          <t>2026-04-03T04:27:19.860965</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208683</t>
+          <t>2026-04-03T04:27:19.860971</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1378</v>
+        <v>1405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208686</t>
+          <t>2026-04-03T04:27:19.860977</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1393</v>
+        <v>1445</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208689</t>
+          <t>2026-04-03T04:27:19.860983</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1393</v>
+        <v>1447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208692</t>
+          <t>2026-04-03T04:27:19.860989</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1400</v>
+        <v>1445</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208695</t>
+          <t>2026-04-03T04:27:19.860994</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208698</t>
+          <t>2026-04-03T04:27:19.861000</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208701</t>
+          <t>2026-04-03T04:27:19.861006</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1378</v>
+        <v>1393</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208703</t>
+          <t>2026-04-03T04:27:19.861012</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208706</t>
+          <t>2026-04-03T04:27:19.861017</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1390</v>
+        <v>1378</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208709</t>
+          <t>2026-04-03T04:27:19.861022</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208712</t>
+          <t>2026-04-03T04:27:19.861028</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208716</t>
+          <t>2026-04-03T04:27:19.861033</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1395</v>
+        <v>1378</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208719</t>
+          <t>2026-04-03T04:27:19.861039</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208722</t>
+          <t>2026-04-03T04:27:19.861044</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208725</t>
+          <t>2026-04-03T04:27:19.861050</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208728</t>
+          <t>2026-04-03T04:27:19.861056</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208731</t>
+          <t>2026-04-03T04:27:19.861061</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208734</t>
+          <t>2026-04-03T04:27:19.861067</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1393</v>
+        <v>1397</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208736</t>
+          <t>2026-04-03T04:27:19.861077</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208739</t>
+          <t>2026-04-03T04:27:19.861083</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1365</v>
+        <v>1391</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208742</t>
+          <t>2026-04-03T04:27:19.861088</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1393</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208744</t>
+          <t>2026-04-03T04:27:19.861094</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208750</t>
+          <t>2026-04-03T04:27:19.861100</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208753</t>
+          <t>2026-04-03T04:27:19.861106</t>
         </is>
       </c>
     </row>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208756</t>
+          <t>2026-04-03T04:27:19.861111</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208759</t>
+          <t>2026-04-03T04:27:19.861117</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1404</v>
+        <v>1378</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208761</t>
+          <t>2026-04-03T04:27:19.861122</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1392</v>
+        <v>1366</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208764</t>
+          <t>2026-04-03T04:27:19.861128</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1410</v>
+        <v>1364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208767</t>
+          <t>2026-04-03T04:27:19.861133</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208770</t>
+          <t>2026-04-03T04:27:19.861139</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208773</t>
+          <t>2026-04-03T04:27:19.861145</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1392</v>
+        <v>1410</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208775</t>
+          <t>2026-04-03T04:27:19.861150</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1418</v>
+        <v>1412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208778</t>
+          <t>2026-04-03T04:27:19.861156</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208781</t>
+          <t>2026-04-03T04:27:19.861162</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1412</v>
+        <v>1410</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208784</t>
+          <t>2026-04-03T04:27:19.861168</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1411.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208786</t>
+          <t>2026-04-03T04:27:19.861173</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1392.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1410</v>
+        <v>1392</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208789</t>
+          <t>2026-04-03T04:27:19.861179</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1346.00</t>
+          <t>1410.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1346</v>
+        <v>1410</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208792</t>
+          <t>2026-04-03T04:27:19.861184</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1350.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1350</v>
+        <v>1418</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-02T04:27:08.208795</t>
+          <t>2026-04-03T04:27:19.861190</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860912</t>
+          <t>2026-04-04T04:13:38.094512</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860927</t>
+          <t>2026-04-04T04:13:38.094532</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860931</t>
+          <t>2026-04-04T04:13:38.094536</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860934</t>
+          <t>2026-04-04T04:13:38.094540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1445</v>
+        <v>1435</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860937</t>
+          <t>2026-04-04T04:13:38.094544</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1443</v>
+        <v>1418</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860940</t>
+          <t>2026-04-04T04:13:38.094548</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1443</v>
+        <v>1418</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860943</t>
+          <t>2026-04-04T04:13:38.094552</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860946</t>
+          <t>2026-04-04T04:13:38.094556</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1428</v>
+        <v>1446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860949</t>
+          <t>2026-04-04T04:13:38.094560</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1445</v>
+        <v>1442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860953</t>
+          <t>2026-04-04T04:13:38.094564</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860965</t>
+          <t>2026-04-04T04:13:38.094567</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860971</t>
+          <t>2026-04-04T04:13:38.094571</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860977</t>
+          <t>2026-04-04T04:13:38.094574</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860983</t>
+          <t>2026-04-04T04:13:38.094578</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860989</t>
+          <t>2026-04-04T04:13:38.094582</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.860994</t>
+          <t>2026-04-04T04:13:38.094585</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861000</t>
+          <t>2026-04-04T04:13:38.094589</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1400</v>
+        <v>1445</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861006</t>
+          <t>2026-04-04T04:13:38.094593</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1393</v>
+        <v>1405</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861012</t>
+          <t>2026-04-04T04:13:38.094596</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861017</t>
+          <t>2026-04-04T04:13:38.094600</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1378</v>
+        <v>1447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861022</t>
+          <t>2026-04-04T04:13:38.094603</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1395</v>
+        <v>1443</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861028</t>
+          <t>2026-04-04T04:13:38.094607</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861033</t>
+          <t>2026-04-04T04:13:38.094611</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1378</v>
+        <v>1445</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861039</t>
+          <t>2026-04-04T04:13:38.094614</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861044</t>
+          <t>2026-04-04T04:13:38.094618</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1390</v>
+        <v>1378</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861050</t>
+          <t>2026-04-04T04:13:38.094621</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861056</t>
+          <t>2026-04-04T04:13:38.094625</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861061</t>
+          <t>2026-04-04T04:13:38.094629</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861067</t>
+          <t>2026-04-04T04:13:38.094632</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861077</t>
+          <t>2026-04-04T04:13:38.094636</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1378</v>
+        <v>1390</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861083</t>
+          <t>2026-04-04T04:13:38.094640</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1391</v>
+        <v>1395</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861088</t>
+          <t>2026-04-04T04:13:38.094643</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1393</v>
+        <v>1378</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861094</t>
+          <t>2026-04-04T04:13:38.094651</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861100</t>
+          <t>2026-04-04T04:13:38.094655</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1365</v>
+        <v>1395</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861106</t>
+          <t>2026-04-04T04:13:38.094658</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861111</t>
+          <t>2026-04-04T04:13:38.094662</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861117</t>
+          <t>2026-04-04T04:13:38.094666</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1378</v>
+        <v>1391</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861122</t>
+          <t>2026-04-04T04:13:38.094669</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1366</v>
+        <v>1378</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861128</t>
+          <t>2026-04-04T04:13:38.094673</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861133</t>
+          <t>2026-04-04T04:13:38.094677</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1410</v>
+        <v>1397</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861139</t>
+          <t>2026-04-04T04:13:38.094680</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1404</v>
+        <v>1395</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861145</t>
+          <t>2026-04-04T04:13:38.094684</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1410</v>
+        <v>1378</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861150</t>
+          <t>2026-04-04T04:13:38.094688</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1412</v>
+        <v>1364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861156</t>
+          <t>2026-04-04T04:13:38.094691</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861162</t>
+          <t>2026-04-04T04:13:38.094695</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1410</v>
+        <v>1366</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861168</t>
+          <t>2026-04-04T04:13:38.094699</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1412</v>
+        <v>1365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861173</t>
+          <t>2026-04-04T04:13:38.094702</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1392.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1392</v>
+        <v>1364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861179</t>
+          <t>2026-04-04T04:13:38.094706</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1410.00</t>
+          <t>1412.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861184</t>
+          <t>2026-04-04T04:13:38.094709</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1404.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1418</v>
+        <v>1404</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-03T04:27:19.861190</t>
+          <t>2026-04-04T04:13:38.094713</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094512</t>
+          <t>2026-04-05T04:34:35.073926</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1443</v>
+        <v>1441</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094532</t>
+          <t>2026-04-05T04:34:35.073940</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094536</t>
+          <t>2026-04-05T04:34:35.073944</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1443</v>
+        <v>1418</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094540</t>
+          <t>2026-04-05T04:34:35.073947</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094544</t>
+          <t>2026-04-05T04:34:35.073950</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1418</v>
+        <v>1435</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094548</t>
+          <t>2026-04-05T04:34:35.073953</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1418</v>
+        <v>1442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094552</t>
+          <t>2026-04-05T04:34:35.073956</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094556</t>
+          <t>2026-04-05T04:34:35.073959</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094560</t>
+          <t>2026-04-05T04:34:35.073962</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1442</v>
+        <v>1446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094564</t>
+          <t>2026-04-05T04:34:35.073965</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1443</v>
+        <v>1418</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094567</t>
+          <t>2026-04-05T04:34:35.073968</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094571</t>
+          <t>2026-04-05T04:34:35.073971</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094574</t>
+          <t>2026-04-05T04:34:35.073974</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094578</t>
+          <t>2026-04-05T04:34:35.073977</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094582</t>
+          <t>2026-04-05T04:34:35.073979</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094585</t>
+          <t>2026-04-05T04:34:35.073982</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094589</t>
+          <t>2026-04-05T04:34:35.073985</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1445</v>
+        <v>1449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094593</t>
+          <t>2026-04-05T04:34:35.073988</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1405</v>
+        <v>1445</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094596</t>
+          <t>2026-04-05T04:34:35.073991</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1443</v>
+        <v>1447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094600</t>
+          <t>2026-04-05T04:34:35.073994</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094603</t>
+          <t>2026-04-05T04:34:35.073998</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094607</t>
+          <t>2026-04-05T04:34:35.074001</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1445</v>
+        <v>1405</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094611</t>
+          <t>2026-04-05T04:34:35.074004</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094614</t>
+          <t>2026-04-05T04:34:35.074007</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094618</t>
+          <t>2026-04-05T04:34:35.074010</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1378</v>
+        <v>1400</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094621</t>
+          <t>2026-04-05T04:34:35.074013</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094625</t>
+          <t>2026-04-05T04:34:35.074016</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1395</v>
+        <v>1378</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094629</t>
+          <t>2026-04-05T04:34:35.074021</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094632</t>
+          <t>2026-04-05T04:34:35.074024</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094636</t>
+          <t>2026-04-05T04:34:35.074027</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1390</v>
+        <v>1378</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094640</t>
+          <t>2026-04-05T04:34:35.074029</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1395</v>
+        <v>1393</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094643</t>
+          <t>2026-04-05T04:34:35.074032</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1378</v>
+        <v>1395</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094651</t>
+          <t>2026-04-05T04:34:35.074035</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094655</t>
+          <t>2026-04-05T04:34:35.074038</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094658</t>
+          <t>2026-04-05T04:34:35.074041</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094662</t>
+          <t>2026-04-05T04:34:35.074043</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1393</v>
+        <v>1391</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094666</t>
+          <t>2026-04-05T04:34:35.074046</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094669</t>
+          <t>2026-04-05T04:34:35.074049</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1378</v>
+        <v>1393</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094673</t>
+          <t>2026-04-05T04:34:35.074052</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094677</t>
+          <t>2026-04-05T04:34:35.074054</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1397</v>
+        <v>1378</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094680</t>
+          <t>2026-04-05T04:34:35.074057</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094684</t>
+          <t>2026-04-05T04:34:35.074060</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1378</v>
+        <v>1364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094688</t>
+          <t>2026-04-05T04:34:35.074063</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094691</t>
+          <t>2026-04-05T04:34:35.074066</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094695</t>
+          <t>2026-04-05T04:34:35.074069</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1365.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1366</v>
+        <v>1365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094699</t>
+          <t>2026-04-05T04:34:35.074072</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094702</t>
+          <t>2026-04-05T04:34:35.074075</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1378.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1364</v>
+        <v>1378</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094706</t>
+          <t>2026-04-05T04:34:35.074078</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094709</t>
+          <t>2026-04-05T04:34:35.074080</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-04T04:13:38.094713</t>
+          <t>2026-04-05T04:34:35.074083</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073926</t>
+          <t>2026-04-06T04:41:45.996298</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073940</t>
+          <t>2026-04-06T04:41:45.996312</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073944</t>
+          <t>2026-04-06T04:41:45.996316</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073947</t>
+          <t>2026-04-06T04:41:45.996319</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073950</t>
+          <t>2026-04-06T04:41:45.996322</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073953</t>
+          <t>2026-04-06T04:41:45.996325</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073956</t>
+          <t>2026-04-06T04:41:45.996328</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073959</t>
+          <t>2026-04-06T04:41:45.996331</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073962</t>
+          <t>2026-04-06T04:41:45.996334</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1446</v>
+        <v>1435</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073965</t>
+          <t>2026-04-06T04:41:45.996337</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073968</t>
+          <t>2026-04-06T04:41:45.996340</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073971</t>
+          <t>2026-04-06T04:41:45.996343</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073974</t>
+          <t>2026-04-06T04:41:45.996346</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073977</t>
+          <t>2026-04-06T04:41:45.996349</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073979</t>
+          <t>2026-04-06T04:41:45.996351</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073982</t>
+          <t>2026-04-06T04:41:45.996354</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073985</t>
+          <t>2026-04-06T04:41:45.996357</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073988</t>
+          <t>2026-04-06T04:41:45.996360</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073991</t>
+          <t>2026-04-06T04:41:45.996363</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073994</t>
+          <t>2026-04-06T04:41:45.996365</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.073998</t>
+          <t>2026-04-06T04:41:45.996368</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074001</t>
+          <t>2026-04-06T04:41:45.996371</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074004</t>
+          <t>2026-04-06T04:41:45.996374</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074007</t>
+          <t>2026-04-06T04:41:45.996376</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074010</t>
+          <t>2026-04-06T04:41:45.996379</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1400</v>
+        <v>1447</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074013</t>
+          <t>2026-04-06T04:41:45.996382</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074016</t>
+          <t>2026-04-06T04:41:45.996385</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1378</v>
+        <v>1405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074021</t>
+          <t>2026-04-06T04:41:45.996388</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074024</t>
+          <t>2026-04-06T04:41:45.996390</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074027</t>
+          <t>2026-04-06T04:41:45.996396</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074029</t>
+          <t>2026-04-06T04:41:45.996399</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074032</t>
+          <t>2026-04-06T04:41:45.996401</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074035</t>
+          <t>2026-04-06T04:41:45.996404</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074038</t>
+          <t>2026-04-06T04:41:45.996407</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074041</t>
+          <t>2026-04-06T04:41:45.996410</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074043</t>
+          <t>2026-04-06T04:41:45.996413</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074046</t>
+          <t>2026-04-06T04:41:45.996416</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074049</t>
+          <t>2026-04-06T04:41:45.996418</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074052</t>
+          <t>2026-04-06T04:41:45.996421</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074054</t>
+          <t>2026-04-06T04:41:45.996424</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074057</t>
+          <t>2026-04-06T04:41:45.996427</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074060</t>
+          <t>2026-04-06T04:41:45.996430</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074063</t>
+          <t>2026-04-06T04:41:45.996432</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074066</t>
+          <t>2026-04-06T04:41:45.996435</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1393.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1364</v>
+        <v>1393</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074069</t>
+          <t>2026-04-06T04:41:45.996438</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1365.00</t>
+          <t>1397.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1365</v>
+        <v>1397</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074072</t>
+          <t>2026-04-06T04:41:45.996441</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1366</v>
+        <v>1395</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074075</t>
+          <t>2026-04-06T04:41:45.996443</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074078</t>
+          <t>2026-04-06T04:41:45.996446</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1412.00</t>
+          <t>1366.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1412</v>
+        <v>1366</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074080</t>
+          <t>2026-04-06T04:41:45.996449</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1404.00</t>
+          <t>1364.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1404</v>
+        <v>1364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-05T04:34:35.074083</t>
+          <t>2026-04-06T04:41:45.996452</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996298</t>
+          <t>2026-04-07T04:30:29.162896</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996312</t>
+          <t>2026-04-07T04:30:29.162905</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996316</t>
+          <t>2026-04-07T04:30:29.162909</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996319</t>
+          <t>2026-04-07T04:30:29.162912</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996322</t>
+          <t>2026-04-07T04:30:29.162915</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996325</t>
+          <t>2026-04-07T04:30:29.162918</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996328</t>
+          <t>2026-04-07T04:30:29.162921</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996331</t>
+          <t>2026-04-07T04:30:29.162924</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996334</t>
+          <t>2026-04-07T04:30:29.162927</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996337</t>
+          <t>2026-04-07T04:30:29.162930</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996340</t>
+          <t>2026-04-07T04:30:29.162933</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996343</t>
+          <t>2026-04-07T04:30:29.162935</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996346</t>
+          <t>2026-04-07T04:30:29.162938</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1446</v>
+        <v>1435</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996349</t>
+          <t>2026-04-07T04:30:29.162941</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996351</t>
+          <t>2026-04-07T04:30:29.162943</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996354</t>
+          <t>2026-04-07T04:30:29.162946</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996357</t>
+          <t>2026-04-07T04:30:29.162949</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996360</t>
+          <t>2026-04-07T04:30:29.162952</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996363</t>
+          <t>2026-04-07T04:30:29.162954</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996365</t>
+          <t>2026-04-07T04:30:29.162957</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996368</t>
+          <t>2026-04-07T04:30:29.162960</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996371</t>
+          <t>2026-04-07T04:30:29.162962</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996374</t>
+          <t>2026-04-07T04:30:29.162965</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996376</t>
+          <t>2026-04-07T04:30:29.162968</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996379</t>
+          <t>2026-04-07T04:30:29.162970</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996382</t>
+          <t>2026-04-07T04:30:29.162973</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996385</t>
+          <t>2026-04-07T04:30:29.162976</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996388</t>
+          <t>2026-04-07T04:30:29.162979</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996390</t>
+          <t>2026-04-07T04:30:29.162981</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996396</t>
+          <t>2026-04-07T04:30:29.162984</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1378</v>
+        <v>1405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996399</t>
+          <t>2026-04-07T04:30:29.162987</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996401</t>
+          <t>2026-04-07T04:30:29.162989</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996404</t>
+          <t>2026-04-07T04:30:29.162992</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996407</t>
+          <t>2026-04-07T04:30:29.162998</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1400</v>
+        <v>1447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996410</t>
+          <t>2026-04-07T04:30:29.163001</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996413</t>
+          <t>2026-04-07T04:30:29.163003</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996416</t>
+          <t>2026-04-07T04:30:29.163006</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996418</t>
+          <t>2026-04-07T04:30:29.163009</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996421</t>
+          <t>2026-04-07T04:30:29.163012</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996424</t>
+          <t>2026-04-07T04:30:29.163037</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996427</t>
+          <t>2026-04-07T04:30:29.163041</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996430</t>
+          <t>2026-04-07T04:30:29.163044</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996432</t>
+          <t>2026-04-07T04:30:29.163047</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996435</t>
+          <t>2026-04-07T04:30:29.163050</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996438</t>
+          <t>2026-04-07T04:30:29.163052</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1397.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1397</v>
+        <v>1395</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996441</t>
+          <t>2026-04-07T04:30:29.163055</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996443</t>
+          <t>2026-04-07T04:30:29.163058</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996446</t>
+          <t>2026-04-07T04:30:29.163061</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1366.00</t>
+          <t>1395.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1366</v>
+        <v>1395</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996449</t>
+          <t>2026-04-07T04:30:29.163063</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1364.00</t>
+          <t>1391.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1364</v>
+        <v>1391</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-06T04:41:45.996452</t>
+          <t>2026-04-07T04:30:29.163066</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162896</t>
+          <t>2026-04-08T04:34:16.652269</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1434</v>
+        <v>1471</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162905</t>
+          <t>2026-04-08T04:34:16.652283</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162909</t>
+          <t>2026-04-08T04:34:16.652287</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1399</v>
+        <v>1448</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162912</t>
+          <t>2026-04-08T04:34:16.652290</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162915</t>
+          <t>2026-04-08T04:34:16.652293</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1436</v>
+        <v>1470</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162918</t>
+          <t>2026-04-08T04:34:16.652296</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162921</t>
+          <t>2026-04-08T04:34:16.652299</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162924</t>
+          <t>2026-04-08T04:34:16.652302</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162927</t>
+          <t>2026-04-08T04:34:16.652305</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162930</t>
+          <t>2026-04-08T04:34:16.652308</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162933</t>
+          <t>2026-04-08T04:34:16.652311</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162935</t>
+          <t>2026-04-08T04:34:16.652314</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162938</t>
+          <t>2026-04-08T04:34:16.652316</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162941</t>
+          <t>2026-04-08T04:34:16.652319</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162943</t>
+          <t>2026-04-08T04:34:16.652322</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162946</t>
+          <t>2026-04-08T04:34:16.652325</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162949</t>
+          <t>2026-04-08T04:34:16.652327</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162952</t>
+          <t>2026-04-08T04:34:16.652331</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162954</t>
+          <t>2026-04-08T04:34:16.652334</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162957</t>
+          <t>2026-04-08T04:34:16.652336</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162960</t>
+          <t>2026-04-08T04:34:16.652339</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162962</t>
+          <t>2026-04-08T04:34:16.652342</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162965</t>
+          <t>2026-04-08T04:34:16.652345</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1446</v>
+        <v>1435</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162968</t>
+          <t>2026-04-08T04:34:16.652347</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162970</t>
+          <t>2026-04-08T04:34:16.652350</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162973</t>
+          <t>2026-04-08T04:34:16.652353</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162976</t>
+          <t>2026-04-08T04:34:16.652359</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162979</t>
+          <t>2026-04-08T04:34:16.652362</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162981</t>
+          <t>2026-04-08T04:34:16.652365</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162984</t>
+          <t>2026-04-08T04:34:16.652368</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162987</t>
+          <t>2026-04-08T04:34:16.652370</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162989</t>
+          <t>2026-04-08T04:34:16.652373</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162992</t>
+          <t>2026-04-08T04:34:16.652376</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.162998</t>
+          <t>2026-04-08T04:34:16.652378</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163001</t>
+          <t>2026-04-08T04:34:16.652381</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163003</t>
+          <t>2026-04-08T04:34:16.652384</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1400</v>
+        <v>1447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163006</t>
+          <t>2026-04-08T04:34:16.652389</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163009</t>
+          <t>2026-04-08T04:34:16.652392</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163012</t>
+          <t>2026-04-08T04:34:16.652397</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163037</t>
+          <t>2026-04-08T04:34:16.652399</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1378</v>
+        <v>1405</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163041</t>
+          <t>2026-04-08T04:34:16.652402</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163044</t>
+          <t>2026-04-08T04:34:16.652405</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163047</t>
+          <t>2026-04-08T04:34:16.652408</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163050</t>
+          <t>2026-04-08T04:34:16.652410</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163052</t>
+          <t>2026-04-08T04:34:16.652413</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163055</t>
+          <t>2026-04-08T04:34:16.652416</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163058</t>
+          <t>2026-04-08T04:34:16.652419</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163061</t>
+          <t>2026-04-08T04:34:16.652422</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163063</t>
+          <t>2026-04-08T04:34:16.652425</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1391.00</t>
+          <t>1390.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-07T04:30:29.163066</t>
+          <t>2026-04-08T04:34:16.652428</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652269</t>
+          <t>2026-04-09T04:31:11.789278</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652283</t>
+          <t>2026-04-09T04:31:11.789296</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652287</t>
+          <t>2026-04-09T04:31:11.789300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652290</t>
+          <t>2026-04-09T04:31:11.789303</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1474</v>
+        <v>1449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652293</t>
+          <t>2026-04-09T04:31:11.789306</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1470</v>
+        <v>1422</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652296</t>
+          <t>2026-04-09T04:31:11.789310</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1434</v>
+        <v>1448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652299</t>
+          <t>2026-04-09T04:31:11.789313</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652302</t>
+          <t>2026-04-09T04:31:11.789316</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1431</v>
+        <v>1470</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652305</t>
+          <t>2026-04-09T04:31:11.789319</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1436</v>
+        <v>1471</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652308</t>
+          <t>2026-04-09T04:31:11.789322</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1399</v>
+        <v>1474</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652311</t>
+          <t>2026-04-09T04:31:11.789325</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652314</t>
+          <t>2026-04-09T04:31:11.789328</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652316</t>
+          <t>2026-04-09T04:31:11.789331</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652319</t>
+          <t>2026-04-09T04:31:11.789334</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652322</t>
+          <t>2026-04-09T04:31:11.789337</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652325</t>
+          <t>2026-04-09T04:31:11.789340</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652327</t>
+          <t>2026-04-09T04:31:11.789343</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1430</v>
+        <v>1436</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652331</t>
+          <t>2026-04-09T04:31:11.789346</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1445</v>
+        <v>1399</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652334</t>
+          <t>2026-04-09T04:31:11.789349</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1441</v>
+        <v>1431</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652336</t>
+          <t>2026-04-09T04:31:11.789352</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1443</v>
+        <v>1430</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652339</t>
+          <t>2026-04-09T04:31:11.789354</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652342</t>
+          <t>2026-04-09T04:31:11.789357</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1418</v>
+        <v>1433</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652345</t>
+          <t>2026-04-09T04:31:11.789360</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652347</t>
+          <t>2026-04-09T04:31:11.789363</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652350</t>
+          <t>2026-04-09T04:31:11.789366</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1442</v>
+        <v>1418</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652353</t>
+          <t>2026-04-09T04:31:11.789369</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1446</v>
+        <v>1443</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652359</t>
+          <t>2026-04-09T04:31:11.789375</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1418</v>
+        <v>1435</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652362</t>
+          <t>2026-04-09T04:31:11.789378</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652365</t>
+          <t>2026-04-09T04:31:11.789381</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652368</t>
+          <t>2026-04-09T04:31:11.789384</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1428</v>
+        <v>1442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652370</t>
+          <t>2026-04-09T04:31:11.789387</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652373</t>
+          <t>2026-04-09T04:31:11.789390</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1445</v>
+        <v>1418</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652376</t>
+          <t>2026-04-09T04:31:11.789393</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652378</t>
+          <t>2026-04-09T04:31:11.789395</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652381</t>
+          <t>2026-04-09T04:31:11.789399</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652384</t>
+          <t>2026-04-09T04:31:11.789402</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652389</t>
+          <t>2026-04-09T04:31:11.789405</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1443</v>
+        <v>1449</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652392</t>
+          <t>2026-04-09T04:31:11.789408</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1443</v>
+        <v>1428</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652397</t>
+          <t>2026-04-09T04:31:11.789411</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>1443</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652399</t>
+          <t>2026-04-09T04:31:11.789414</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1405</v>
+        <v>1445</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652402</t>
+          <t>2026-04-09T04:31:11.789417</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652405</t>
+          <t>2026-04-09T04:31:11.789420</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1400</v>
+        <v>1405</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652408</t>
+          <t>2026-04-09T04:31:11.789423</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1393</v>
+        <v>1447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652410</t>
+          <t>2026-04-09T04:31:11.789426</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1393.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1393</v>
+        <v>1443</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652413</t>
+          <t>2026-04-09T04:31:11.789428</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652416</t>
+          <t>2026-04-09T04:31:11.789431</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652419</t>
+          <t>2026-04-09T04:31:11.789434</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1378.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1378</v>
+        <v>1443</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652422</t>
+          <t>2026-04-09T04:31:11.789437</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652425</t>
+          <t>2026-04-09T04:31:11.789440</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1390.00</t>
+          <t>1400.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1390</v>
+        <v>1400</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-08T04:34:16.652428</t>
+          <t>2026-04-09T04:31:11.789443</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789278</t>
+          <t>2026-04-10T04:43:49.372543</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789296</t>
+          <t>2026-04-10T04:43:49.372565</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789300</t>
+          <t>2026-04-10T04:43:49.372569</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789303</t>
+          <t>2026-04-10T04:43:49.372572</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789306</t>
+          <t>2026-04-10T04:43:49.372576</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789310</t>
+          <t>2026-04-10T04:43:49.372579</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789313</t>
+          <t>2026-04-10T04:43:49.372582</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789316</t>
+          <t>2026-04-10T04:43:49.372585</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789319</t>
+          <t>2026-04-10T04:43:49.372588</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789322</t>
+          <t>2026-04-10T04:43:49.372591</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789325</t>
+          <t>2026-04-10T04:43:49.372594</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789328</t>
+          <t>2026-04-10T04:43:49.372597</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1399</v>
+        <v>1448</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789331</t>
+          <t>2026-04-10T04:43:49.372600</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789334</t>
+          <t>2026-04-10T04:43:49.372603</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789337</t>
+          <t>2026-04-10T04:43:49.372606</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1434</v>
+        <v>1471</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789340</t>
+          <t>2026-04-10T04:43:49.372608</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789343</t>
+          <t>2026-04-10T04:43:49.372611</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1436</v>
+        <v>1470</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789346</t>
+          <t>2026-04-10T04:43:49.372614</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789349</t>
+          <t>2026-04-10T04:43:49.372617</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789352</t>
+          <t>2026-04-10T04:43:49.372620</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789354</t>
+          <t>2026-04-10T04:43:49.372623</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789357</t>
+          <t>2026-04-10T04:43:49.372625</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789360</t>
+          <t>2026-04-10T04:43:49.372628</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789363</t>
+          <t>2026-04-10T04:43:49.372631</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789366</t>
+          <t>2026-04-10T04:43:49.372634</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789369</t>
+          <t>2026-04-10T04:43:49.372637</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789375</t>
+          <t>2026-04-10T04:43:49.372639</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789378</t>
+          <t>2026-04-10T04:43:49.372642</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789381</t>
+          <t>2026-04-10T04:43:49.372645</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789384</t>
+          <t>2026-04-10T04:43:49.372648</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789387</t>
+          <t>2026-04-10T04:43:49.372651</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1446</v>
+        <v>1435</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789390</t>
+          <t>2026-04-10T04:43:49.372654</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789393</t>
+          <t>2026-04-10T04:43:49.372657</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789395</t>
+          <t>2026-04-10T04:43:49.372660</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789399</t>
+          <t>2026-04-10T04:43:49.372663</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789402</t>
+          <t>2026-04-10T04:43:49.372666</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789405</t>
+          <t>2026-04-10T04:43:49.372668</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789408</t>
+          <t>2026-04-10T04:43:49.372671</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789411</t>
+          <t>2026-04-10T04:43:49.372674</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789414</t>
+          <t>2026-04-10T04:43:49.372677</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789417</t>
+          <t>2026-04-10T04:43:49.372680</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789420</t>
+          <t>2026-04-10T04:43:49.372683</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1405</v>
+        <v>1428</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789423</t>
+          <t>2026-04-10T04:43:49.372686</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789426</t>
+          <t>2026-04-10T04:43:49.372689</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789428</t>
+          <t>2026-04-10T04:43:49.372692</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789431</t>
+          <t>2026-04-10T04:43:49.372695</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789434</t>
+          <t>2026-04-10T04:43:49.372698</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789437</t>
+          <t>2026-04-10T04:43:49.372704</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1395.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1395</v>
+        <v>1445</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789440</t>
+          <t>2026-04-10T04:43:49.372707</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1400.00</t>
+          <t>1447.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1400</v>
+        <v>1447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-09T04:31:11.789443</t>
+          <t>2026-04-10T04:43:49.372710</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1455</v>
+        <v>1448</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372543</t>
+          <t>2026-04-11T04:19:27.271480</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372565</t>
+          <t>2026-04-11T04:19:27.271496</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372569</t>
+          <t>2026-04-11T04:19:27.271500</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372572</t>
+          <t>2026-04-11T04:19:27.271510</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372576</t>
+          <t>2026-04-11T04:19:27.271515</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1422</v>
+        <v>1450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372579</t>
+          <t>2026-04-11T04:19:27.271519</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1422</v>
+        <v>1448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372582</t>
+          <t>2026-04-11T04:19:27.271525</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372585</t>
+          <t>2026-04-11T04:19:27.271530</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372588</t>
+          <t>2026-04-11T04:19:27.271535</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372591</t>
+          <t>2026-04-11T04:19:27.271541</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372594</t>
+          <t>2026-04-11T04:19:27.271544</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372597</t>
+          <t>2026-04-11T04:19:27.271547</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372600</t>
+          <t>2026-04-11T04:19:27.271550</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372603</t>
+          <t>2026-04-11T04:19:27.271552</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372606</t>
+          <t>2026-04-11T04:19:27.271555</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372608</t>
+          <t>2026-04-11T04:19:27.271558</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1476</v>
+        <v>1474</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372611</t>
+          <t>2026-04-11T04:19:27.271561</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372614</t>
+          <t>2026-04-11T04:19:27.271564</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1399</v>
+        <v>1433</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372617</t>
+          <t>2026-04-11T04:19:27.271567</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1431</v>
+        <v>1434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372620</t>
+          <t>2026-04-11T04:19:27.271570</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1434</v>
+        <v>1431</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372623</t>
+          <t>2026-04-11T04:19:27.271573</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372625</t>
+          <t>2026-04-11T04:19:27.271576</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1433</v>
+        <v>1399</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372628</t>
+          <t>2026-04-11T04:19:27.271578</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372631</t>
+          <t>2026-04-11T04:19:27.271581</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1433</v>
+        <v>1431</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372634</t>
+          <t>2026-04-11T04:19:27.271584</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1399</v>
+        <v>1430</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372637</t>
+          <t>2026-04-11T04:19:27.271587</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1431</v>
+        <v>1436</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372639</t>
+          <t>2026-04-11T04:19:27.271590</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1436</v>
+        <v>1399</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372642</t>
+          <t>2026-04-11T04:19:27.271592</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1430</v>
+        <v>1433</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372645</t>
+          <t>2026-04-11T04:19:27.271595</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372648</t>
+          <t>2026-04-11T04:19:27.271598</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1441</v>
+        <v>1418</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372651</t>
+          <t>2026-04-11T04:19:27.271601</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1435</v>
+        <v>1443</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372654</t>
+          <t>2026-04-11T04:19:27.271604</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1418</v>
+        <v>1445</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372657</t>
+          <t>2026-04-11T04:19:27.271607</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372660</t>
+          <t>2026-04-11T04:19:27.271609</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372663</t>
+          <t>2026-04-11T04:19:27.271612</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372666</t>
+          <t>2026-04-11T04:19:27.271615</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372668</t>
+          <t>2026-04-11T04:19:27.271618</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372671</t>
+          <t>2026-04-11T04:19:27.271621</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1418</v>
+        <v>1443</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372674</t>
+          <t>2026-04-11T04:19:27.271624</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372677</t>
+          <t>2026-04-11T04:19:27.271627</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1446</v>
+        <v>1418</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372680</t>
+          <t>2026-04-11T04:19:27.271631</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372683</t>
+          <t>2026-04-11T04:19:27.271634</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1428</v>
+        <v>1449</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372686</t>
+          <t>2026-04-11T04:19:27.271637</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1449</v>
+        <v>1443</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372689</t>
+          <t>2026-04-11T04:19:27.271639</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372692</t>
+          <t>2026-04-11T04:19:27.271642</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372695</t>
+          <t>2026-04-11T04:19:27.271645</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372698</t>
+          <t>2026-04-11T04:19:27.271648</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1428.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1443</v>
+        <v>1428</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372704</t>
+          <t>2026-04-11T04:19:27.271655</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372707</t>
+          <t>2026-04-11T04:19:27.271658</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-10T04:43:49.372710</t>
+          <t>2026-04-11T04:19:27.271661</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271480</t>
+          <t>2026-04-12T04:43:51.574830</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271496</t>
+          <t>2026-04-12T04:43:51.574847</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271500</t>
+          <t>2026-04-12T04:43:51.574852</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271510</t>
+          <t>2026-04-12T04:43:51.574855</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271515</t>
+          <t>2026-04-12T04:43:51.574858</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271519</t>
+          <t>2026-04-12T04:43:51.574861</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271525</t>
+          <t>2026-04-12T04:43:51.574864</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271530</t>
+          <t>2026-04-12T04:43:51.574868</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271535</t>
+          <t>2026-04-12T04:43:51.574871</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271541</t>
+          <t>2026-04-12T04:43:51.574876</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271544</t>
+          <t>2026-04-12T04:43:51.574900</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271547</t>
+          <t>2026-04-12T04:43:51.574905</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271550</t>
+          <t>2026-04-12T04:43:51.574910</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271552</t>
+          <t>2026-04-12T04:43:51.574915</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271555</t>
+          <t>2026-04-12T04:43:51.574920</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271558</t>
+          <t>2026-04-12T04:43:51.574925</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271561</t>
+          <t>2026-04-12T04:43:51.574930</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271564</t>
+          <t>2026-04-12T04:43:51.574934</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271567</t>
+          <t>2026-04-12T04:43:51.574940</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1434</v>
+        <v>1471</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271570</t>
+          <t>2026-04-12T04:43:51.574945</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271573</t>
+          <t>2026-04-12T04:43:51.574950</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271576</t>
+          <t>2026-04-12T04:43:51.574954</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1399</v>
+        <v>1448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271578</t>
+          <t>2026-04-12T04:43:51.574956</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1436</v>
+        <v>1470</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271581</t>
+          <t>2026-04-12T04:43:51.574959</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271584</t>
+          <t>2026-04-12T04:43:51.574962</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271587</t>
+          <t>2026-04-12T04:43:51.574965</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271590</t>
+          <t>2026-04-12T04:43:51.574968</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271592</t>
+          <t>2026-04-12T04:43:51.574971</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271595</t>
+          <t>2026-04-12T04:43:51.574974</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271598</t>
+          <t>2026-04-12T04:43:51.574977</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271601</t>
+          <t>2026-04-12T04:43:51.574980</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271604</t>
+          <t>2026-04-12T04:43:51.574982</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271607</t>
+          <t>2026-04-12T04:43:51.574985</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271609</t>
+          <t>2026-04-12T04:43:51.574988</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271612</t>
+          <t>2026-04-12T04:43:51.574991</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271615</t>
+          <t>2026-04-12T04:43:51.574994</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271618</t>
+          <t>2026-04-12T04:43:51.574997</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271621</t>
+          <t>2026-04-12T04:43:51.575000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271624</t>
+          <t>2026-04-12T04:43:51.575003</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271627</t>
+          <t>2026-04-12T04:43:51.575006</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271631</t>
+          <t>2026-04-12T04:43:51.575009</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1446</v>
+        <v>1435</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271634</t>
+          <t>2026-04-12T04:43:51.575012</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271637</t>
+          <t>2026-04-12T04:43:51.575014</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271639</t>
+          <t>2026-04-12T04:43:51.575017</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271642</t>
+          <t>2026-04-12T04:43:51.575020</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271645</t>
+          <t>2026-04-12T04:43:51.575023</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271648</t>
+          <t>2026-04-12T04:43:51.575026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1428.00</t>
+          <t>1418.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1428</v>
+        <v>1418</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271655</t>
+          <t>2026-04-12T04:43:51.575033</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271658</t>
+          <t>2026-04-12T04:43:51.575036</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1447.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-11T04:19:27.271661</t>
+          <t>2026-04-12T04:43:51.575038</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574830</t>
+          <t>2026-04-13T04:55:08.963865</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1454</v>
+        <v>1443</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574847</t>
+          <t>2026-04-13T04:55:08.963879</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574852</t>
+          <t>2026-04-13T04:55:08.963883</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1422</v>
+        <v>1405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574855</t>
+          <t>2026-04-13T04:55:08.963886</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574858</t>
+          <t>2026-04-13T04:55:08.963889</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574861</t>
+          <t>2026-04-13T04:55:08.963892</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574864</t>
+          <t>2026-04-13T04:55:08.963895</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574868</t>
+          <t>2026-04-13T04:55:08.963898</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574871</t>
+          <t>2026-04-13T04:55:08.963901</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574876</t>
+          <t>2026-04-13T04:55:08.963904</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574900</t>
+          <t>2026-04-13T04:55:08.963907</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574905</t>
+          <t>2026-04-13T04:55:08.963909</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574910</t>
+          <t>2026-04-13T04:55:08.963912</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574915</t>
+          <t>2026-04-13T04:55:08.963915</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574920</t>
+          <t>2026-04-13T04:55:08.963917</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574925</t>
+          <t>2026-04-13T04:55:08.963920</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574930</t>
+          <t>2026-04-13T04:55:08.963923</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574934</t>
+          <t>2026-04-13T04:55:08.963926</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574940</t>
+          <t>2026-04-13T04:55:08.963929</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574945</t>
+          <t>2026-04-13T04:55:08.963931</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574950</t>
+          <t>2026-04-13T04:55:08.963934</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574954</t>
+          <t>2026-04-13T04:55:08.963937</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574956</t>
+          <t>2026-04-13T04:55:08.963939</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574959</t>
+          <t>2026-04-13T04:55:08.963943</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574962</t>
+          <t>2026-04-13T04:55:08.963946</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1434</v>
+        <v>1471</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574965</t>
+          <t>2026-04-13T04:55:08.963948</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1436</v>
+        <v>1470</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574968</t>
+          <t>2026-04-13T04:55:08.963951</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1399</v>
+        <v>1448</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574971</t>
+          <t>2026-04-13T04:55:08.963954</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574974</t>
+          <t>2026-04-13T04:55:08.963957</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574977</t>
+          <t>2026-04-13T04:55:08.963959</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574980</t>
+          <t>2026-04-13T04:55:08.963962</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574982</t>
+          <t>2026-04-13T04:55:08.963965</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574985</t>
+          <t>2026-04-13T04:55:08.963967</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574988</t>
+          <t>2026-04-13T04:55:08.963970</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574991</t>
+          <t>2026-04-13T04:55:08.963973</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574994</t>
+          <t>2026-04-13T04:55:08.963976</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.574997</t>
+          <t>2026-04-13T04:55:08.963979</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575000</t>
+          <t>2026-04-13T04:55:08.963981</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575003</t>
+          <t>2026-04-13T04:55:08.963984</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575006</t>
+          <t>2026-04-13T04:55:08.963987</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575009</t>
+          <t>2026-04-13T04:55:08.963989</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575012</t>
+          <t>2026-04-13T04:55:08.963992</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575014</t>
+          <t>2026-04-13T04:55:08.963995</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575017</t>
+          <t>2026-04-13T04:55:08.963998</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575020</t>
+          <t>2026-04-13T04:55:08.964000</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1446</v>
+        <v>1435</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575023</t>
+          <t>2026-04-13T04:55:08.964003</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575026</t>
+          <t>2026-04-13T04:55:08.964006</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575033</t>
+          <t>2026-04-13T04:55:08.964012</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575036</t>
+          <t>2026-04-13T04:55:08.964015</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1449</v>
+        <v>1442</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-12T04:43:51.575038</t>
+          <t>2026-04-13T04:55:08.964018</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963865</t>
+          <t>2026-04-14T04:42:40.125782</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963879</t>
+          <t>2026-04-14T04:42:40.125796</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963883</t>
+          <t>2026-04-14T04:42:40.125800</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963886</t>
+          <t>2026-04-14T04:42:40.125804</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963889</t>
+          <t>2026-04-14T04:42:40.125807</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1459.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1446</v>
+        <v>1459</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963892</t>
+          <t>2026-04-14T04:42:40.125810</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1454</v>
+        <v>1443</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963895</t>
+          <t>2026-04-14T04:42:40.125814</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963898</t>
+          <t>2026-04-14T04:42:40.125817</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963901</t>
+          <t>2026-04-14T04:42:40.125821</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963904</t>
+          <t>2026-04-14T04:42:40.125824</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1422</v>
+        <v>1405</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963907</t>
+          <t>2026-04-14T04:42:40.125831</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963909</t>
+          <t>2026-04-14T04:42:40.125835</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963912</t>
+          <t>2026-04-14T04:42:40.125840</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963915</t>
+          <t>2026-04-14T04:42:40.125845</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963917</t>
+          <t>2026-04-14T04:42:40.125849</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963920</t>
+          <t>2026-04-14T04:42:40.125854</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963923</t>
+          <t>2026-04-14T04:42:40.125859</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963926</t>
+          <t>2026-04-14T04:42:40.125865</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963929</t>
+          <t>2026-04-14T04:42:40.125870</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963931</t>
+          <t>2026-04-14T04:42:40.125876</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963934</t>
+          <t>2026-04-14T04:42:40.125880</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963937</t>
+          <t>2026-04-14T04:42:40.125886</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963939</t>
+          <t>2026-04-14T04:42:40.125891</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963943</t>
+          <t>2026-04-14T04:42:40.125894</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963946</t>
+          <t>2026-04-14T04:42:40.125898</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963948</t>
+          <t>2026-04-14T04:42:40.125901</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963951</t>
+          <t>2026-04-14T04:42:40.125904</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963954</t>
+          <t>2026-04-14T04:42:40.125907</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963957</t>
+          <t>2026-04-14T04:42:40.125910</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963959</t>
+          <t>2026-04-14T04:42:40.125914</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1399</v>
+        <v>1448</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963962</t>
+          <t>2026-04-14T04:42:40.125917</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963965</t>
+          <t>2026-04-14T04:42:40.125920</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963967</t>
+          <t>2026-04-14T04:42:40.125923</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963970</t>
+          <t>2026-04-14T04:42:40.125926</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1434</v>
+        <v>1471</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963973</t>
+          <t>2026-04-14T04:42:40.125929</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1436</v>
+        <v>1470</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963976</t>
+          <t>2026-04-14T04:42:40.125933</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963979</t>
+          <t>2026-04-14T04:42:40.125936</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963981</t>
+          <t>2026-04-14T04:42:40.125939</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963984</t>
+          <t>2026-04-14T04:42:40.125942</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963987</t>
+          <t>2026-04-14T04:42:40.125945</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963989</t>
+          <t>2026-04-14T04:42:40.125949</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963992</t>
+          <t>2026-04-14T04:42:40.125952</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963995</t>
+          <t>2026-04-14T04:42:40.125955</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.963998</t>
+          <t>2026-04-14T04:42:40.125958</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1431.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1443</v>
+        <v>1431</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.964000</t>
+          <t>2026-04-14T04:42:40.125961</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1436.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.964003</t>
+          <t>2026-04-14T04:42:40.125964</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.964006</t>
+          <t>2026-04-14T04:42:40.125967</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1418.00</t>
+          <t>1399.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1418</v>
+        <v>1399</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.964012</t>
+          <t>2026-04-14T04:42:40.125974</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.964015</t>
+          <t>2026-04-14T04:42:40.125977</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1442.00</t>
+          <t>1441.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-13T04:55:08.964018</t>
+          <t>2026-04-14T04:42:40.125980</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125782</t>
+          <t>2026-04-15T04:42:56.833494</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125796</t>
+          <t>2026-04-15T04:42:56.833507</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1450</v>
+        <v>1478</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125800</t>
+          <t>2026-04-15T04:42:56.833510</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1405</v>
+        <v>1435</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125804</t>
+          <t>2026-04-15T04:42:56.833540</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125807</t>
+          <t>2026-04-15T04:42:56.833547</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1459.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1459</v>
+        <v>1477</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125810</t>
+          <t>2026-04-15T04:42:56.833551</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125814</t>
+          <t>2026-04-15T04:42:56.833554</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125817</t>
+          <t>2026-04-15T04:42:56.833558</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125821</t>
+          <t>2026-04-15T04:42:56.833561</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125824</t>
+          <t>2026-04-15T04:42:56.833564</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125831</t>
+          <t>2026-04-15T04:42:56.833567</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125835</t>
+          <t>2026-04-15T04:42:56.833570</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1422</v>
+        <v>1405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125840</t>
+          <t>2026-04-15T04:42:56.833573</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125845</t>
+          <t>2026-04-15T04:42:56.833576</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125849</t>
+          <t>2026-04-15T04:42:56.833579</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125854</t>
+          <t>2026-04-15T04:42:56.833582</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125859</t>
+          <t>2026-04-15T04:42:56.833585</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1454</v>
+        <v>1443</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125865</t>
+          <t>2026-04-15T04:42:56.833588</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125870</t>
+          <t>2026-04-15T04:42:56.833591</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125876</t>
+          <t>2026-04-15T04:42:56.833594</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125880</t>
+          <t>2026-04-15T04:42:56.833597</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125886</t>
+          <t>2026-04-15T04:42:56.833600</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125891</t>
+          <t>2026-04-15T04:42:56.833603</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125894</t>
+          <t>2026-04-15T04:42:56.833606</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125898</t>
+          <t>2026-04-15T04:42:56.833609</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125901</t>
+          <t>2026-04-15T04:42:56.833612</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125904</t>
+          <t>2026-04-15T04:42:56.833618</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125907</t>
+          <t>2026-04-15T04:42:56.833621</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125910</t>
+          <t>2026-04-15T04:42:56.833624</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125914</t>
+          <t>2026-04-15T04:42:56.833627</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125917</t>
+          <t>2026-04-15T04:42:56.833631</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125920</t>
+          <t>2026-04-15T04:42:56.833634</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125923</t>
+          <t>2026-04-15T04:42:56.833638</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125926</t>
+          <t>2026-04-15T04:42:56.833643</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125929</t>
+          <t>2026-04-15T04:42:56.833646</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125933</t>
+          <t>2026-04-15T04:42:56.833649</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1434</v>
+        <v>1471</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125936</t>
+          <t>2026-04-15T04:42:56.833653</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125939</t>
+          <t>2026-04-15T04:42:56.833657</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125942</t>
+          <t>2026-04-15T04:42:56.833659</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125945</t>
+          <t>2026-04-15T04:42:56.833662</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1399</v>
+        <v>1448</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125949</t>
+          <t>2026-04-15T04:42:56.833665</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1436</v>
+        <v>1470</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125952</t>
+          <t>2026-04-15T04:42:56.833668</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125955</t>
+          <t>2026-04-15T04:42:56.833671</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125958</t>
+          <t>2026-04-15T04:42:56.833674</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125961</t>
+          <t>2026-04-15T04:42:56.833677</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125964</t>
+          <t>2026-04-15T04:42:56.833681</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125967</t>
+          <t>2026-04-15T04:42:56.833684</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125974</t>
+          <t>2026-04-15T04:42:56.833687</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1433.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1445</v>
+        <v>1433</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125977</t>
+          <t>2026-04-15T04:42:56.833690</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1441.00</t>
+          <t>1430.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1441</v>
+        <v>1430</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-14T04:42:40.125980</t>
+          <t>2026-04-15T04:42:56.833693</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833494</t>
+          <t>2026-04-16T04:48:28.663335</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833507</t>
+          <t>2026-04-16T04:48:28.663352</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833510</t>
+          <t>2026-04-16T04:48:28.663356</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1435</v>
+        <v>1476</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833540</t>
+          <t>2026-04-16T04:48:28.663359</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833547</t>
+          <t>2026-04-16T04:48:28.663362</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1477</v>
+        <v>1435</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833551</t>
+          <t>2026-04-16T04:48:28.663365</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1455</v>
+        <v>1435</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833554</t>
+          <t>2026-04-16T04:48:28.663368</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833558</t>
+          <t>2026-04-16T04:48:28.663371</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1448</v>
+        <v>1477</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833561</t>
+          <t>2026-04-16T04:48:28.663374</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1450</v>
+        <v>1481</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833564</t>
+          <t>2026-04-16T04:48:28.663377</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1405</v>
+        <v>1476</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833567</t>
+          <t>2026-04-16T04:48:28.663380</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1450</v>
+        <v>1478</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833570</t>
+          <t>2026-04-16T04:48:28.663383</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833573</t>
+          <t>2026-04-16T04:48:28.663386</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833576</t>
+          <t>2026-04-16T04:48:28.663389</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833579</t>
+          <t>2026-04-16T04:48:28.663391</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833582</t>
+          <t>2026-04-16T04:48:28.663394</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833585</t>
+          <t>2026-04-16T04:48:28.663397</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833588</t>
+          <t>2026-04-16T04:48:28.663400</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1450</v>
+        <v>1405</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833591</t>
+          <t>2026-04-16T04:48:28.663403</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833594</t>
+          <t>2026-04-16T04:48:28.663406</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833597</t>
+          <t>2026-04-16T04:48:28.663408</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833600</t>
+          <t>2026-04-16T04:48:28.663411</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1422</v>
+        <v>1450</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833603</t>
+          <t>2026-04-16T04:48:28.663414</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833606</t>
+          <t>2026-04-16T04:48:28.663417</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833609</t>
+          <t>2026-04-16T04:48:28.663419</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1455</v>
+        <v>1422</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833612</t>
+          <t>2026-04-16T04:48:28.663422</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833618</t>
+          <t>2026-04-16T04:48:28.663428</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1422</v>
+        <v>1450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833621</t>
+          <t>2026-04-16T04:48:28.663431</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833624</t>
+          <t>2026-04-16T04:48:28.663434</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833627</t>
+          <t>2026-04-16T04:48:28.663437</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1422</v>
+        <v>1455</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833631</t>
+          <t>2026-04-16T04:48:28.663440</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833634</t>
+          <t>2026-04-16T04:48:28.663443</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1450</v>
+        <v>1422</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833638</t>
+          <t>2026-04-16T04:48:28.663446</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833643</t>
+          <t>2026-04-16T04:48:28.663449</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833646</t>
+          <t>2026-04-16T04:48:28.663452</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833649</t>
+          <t>2026-04-16T04:48:28.663454</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833653</t>
+          <t>2026-04-16T04:48:28.663457</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833657</t>
+          <t>2026-04-16T04:48:28.663460</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1474</v>
+        <v>1422</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833659</t>
+          <t>2026-04-16T04:48:28.663463</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1476</v>
+        <v>1448</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833662</t>
+          <t>2026-04-16T04:48:28.663466</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833665</t>
+          <t>2026-04-16T04:48:28.663469</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1470</v>
+        <v>1450</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833668</t>
+          <t>2026-04-16T04:48:28.663472</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1434</v>
+        <v>1448</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833671</t>
+          <t>2026-04-16T04:48:28.663474</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1431</v>
+        <v>1471</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833674</t>
+          <t>2026-04-16T04:48:28.663477</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1431.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1431</v>
+        <v>1474</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833677</t>
+          <t>2026-04-16T04:48:28.663480</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1436.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1436</v>
+        <v>1476</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833681</t>
+          <t>2026-04-16T04:48:28.663483</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1470.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1433</v>
+        <v>1470</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833684</t>
+          <t>2026-04-16T04:48:28.663486</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1399.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1399</v>
+        <v>1474</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833687</t>
+          <t>2026-04-16T04:48:28.663489</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833690</t>
+          <t>2026-04-16T04:48:28.663491</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1430.00</t>
+          <t>1434.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1430</v>
+        <v>1434</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-15T04:42:56.833693</t>
+          <t>2026-04-16T04:48:28.663494</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1471</v>
+        <v>1455</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663335</t>
+          <t>2026-04-17T04:46:14.896561</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663352</t>
+          <t>2026-04-17T04:46:14.896572</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663356</t>
+          <t>2026-04-17T04:46:14.896577</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663359</t>
+          <t>2026-04-17T04:46:14.896582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1477</v>
+        <v>1468</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663362</t>
+          <t>2026-04-17T04:46:14.896586</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663365</t>
+          <t>2026-04-17T04:46:14.896590</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663368</t>
+          <t>2026-04-17T04:46:14.896593</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663371</t>
+          <t>2026-04-17T04:46:14.896597</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663374</t>
+          <t>2026-04-17T04:46:14.896600</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663377</t>
+          <t>2026-04-17T04:46:14.896603</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663380</t>
+          <t>2026-04-17T04:46:14.896607</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663383</t>
+          <t>2026-04-17T04:46:14.896610</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1405</v>
+        <v>1435</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663386</t>
+          <t>2026-04-17T04:46:14.896613</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663389</t>
+          <t>2026-04-17T04:46:14.896616</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663391</t>
+          <t>2026-04-17T04:46:14.896620</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663394</t>
+          <t>2026-04-17T04:46:14.896623</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1450</v>
+        <v>1478</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663397</t>
+          <t>2026-04-17T04:46:14.896626</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663400</t>
+          <t>2026-04-17T04:46:14.896651</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663403</t>
+          <t>2026-04-17T04:46:14.896655</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663406</t>
+          <t>2026-04-17T04:46:14.896658</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663408</t>
+          <t>2026-04-17T04:46:14.896662</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663411</t>
+          <t>2026-04-17T04:46:14.896665</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663414</t>
+          <t>2026-04-17T04:46:14.896668</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663417</t>
+          <t>2026-04-17T04:46:14.896671</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663419</t>
+          <t>2026-04-17T04:46:14.896675</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1422</v>
+        <v>1405</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663422</t>
+          <t>2026-04-17T04:46:14.896678</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663428</t>
+          <t>2026-04-17T04:46:14.896681</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663431</t>
+          <t>2026-04-17T04:46:14.896685</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1454</v>
+        <v>1443</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663434</t>
+          <t>2026-04-17T04:46:14.896688</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663437</t>
+          <t>2026-04-17T04:46:14.896694</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663440</t>
+          <t>2026-04-17T04:46:14.896697</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663443</t>
+          <t>2026-04-17T04:46:14.896701</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663446</t>
+          <t>2026-04-17T04:46:14.896704</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663449</t>
+          <t>2026-04-17T04:46:14.896707</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663452</t>
+          <t>2026-04-17T04:46:14.896710</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663454</t>
+          <t>2026-04-17T04:46:14.896714</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663457</t>
+          <t>2026-04-17T04:46:14.896717</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663460</t>
+          <t>2026-04-17T04:46:14.896720</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663463</t>
+          <t>2026-04-17T04:46:14.896723</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663466</t>
+          <t>2026-04-17T04:46:14.896727</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663469</t>
+          <t>2026-04-17T04:46:14.896730</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663472</t>
+          <t>2026-04-17T04:46:14.896733</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663474</t>
+          <t>2026-04-17T04:46:14.896737</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663477</t>
+          <t>2026-04-17T04:46:14.896740</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663480</t>
+          <t>2026-04-17T04:46:14.896744</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663483</t>
+          <t>2026-04-17T04:46:14.896748</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1470.00</t>
+          <t>1449.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1470</v>
+        <v>1449</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663486</t>
+          <t>2026-04-17T04:46:14.896752</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1474</v>
+        <v>1448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663489</t>
+          <t>2026-04-17T04:46:14.896755</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1433.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1433</v>
+        <v>1476</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663491</t>
+          <t>2026-04-17T04:46:14.896758</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1434.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1434</v>
+        <v>1471</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-16T04:48:28.663494</t>
+          <t>2026-04-17T04:46:14.896761</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896561</t>
+          <t>2026-04-18T04:29:42.373188</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896572</t>
+          <t>2026-04-18T04:29:42.373205</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1475.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896577</t>
+          <t>2026-04-18T04:29:42.373208</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896582</t>
+          <t>2026-04-18T04:29:42.373211</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1468.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1468</v>
+        <v>1478</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896586</t>
+          <t>2026-04-18T04:29:42.373215</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896590</t>
+          <t>2026-04-18T04:29:42.373218</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896593</t>
+          <t>2026-04-18T04:29:42.373221</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896597</t>
+          <t>2026-04-18T04:29:42.373224</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1477</v>
+        <v>1468</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896600</t>
+          <t>2026-04-18T04:29:42.373227</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1471</v>
+        <v>1455</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896603</t>
+          <t>2026-04-18T04:29:42.373230</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896607</t>
+          <t>2026-04-18T04:29:42.373233</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896610</t>
+          <t>2026-04-18T04:29:42.373235</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896613</t>
+          <t>2026-04-18T04:29:42.373238</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896616</t>
+          <t>2026-04-18T04:29:42.373241</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896620</t>
+          <t>2026-04-18T04:29:42.373244</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896623</t>
+          <t>2026-04-18T04:29:42.373246</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896626</t>
+          <t>2026-04-18T04:29:42.373249</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896651</t>
+          <t>2026-04-18T04:29:42.373253</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1405</v>
+        <v>1435</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896655</t>
+          <t>2026-04-18T04:29:42.373256</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896658</t>
+          <t>2026-04-18T04:29:42.373258</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896662</t>
+          <t>2026-04-18T04:29:42.373261</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896665</t>
+          <t>2026-04-18T04:29:42.373264</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1450</v>
+        <v>1478</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896668</t>
+          <t>2026-04-18T04:29:42.373267</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896671</t>
+          <t>2026-04-18T04:29:42.373272</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896675</t>
+          <t>2026-04-18T04:29:42.373275</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896678</t>
+          <t>2026-04-18T04:29:42.373278</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896681</t>
+          <t>2026-04-18T04:29:42.373281</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896685</t>
+          <t>2026-04-18T04:29:42.373284</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896688</t>
+          <t>2026-04-18T04:29:42.373287</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896694</t>
+          <t>2026-04-18T04:29:42.373290</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1454</v>
+        <v>1443</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896697</t>
+          <t>2026-04-18T04:29:42.373292</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896701</t>
+          <t>2026-04-18T04:29:42.373295</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1422</v>
+        <v>1405</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896704</t>
+          <t>2026-04-18T04:29:42.373298</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896707</t>
+          <t>2026-04-18T04:29:42.373301</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896710</t>
+          <t>2026-04-18T04:29:42.373304</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896714</t>
+          <t>2026-04-18T04:29:42.373306</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896717</t>
+          <t>2026-04-18T04:29:42.373309</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896720</t>
+          <t>2026-04-18T04:29:42.373314</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896723</t>
+          <t>2026-04-18T04:29:42.373317</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896727</t>
+          <t>2026-04-18T04:29:42.373320</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896730</t>
+          <t>2026-04-18T04:29:42.373323</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896733</t>
+          <t>2026-04-18T04:29:42.373325</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896737</t>
+          <t>2026-04-18T04:29:42.373328</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896740</t>
+          <t>2026-04-18T04:29:42.373331</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896744</t>
+          <t>2026-04-18T04:29:42.373334</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896748</t>
+          <t>2026-04-18T04:29:42.373337</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1449.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896752</t>
+          <t>2026-04-18T04:29:42.373340</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896755</t>
+          <t>2026-04-18T04:29:42.373342</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1476</v>
+        <v>1450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896758</t>
+          <t>2026-04-18T04:29:42.373346</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1471</v>
+        <v>1448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-17T04:46:14.896761</t>
+          <t>2026-04-18T04:29:42.373348</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,7 +544,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373188</t>
+          <t>2026-04-19T04:47:52.947466</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,7 +609,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373205</t>
+          <t>2026-04-19T04:47:52.947482</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373208</t>
+          <t>2026-04-19T04:47:52.947486</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1473</v>
+        <v>1435</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373211</t>
+          <t>2026-04-19T04:47:52.947489</t>
         </is>
       </c>
     </row>
@@ -751,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373215</t>
+          <t>2026-04-19T04:47:52.947492</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1435</v>
+        <v>1478</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373218</t>
+          <t>2026-04-19T04:47:52.947495</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1435</v>
+        <v>1455</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373221</t>
+          <t>2026-04-19T04:47:52.947498</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373224</t>
+          <t>2026-04-19T04:47:52.947501</t>
         </is>
       </c>
     </row>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1468.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373227</t>
+          <t>2026-04-19T04:47:52.947505</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1455</v>
+        <v>1468</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373230</t>
+          <t>2026-04-19T04:47:52.947507</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1463</v>
+        <v>1435</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373233</t>
+          <t>2026-04-19T04:47:52.947510</t>
         </is>
       </c>
     </row>
@@ -1259,7 +1259,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373235</t>
+          <t>2026-04-19T04:47:52.947513</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373238</t>
+          <t>2026-04-19T04:47:52.947516</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373241</t>
+          <t>2026-04-19T04:47:52.947518</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373244</t>
+          <t>2026-04-19T04:47:52.947521</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373246</t>
+          <t>2026-04-19T04:47:52.947524</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373249</t>
+          <t>2026-04-19T04:47:52.947527</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373253</t>
+          <t>2026-04-19T04:47:52.947530</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1435</v>
+        <v>1478</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373256</t>
+          <t>2026-04-19T04:47:52.947532</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1476</v>
+        <v>1481</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373258</t>
+          <t>2026-04-19T04:47:52.947535</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373261</t>
+          <t>2026-04-19T04:47:52.947538</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1909,7 +1909,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373264</t>
+          <t>2026-04-19T04:47:52.947541</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1478</v>
+        <v>1435</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373267</t>
+          <t>2026-04-19T04:47:52.947543</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373272</t>
+          <t>2026-04-19T04:47:52.947546</t>
         </is>
       </c>
     </row>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373275</t>
+          <t>2026-04-19T04:47:52.947551</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1405</v>
+        <v>1455</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373278</t>
+          <t>2026-04-19T04:47:52.947554</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373281</t>
+          <t>2026-04-19T04:47:52.947557</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1450</v>
+        <v>1405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373284</t>
+          <t>2026-04-19T04:47:52.947560</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373287</t>
+          <t>2026-04-19T04:47:52.947563</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2429,7 +2429,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373290</t>
+          <t>2026-04-19T04:47:52.947566</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1443</v>
+        <v>1405</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373292</t>
+          <t>2026-04-19T04:47:52.947568</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373295</t>
+          <t>2026-04-19T04:47:52.947571</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373298</t>
+          <t>2026-04-19T04:47:52.947574</t>
         </is>
       </c>
     </row>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373301</t>
+          <t>2026-04-19T04:47:52.947577</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1450</v>
+        <v>1443</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373304</t>
+          <t>2026-04-19T04:47:52.947579</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1448</v>
+        <v>1446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373306</t>
+          <t>2026-04-19T04:47:52.947582</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1448</v>
+        <v>1454</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373309</t>
+          <t>2026-04-19T04:47:52.947585</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1454</v>
+        <v>1448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373314</t>
+          <t>2026-04-19T04:47:52.947588</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1422</v>
+        <v>1448</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373317</t>
+          <t>2026-04-19T04:47:52.947590</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373320</t>
+          <t>2026-04-19T04:47:52.947593</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1450</v>
+        <v>1422</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373323</t>
+          <t>2026-04-19T04:47:52.947596</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373325</t>
+          <t>2026-04-19T04:47:52.947601</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1422</v>
+        <v>1455</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373328</t>
+          <t>2026-04-19T04:47:52.947604</t>
         </is>
       </c>
     </row>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1455</v>
+        <v>1448</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373331</t>
+          <t>2026-04-19T04:47:52.947608</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373334</t>
+          <t>2026-04-19T04:47:52.947611</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373337</t>
+          <t>2026-04-19T04:47:52.947613</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373340</t>
+          <t>2026-04-19T04:47:52.947616</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1448</v>
+        <v>1422</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373342</t>
+          <t>2026-04-19T04:47:52.947619</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373346</t>
+          <t>2026-04-19T04:47:52.947622</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-18T04:29:42.373348</t>
+          <t>2026-04-19T04:47:52.947625</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947466</t>
+          <t>2026-04-20T04:54:55.263321</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1474</v>
+        <v>1465</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947482</t>
+          <t>2026-04-20T04:54:55.263337</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1475.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1475</v>
+        <v>1465</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947486</t>
+          <t>2026-04-20T04:54:55.263342</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947489</t>
+          <t>2026-04-20T04:54:55.263345</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947492</t>
+          <t>2026-04-20T04:54:55.263348</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1461.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1478</v>
+        <v>1461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947495</t>
+          <t>2026-04-20T04:54:55.263351</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947498</t>
+          <t>2026-04-20T04:54:55.263354</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947501</t>
+          <t>2026-04-20T04:54:55.263358</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947505</t>
+          <t>2026-04-20T04:54:55.263361</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1468.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1468</v>
+        <v>1478</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947507</t>
+          <t>2026-04-20T04:54:55.263364</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947510</t>
+          <t>2026-04-20T04:54:55.263367</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1475.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947513</t>
+          <t>2026-04-20T04:54:55.263371</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947516</t>
+          <t>2026-04-20T04:54:55.263374</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1477</v>
+        <v>1468</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947518</t>
+          <t>2026-04-20T04:54:55.263376</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947521</t>
+          <t>2026-04-20T04:54:55.263379</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947524</t>
+          <t>2026-04-20T04:54:55.263382</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947527</t>
+          <t>2026-04-20T04:54:55.263385</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1471</v>
+        <v>1455</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947530</t>
+          <t>2026-04-20T04:54:55.263388</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947532</t>
+          <t>2026-04-20T04:54:55.263391</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947535</t>
+          <t>2026-04-20T04:54:55.263394</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947538</t>
+          <t>2026-04-20T04:54:55.263397</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947541</t>
+          <t>2026-04-20T04:54:55.263400</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947543</t>
+          <t>2026-04-20T04:54:55.263402</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947546</t>
+          <t>2026-04-20T04:54:55.263408</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947551</t>
+          <t>2026-04-20T04:54:55.263411</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1455</v>
+        <v>1481</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947554</t>
+          <t>2026-04-20T04:54:55.263413</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947557</t>
+          <t>2026-04-20T04:54:55.263416</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1405</v>
+        <v>1435</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947560</t>
+          <t>2026-04-20T04:54:55.263419</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1450</v>
+        <v>1478</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947563</t>
+          <t>2026-04-20T04:54:55.263422</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947566</t>
+          <t>2026-04-20T04:54:55.263425</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947568</t>
+          <t>2026-04-20T04:54:55.263427</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947571</t>
+          <t>2026-04-20T04:54:55.263430</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947574</t>
+          <t>2026-04-20T04:54:55.263433</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947577</t>
+          <t>2026-04-20T04:54:55.263436</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947579</t>
+          <t>2026-04-20T04:54:55.263439</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947582</t>
+          <t>2026-04-20T04:54:55.263442</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1454</v>
+        <v>1443</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947585</t>
+          <t>2026-04-20T04:54:55.263445</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947588</t>
+          <t>2026-04-20T04:54:55.263448</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947590</t>
+          <t>2026-04-20T04:54:55.263450</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947593</t>
+          <t>2026-04-20T04:54:55.263453</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1422</v>
+        <v>1405</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947596</t>
+          <t>2026-04-20T04:54:55.263456</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947601</t>
+          <t>2026-04-20T04:54:55.263459</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947604</t>
+          <t>2026-04-20T04:54:55.263462</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947608</t>
+          <t>2026-04-20T04:54:55.263465</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3404,14 +3404,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947611</t>
+          <t>2026-04-20T04:54:55.263468</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947613</t>
+          <t>2026-04-20T04:54:55.263471</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3534,14 +3534,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947616</t>
+          <t>2026-04-20T04:54:55.263474</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947619</t>
+          <t>2026-04-20T04:54:55.263477</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947622</t>
+          <t>2026-04-20T04:54:55.263480</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1448</v>
+        <v>1455</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-19T04:47:52.947625</t>
+          <t>2026-04-20T04:54:55.263483</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263321</t>
+          <t>2026-04-21T04:45:45.088692</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1469.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263337</t>
+          <t>2026-04-21T04:45:45.088707</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1465</v>
+        <v>1435</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263342</t>
+          <t>2026-04-21T04:45:45.088710</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1435</v>
+        <v>1463</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263345</t>
+          <t>2026-04-21T04:45:45.088713</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263348</t>
+          <t>2026-04-21T04:45:45.088716</t>
         </is>
       </c>
     </row>
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1461.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1461</v>
+        <v>1435</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263351</t>
+          <t>2026-04-21T04:45:45.088719</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1474</v>
+        <v>1465</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263354</t>
+          <t>2026-04-21T04:45:45.088722</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263358</t>
+          <t>2026-04-21T04:45:45.088726</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263361</t>
+          <t>2026-04-21T04:45:45.088729</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1461.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1478</v>
+        <v>1461</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263364</t>
+          <t>2026-04-21T04:45:45.088732</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1435</v>
+        <v>1463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263367</t>
+          <t>2026-04-21T04:45:45.088735</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1475.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1475</v>
+        <v>1478</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263371</t>
+          <t>2026-04-21T04:45:45.088738</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1475.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1435</v>
+        <v>1475</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263374</t>
+          <t>2026-04-21T04:45:45.088741</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1468.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1468</v>
+        <v>1473</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263376</t>
+          <t>2026-04-21T04:45:45.088743</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1465</v>
+        <v>1435</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263379</t>
+          <t>2026-04-21T04:45:45.088746</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1463</v>
+        <v>1474</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263382</t>
+          <t>2026-04-21T04:45:45.088749</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263385</t>
+          <t>2026-04-21T04:45:45.088752</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1455</v>
+        <v>1468</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263388</t>
+          <t>2026-04-21T04:45:45.088757</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1478</v>
+        <v>1463</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263391</t>
+          <t>2026-04-21T04:45:45.088760</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1471</v>
+        <v>1463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263394</t>
+          <t>2026-04-21T04:45:45.088763</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1476</v>
+        <v>1465</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263397</t>
+          <t>2026-04-21T04:45:45.088766</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1476</v>
+        <v>1435</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263400</t>
+          <t>2026-04-21T04:45:45.088769</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1435</v>
+        <v>1455</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263402</t>
+          <t>2026-04-21T04:45:45.088771</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263408</t>
+          <t>2026-04-21T04:45:45.088774</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263411</t>
+          <t>2026-04-21T04:45:45.088777</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263413</t>
+          <t>2026-04-21T04:45:45.088781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1477</v>
+        <v>1435</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263416</t>
+          <t>2026-04-21T04:45:45.088784</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1435</v>
+        <v>1476</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263419</t>
+          <t>2026-04-21T04:45:45.088788</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,7 +2364,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263422</t>
+          <t>2026-04-21T04:45:45.088791</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1476</v>
+        <v>1435</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263425</t>
+          <t>2026-04-21T04:45:45.088794</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1405</v>
+        <v>1476</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263427</t>
+          <t>2026-04-21T04:45:45.088796</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1448</v>
+        <v>1481</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263430</t>
+          <t>2026-04-21T04:45:45.088799</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1450</v>
+        <v>1476</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263433</t>
+          <t>2026-04-21T04:45:45.088802</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1448</v>
+        <v>1478</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263436</t>
+          <t>2026-04-21T04:45:45.088805</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1455</v>
+        <v>1477</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263439</t>
+          <t>2026-04-21T04:45:45.088808</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1450</v>
+        <v>1455</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263442</t>
+          <t>2026-04-21T04:45:45.088811</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1443</v>
+        <v>1450</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263445</t>
+          <t>2026-04-21T04:45:45.088814</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263448</t>
+          <t>2026-04-21T04:45:45.088819</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263450</t>
+          <t>2026-04-21T04:45:45.088821</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1450</v>
+        <v>1405</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263453</t>
+          <t>2026-04-21T04:45:45.088824</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1405</v>
+        <v>1450</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263456</t>
+          <t>2026-04-21T04:45:45.088827</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263459</t>
+          <t>2026-04-21T04:45:45.088830</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1454</v>
+        <v>1405</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263462</t>
+          <t>2026-04-21T04:45:45.088833</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263465</t>
+          <t>2026-04-21T04:45:45.088836</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263468</t>
+          <t>2026-04-21T04:45:45.088838</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263471</t>
+          <t>2026-04-21T04:45:45.088841</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1446.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263474</t>
+          <t>2026-04-21T04:45:45.088844</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1422</v>
+        <v>1450</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263477</t>
+          <t>2026-04-21T04:45:45.088847</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1454.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1450</v>
+        <v>1454</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263480</t>
+          <t>2026-04-21T04:45:45.088850</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-20T04:54:55.263483</t>
+          <t>2026-04-21T04:45:45.088853</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1465</v>
+        <v>1453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088692</t>
+          <t>2026-04-22T04:43:36.579139</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1469.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1469</v>
+        <v>1448</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,19 +609,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088707</t>
+          <t>2026-04-22T04:43:36.579155</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1435</v>
+        <v>1455</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088710</t>
+          <t>2026-04-22T04:43:36.579158</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1463</v>
+        <v>1422</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088713</t>
+          <t>2026-04-22T04:43:36.579162</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1463</v>
+        <v>1453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088716</t>
+          <t>2026-04-22T04:43:36.579164</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1457.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1435</v>
+        <v>1457</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088719</t>
+          <t>2026-04-22T04:43:36.579167</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1469.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088722</t>
+          <t>2026-04-22T04:43:36.579170</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088726</t>
+          <t>2026-04-22T04:43:36.579174</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088729</t>
+          <t>2026-04-22T04:43:36.579177</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1461.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088732</t>
+          <t>2026-04-22T04:43:36.579180</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1463</v>
+        <v>1435</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,19 +1194,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088735</t>
+          <t>2026-04-22T04:43:36.579182</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088738</t>
+          <t>2026-04-22T04:43:36.579185</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1475.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1475</v>
+        <v>1435</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088741</t>
+          <t>2026-04-22T04:43:36.579188</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1461.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1473</v>
+        <v>1461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088743</t>
+          <t>2026-04-22T04:43:36.579191</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1435</v>
+        <v>1465</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088746</t>
+          <t>2026-04-22T04:43:36.579194</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1474</v>
+        <v>1463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088749</t>
+          <t>2026-04-22T04:43:36.579196</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088752</t>
+          <t>2026-04-22T04:43:36.579199</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1468.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1468</v>
+        <v>1465</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088757</t>
+          <t>2026-04-22T04:43:36.579202</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1475.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1463</v>
+        <v>1475</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088760</t>
+          <t>2026-04-22T04:43:36.579205</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1463</v>
+        <v>1474</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088763</t>
+          <t>2026-04-22T04:43:36.579208</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1465</v>
+        <v>1473</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088766</t>
+          <t>2026-04-22T04:43:36.579210</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1435</v>
+        <v>1473</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088769</t>
+          <t>2026-04-22T04:43:36.579213</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1455</v>
+        <v>1435</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,19 +1974,19 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088771</t>
+          <t>2026-04-22T04:43:36.579216</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1471</v>
+        <v>1478</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088774</t>
+          <t>2026-04-22T04:43:36.579218</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1477</v>
+        <v>1463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088777</t>
+          <t>2026-04-22T04:43:36.579221</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1476</v>
+        <v>1455</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088781</t>
+          <t>2026-04-22T04:43:36.579224</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1435</v>
+        <v>1468</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088784</t>
+          <t>2026-04-22T04:43:36.579227</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1476</v>
+        <v>1435</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088788</t>
+          <t>2026-04-22T04:43:36.579230</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088791</t>
+          <t>2026-04-22T04:43:36.579233</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1435</v>
+        <v>1463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088794</t>
+          <t>2026-04-22T04:43:36.579236</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1476</v>
+        <v>1435</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088796</t>
+          <t>2026-04-22T04:43:36.579239</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088799</t>
+          <t>2026-04-22T04:43:36.579241</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088802</t>
+          <t>2026-04-22T04:43:36.579244</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088805</t>
+          <t>2026-04-22T04:43:36.579247</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1477</v>
+        <v>1471</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088808</t>
+          <t>2026-04-22T04:43:36.579250</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1455</v>
+        <v>1477</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088811</t>
+          <t>2026-04-22T04:43:36.579253</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1450</v>
+        <v>1481</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088814</t>
+          <t>2026-04-22T04:43:36.579256</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088819</t>
+          <t>2026-04-22T04:43:36.579259</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088821</t>
+          <t>2026-04-22T04:43:36.579262</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1405</v>
+        <v>1478</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088824</t>
+          <t>2026-04-22T04:43:36.579265</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1450</v>
+        <v>1435</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088827</t>
+          <t>2026-04-22T04:43:36.579267</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1448</v>
+        <v>1477</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088830</t>
+          <t>2026-04-22T04:43:36.579270</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1405</v>
+        <v>1455</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088833</t>
+          <t>2026-04-22T04:43:36.579273</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1443</v>
+        <v>1448</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088836</t>
+          <t>2026-04-22T04:43:36.579276</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1450</v>
+        <v>1448</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088838</t>
+          <t>2026-04-22T04:43:36.579279</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088841</t>
+          <t>2026-04-22T04:43:36.579282</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1446.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1446</v>
+        <v>1450</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088844</t>
+          <t>2026-04-22T04:43:36.579288</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1405.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1450</v>
+        <v>1405</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3599,19 +3599,19 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088847</t>
+          <t>2026-04-22T04:43:36.579291</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3621,11 +3621,11 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1454.00</t>
+          <t>1450.00</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3664,19 +3664,19 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088850</t>
+          <t>2026-04-22T04:43:36.579294</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1450</v>
+        <v>1443</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-21T04:45:45.088853</t>
+          <t>2026-04-22T04:43:36.579297</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,12 +486,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1453.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,19 +544,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579139</t>
+          <t>2026-04-23T04:47:38.296271</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1448</v>
+        <v>1453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579155</t>
+          <t>2026-04-23T04:47:38.296284</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,19 +674,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579158</t>
+          <t>2026-04-23T04:47:38.296288</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1422</v>
+        <v>1453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,19 +739,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579162</t>
+          <t>2026-04-23T04:47:38.296291</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1453.00</t>
+          <t>1456.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1453</v>
+        <v>1456</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,19 +804,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579164</t>
+          <t>2026-04-23T04:47:38.296295</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1457.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1457</v>
+        <v>1422</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,19 +869,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579167</t>
+          <t>2026-04-23T04:47:38.296299</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -891,11 +891,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1469.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1469</v>
+        <v>1422</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,19 +934,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579170</t>
+          <t>2026-04-23T04:47:38.296303</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -956,11 +956,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1463</v>
+        <v>1453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579174</t>
+          <t>2026-04-23T04:47:38.296307</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1457.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1463</v>
+        <v>1457</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1064,19 +1064,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579177</t>
+          <t>2026-04-23T04:47:38.296310</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1465</v>
+        <v>1448</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1129,19 +1129,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579180</t>
+          <t>2026-04-23T04:47:38.296313</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1151,11 +1151,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1435</v>
+        <v>1453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579182</t>
+          <t>2026-04-23T04:47:38.296315</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1216,11 +1216,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579185</t>
+          <t>2026-04-23T04:47:38.296318</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579188</t>
+          <t>2026-04-23T04:47:38.296321</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1461.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,19 +1389,19 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579191</t>
+          <t>2026-04-23T04:47:38.296323</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1465</v>
+        <v>1463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,19 +1454,19 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579194</t>
+          <t>2026-04-23T04:47:38.296326</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1469.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1463</v>
+        <v>1469</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,19 +1519,19 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579196</t>
+          <t>2026-04-23T04:47:38.296329</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,19 +1584,19 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579199</t>
+          <t>2026-04-23T04:47:38.296332</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,19 +1649,19 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579202</t>
+          <t>2026-04-23T04:47:38.296335</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1671,11 +1671,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1475.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1475</v>
+        <v>1435</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1714,19 +1714,19 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579205</t>
+          <t>2026-04-23T04:47:38.296338</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1736,11 +1736,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1474</v>
+        <v>1463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,19 +1779,19 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579208</t>
+          <t>2026-04-23T04:47:38.296340</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,19 +1844,19 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579210</t>
+          <t>2026-04-23T04:47:38.296343</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1866,11 +1866,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579213</t>
+          <t>2026-04-23T04:47:38.296346</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1931,11 +1931,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1435</v>
+        <v>1465</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579216</t>
+          <t>2026-04-23T04:47:38.296349</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1461.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1478</v>
+        <v>1461</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,19 +2039,19 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579218</t>
+          <t>2026-04-23T04:47:38.296351</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1475.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1463</v>
+        <v>1475</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,19 +2104,19 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579221</t>
+          <t>2026-04-23T04:47:38.296354</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2126,11 +2126,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1455</v>
+        <v>1435</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2169,19 +2169,19 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579224</t>
+          <t>2026-04-23T04:47:38.296357</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1468.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1468</v>
+        <v>1473</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,19 +2234,19 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579227</t>
+          <t>2026-04-23T04:47:38.296360</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1435</v>
+        <v>1478</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,19 +2299,19 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579230</t>
+          <t>2026-04-23T04:47:38.296362</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1465</v>
+        <v>1474</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,19 +2364,19 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579233</t>
+          <t>2026-04-23T04:47:38.296365</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,19 +2429,19 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579236</t>
+          <t>2026-04-23T04:47:38.296368</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1435</v>
+        <v>1455</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,19 +2494,19 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579239</t>
+          <t>2026-04-23T04:47:38.296371</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,19 +2559,19 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579241</t>
+          <t>2026-04-23T04:47:38.296373</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2581,11 +2581,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1478</v>
+        <v>1435</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2624,19 +2624,19 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579244</t>
+          <t>2026-04-23T04:47:38.296376</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,19 +2689,19 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579247</t>
+          <t>2026-04-23T04:47:38.296379</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1471</v>
+        <v>1465</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2754,19 +2754,19 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579250</t>
+          <t>2026-04-23T04:47:38.296382</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1477</v>
+        <v>1463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,19 +2819,19 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579253</t>
+          <t>2026-04-23T04:47:38.296385</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,19 +2884,19 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579256</t>
+          <t>2026-04-23T04:47:38.296387</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2949,19 +2949,19 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579259</t>
+          <t>2026-04-23T04:47:38.296390</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2971,11 +2971,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1476</v>
+        <v>1435</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3014,19 +3014,19 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579262</t>
+          <t>2026-04-23T04:47:38.296393</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1478</v>
+        <v>1476</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579265</t>
+          <t>2026-04-23T04:47:38.296396</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1435</v>
+        <v>1477</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,19 +3144,19 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579267</t>
+          <t>2026-04-23T04:47:38.296398</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,19 +3209,19 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579270</t>
+          <t>2026-04-23T04:47:38.296401</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>周生生</t>
+          <t>菜百</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3231,11 +3231,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1455</v>
+        <v>1435</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3274,19 +3274,19 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579273</t>
+          <t>2026-04-23T04:47:38.296404</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>六福</t>
+          <t>周生生</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1481.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1448</v>
+        <v>1481</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,19 +3339,19 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579276</t>
+          <t>2026-04-23T04:47:38.296407</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>金至尊</t>
+          <t>六福</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3361,11 +3361,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1448</v>
+        <v>1476</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3404,19 +3404,19 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579279</t>
+          <t>2026-04-23T04:47:38.296410</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>老庙</t>
+          <t>周大福</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3426,11 +3426,11 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1450</v>
+        <v>1478</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -3469,19 +3469,19 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579282</t>
+          <t>2026-04-23T04:47:38.296413</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>周大福</t>
+          <t>老庙</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3491,11 +3491,11 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1450.00</t>
+          <t>1477.00</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1450</v>
+        <v>1477</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3534,19 +3534,19 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579288</t>
+          <t>2026-04-23T04:47:38.296418</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>菜百</t>
+          <t>金至尊</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3556,11 +3556,11 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1405.00</t>
+          <t>1476.00</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1405</v>
+        <v>1476</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3599,14 +3599,14 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579291</t>
+          <t>2026-04-23T04:47:38.296421</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3664,14 +3664,14 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579294</t>
+          <t>2026-04-23T04:47:38.296424</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3686,11 +3686,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1443.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-04-22T04:43:36.579297</t>
+          <t>2026-04-23T04:47:38.296427</t>
         </is>
       </c>
     </row>

--- a/physical_gold_latest.xlsx
+++ b/physical_gold_latest.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,11 +501,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1445.00</t>
+          <t>1435.00</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>1435</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,14 +544,14 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296271</t>
+          <t>2026-04-24T04:51:34.299728</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -566,11 +566,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1453.00</t>
+          <t>1440.00</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1453</v>
+        <v>1440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -609,14 +609,14 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296284</t>
+          <t>2026-04-24T04:51:34.299742</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -631,11 +631,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1442.00</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1455</v>
+        <v>1442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,14 +674,14 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296288</t>
+          <t>2026-04-24T04:51:34.299746</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -696,11 +696,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1453.00</t>
+          <t>1440.00</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1453</v>
+        <v>1440</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -719,7 +719,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -739,14 +739,14 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296291</t>
+          <t>2026-04-24T04:51:34.299749</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -761,11 +761,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1456.00</t>
+          <t>1443.00</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1456</v>
+        <v>1443</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -804,14 +804,14 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296295</t>
+          <t>2026-04-24T04:51:34.299752</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -826,11 +826,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1422.00</t>
+          <t>1415.00</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1422</v>
+        <v>1415</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -869,14 +869,14 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296299</t>
+          <t>2026-04-24T04:51:34.299761</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -934,14 +934,14 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296303</t>
+          <t>2026-04-24T04:51:34.299767</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296307</t>
+          <t>2026-04-24T04:51:34.299774</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1021,11 +1021,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1457.00</t>
+          <t>1456.00</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1064,14 +1064,14 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296310</t>
+          <t>2026-04-24T04:51:34.299780</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1448.00</t>
+          <t>1445.00</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1448</v>
+        <v>1445</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1129,14 +1129,14 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296313</t>
+          <t>2026-04-24T04:51:34.299786</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296315</t>
+          <t>2026-04-24T04:51:34.299792</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1259,14 +1259,14 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296318</t>
+          <t>2026-04-24T04:51:34.299798</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1281,11 +1281,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1435.00</t>
+          <t>1422.00</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1435</v>
+        <v>1422</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1324,14 +1324,14 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296321</t>
+          <t>2026-04-24T04:51:34.299803</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1346,11 +1346,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1463</v>
+        <v>1453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1389,14 +1389,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296323</t>
+          <t>2026-04-24T04:51:34.299809</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1411,11 +1411,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1453.00</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1463</v>
+        <v>1453</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1454,14 +1454,14 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296326</t>
+          <t>2026-04-24T04:51:34.299815</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1469.00</t>
+          <t>1448.00</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1469</v>
+        <v>1448</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1519,14 +1519,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296329</t>
+          <t>2026-04-24T04:51:34.299822</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1541,11 +1541,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1465</v>
+        <v>1455</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1584,14 +1584,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296332</t>
+          <t>2026-04-24T04:51:34.299827</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1457.00</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1465</v>
+        <v>1457</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1649,14 +1649,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296335</t>
+          <t>2026-04-24T04:51:34.299831</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1714,14 +1714,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296338</t>
+          <t>2026-04-24T04:51:34.299834</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296340</t>
+          <t>2026-04-24T04:51:34.299837</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1801,11 +1801,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1469.00</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1465</v>
+        <v>1469</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296343</t>
+          <t>2026-04-24T04:51:34.299839</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1909,14 +1909,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296346</t>
+          <t>2026-04-24T04:51:34.299842</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296349</t>
+          <t>2026-04-24T04:51:34.299845</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1996,11 +1996,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1461.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1461</v>
+        <v>1465</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296351</t>
+          <t>2026-04-24T04:51:34.299848</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2061,11 +2061,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1475.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1475</v>
+        <v>1465</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2104,14 +2104,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296354</t>
+          <t>2026-04-24T04:51:34.299850</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2169,14 +2169,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296357</t>
+          <t>2026-04-24T04:51:34.299853</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2191,11 +2191,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296360</t>
+          <t>2026-04-24T04:51:34.299856</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2256,11 +2256,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1461.00</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1478</v>
+        <v>1461</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2299,14 +2299,14 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296362</t>
+          <t>2026-04-24T04:51:34.299859</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,11 +2321,11 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1474.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1474</v>
+        <v>1465</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2364,14 +2364,14 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296365</t>
+          <t>2026-04-24T04:51:34.299862</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2386,11 +2386,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1473.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1473</v>
+        <v>1463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2429,14 +2429,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296368</t>
+          <t>2026-04-24T04:51:34.299864</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,11 +2451,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1455.00</t>
+          <t>1474.00</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1455</v>
+        <v>1474</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2494,14 +2494,14 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296371</t>
+          <t>2026-04-24T04:51:34.299867</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2516,11 +2516,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1468.00</t>
+          <t>1478.00</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1468</v>
+        <v>1478</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2559,14 +2559,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296373</t>
+          <t>2026-04-24T04:51:34.299870</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2624,14 +2624,14 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296376</t>
+          <t>2026-04-24T04:51:34.299872</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2646,11 +2646,11 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296379</t>
+          <t>2026-04-24T04:51:34.299875</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2711,11 +2711,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1465.00</t>
+          <t>1475.00</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1465</v>
+        <v>1475</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2754,14 +2754,14 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296382</t>
+          <t>2026-04-24T04:51:34.299878</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2776,11 +2776,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1463.00</t>
+          <t>1473.00</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1463</v>
+        <v>1473</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>跌</t>
+          <t>涨</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2819,14 +2819,14 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296385</t>
+          <t>2026-04-24T04:51:34.299881</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2841,11 +2841,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2884,14 +2884,14 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296387</t>
+          <t>2026-04-24T04:51:34.299884</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2906,11 +2906,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>1471.00</t>
+          <t>1455.00</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1471</v>
+        <v>1455</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2949,14 +2949,14 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296390</t>
+          <t>2026-04-24T04:51:34.299886</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296393</t>
+          <t>2026-04-24T04:51:34.299889</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3036,11 +3036,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>1476.00</t>
+          <t>1463.00</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1476</v>
+        <v>1463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3079,14 +3079,14 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296396</t>
+          <t>2026-04-24T04:51:34.299892</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3101,11 +3101,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1477.00</t>
+          <t>1468.00</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1477</v>
+        <v>1468</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3144,14 +3144,14 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296398</t>
+          <t>2026-04-24T04:51:34.299894</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3166,11 +3166,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1478.00</t>
+          <t>1465.00</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1478</v>
+        <v>1465</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3209,14 +3209,14 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296401</t>
+          <t>2026-04-24T04:51:34.299897</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>--</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3274,14 +3274,14 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296404</t>
+          <t>2026-04-24T04:51:34.299900</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3296,11 +3296,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1481.00</t>
+          <t>1471.00</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1481</v>
+        <v>1471</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>涨</t>
+          <t>跌</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3339,14 +3339,14 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2026-04-23T04:47:38.296407</t>
+          <t>2026-04-24T04:51:34.299903</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t